--- a/Strivers List + other Problems.xlsx
+++ b/Strivers List + other Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973D696C-43F2-4D62-AE7F-A38373FD591A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BAA385-F0B4-4242-B3B4-DF67A801B55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12601,7 +12601,7 @@
     <row r="275" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="57"/>
       <c r="B275" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C275" s="2">
         <v>24</v>

--- a/Strivers List + other Problems.xlsx
+++ b/Strivers List + other Problems.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BAA385-F0B4-4242-B3B4-DF67A801B55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D5C601-7BE4-47CA-A254-5DD7D6EA6664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1838,7 +1838,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2011,6 +2011,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8511,7 +8512,7 @@
     <row r="167" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A167" s="62"/>
       <c r="B167" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C167" s="30">
         <v>16</v>
@@ -10649,7 +10650,7 @@
     <row r="223" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A223" s="57"/>
       <c r="B223" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C223" s="2">
         <v>12</v>
@@ -10686,7 +10687,7 @@
     <row r="224" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A224" s="57"/>
       <c r="B224" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C224" s="2">
         <v>13</v>
@@ -10723,7 +10724,7 @@
     <row r="225" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A225" s="57"/>
       <c r="B225" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C225" s="2">
         <v>14</v>
@@ -10760,7 +10761,7 @@
     <row r="226" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A226" s="57"/>
       <c r="B226" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226" s="2">
         <v>15</v>
@@ -10799,7 +10800,7 @@
     <row r="227" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A227" s="57"/>
       <c r="B227" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C227" s="2">
         <v>16</v>
@@ -10838,7 +10839,7 @@
     <row r="228" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A228" s="57"/>
       <c r="B228" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C228" s="2">
         <v>17</v>
@@ -10875,7 +10876,7 @@
     <row r="229" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A229" s="57"/>
       <c r="B229" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C229" s="2">
         <v>18</v>
@@ -11105,7 +11106,7 @@
     <row r="235" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A235" s="57"/>
       <c r="B235" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C235" s="2">
         <v>24</v>
@@ -11181,7 +11182,7 @@
     <row r="237" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A237" s="57"/>
       <c r="B237" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C237" s="2">
         <v>26</v>
@@ -11218,7 +11219,7 @@
     <row r="238" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A238" s="57"/>
       <c r="B238" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C238" s="2">
         <v>27</v>
@@ -11671,9 +11672,9 @@
       <c r="X249" s="1"/>
       <c r="Y249" s="1"/>
     </row>
-    <row r="250" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1"/>
-      <c r="B250" s="1"/>
+      <c r="B250" s="68"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="3"/>
@@ -11698,9 +11699,9 @@
       <c r="X250" s="1"/>
       <c r="Y250" s="1"/>
     </row>
-    <row r="251" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="1"/>
-      <c r="B251" s="1"/>
+      <c r="B251" s="68"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="3"/>
@@ -12718,7 +12719,7 @@
     <row r="278" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A278" s="57"/>
       <c r="B278" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C278" s="2">
         <v>27</v>

--- a/Strivers List + other Problems.xlsx
+++ b/Strivers List + other Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D5C601-7BE4-47CA-A254-5DD7D6EA6664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3220E384-019B-45EE-959A-25F9F337E0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1979,6 +1979,7 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2011,7 +2012,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2297,8 +2297,8 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="58"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -2412,7 +2412,7 @@
       <c r="Y5" s="1"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="59" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="50" t="b">
@@ -2457,7 +2457,7 @@
       <c r="Y6" s="1"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="59"/>
+      <c r="A7" s="60"/>
       <c r="B7" s="50" t="b">
         <v>0</v>
       </c>
@@ -2500,7 +2500,7 @@
       <c r="Y7" s="1"/>
     </row>
     <row r="8" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="59"/>
+      <c r="A8" s="60"/>
       <c r="B8" s="50" t="b">
         <v>0</v>
       </c>
@@ -2537,7 +2537,7 @@
       <c r="Y8" s="1"/>
     </row>
     <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="59"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="50" t="b">
         <v>1</v>
       </c>
@@ -2574,7 +2574,7 @@
       <c r="Y9" s="1"/>
     </row>
     <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="59"/>
+      <c r="A10" s="60"/>
       <c r="B10" s="50" t="b">
         <v>1</v>
       </c>
@@ -2613,7 +2613,7 @@
       <c r="Y10" s="1"/>
     </row>
     <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="59"/>
+      <c r="A11" s="60"/>
       <c r="B11" s="50" t="b">
         <v>1</v>
       </c>
@@ -2650,7 +2650,7 @@
       <c r="Y11" s="1"/>
     </row>
     <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="59"/>
+      <c r="A12" s="60"/>
       <c r="B12" s="50" t="b">
         <v>1</v>
       </c>
@@ -2683,7 +2683,7 @@
       <c r="Y12" s="1"/>
     </row>
     <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59"/>
+      <c r="A13" s="60"/>
       <c r="B13" s="50" t="b">
         <v>1</v>
       </c>
@@ -2724,7 +2724,7 @@
       <c r="Y13" s="1"/>
     </row>
     <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="59"/>
+      <c r="A14" s="60"/>
       <c r="B14" s="50" t="b">
         <v>1</v>
       </c>
@@ -2761,7 +2761,7 @@
       <c r="Y14" s="1"/>
     </row>
     <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="59"/>
+      <c r="A15" s="60"/>
       <c r="B15" s="50" t="b">
         <v>1</v>
       </c>
@@ -2798,7 +2798,7 @@
       <c r="Y15" s="1"/>
     </row>
     <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59"/>
+      <c r="A16" s="60"/>
       <c r="B16" s="50" t="b">
         <v>1</v>
       </c>
@@ -2835,7 +2835,7 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="59"/>
+      <c r="A17" s="60"/>
       <c r="B17" s="50" t="b">
         <v>1</v>
       </c>
@@ -2876,7 +2876,7 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="59"/>
+      <c r="A18" s="60"/>
       <c r="B18" s="50" t="b">
         <v>0</v>
       </c>
@@ -2913,7 +2913,7 @@
       <c r="Y18" s="1"/>
     </row>
     <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59"/>
+      <c r="A19" s="60"/>
       <c r="B19" s="50" t="b">
         <v>1</v>
       </c>
@@ -2950,7 +2950,7 @@
       <c r="Y19" s="1"/>
     </row>
     <row r="20" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="59"/>
+      <c r="A20" s="60"/>
       <c r="B20" s="50" t="b">
         <v>1</v>
       </c>
@@ -2987,7 +2987,7 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="59"/>
+      <c r="A21" s="60"/>
       <c r="B21" s="50" t="b">
         <v>0</v>
       </c>
@@ -3024,7 +3024,7 @@
       <c r="Y21" s="1"/>
     </row>
     <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59"/>
+      <c r="A22" s="60"/>
       <c r="B22" s="50" t="b">
         <v>1</v>
       </c>
@@ -3063,7 +3063,7 @@
       <c r="Y22" s="1"/>
     </row>
     <row r="23" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="59"/>
+      <c r="A23" s="60"/>
       <c r="B23" s="50" t="b">
         <v>0</v>
       </c>
@@ -3100,7 +3100,7 @@
       <c r="Y23" s="1"/>
     </row>
     <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="59"/>
+      <c r="A24" s="60"/>
       <c r="B24" s="50" t="b">
         <v>0</v>
       </c>
@@ -3141,7 +3141,7 @@
       <c r="Y24" s="1"/>
     </row>
     <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="59"/>
+      <c r="A25" s="60"/>
       <c r="B25" s="50" t="b">
         <v>1</v>
       </c>
@@ -3184,7 +3184,7 @@
       <c r="Y25" s="1"/>
     </row>
     <row r="26" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="59"/>
+      <c r="A26" s="60"/>
       <c r="B26" s="50" t="b">
         <v>0</v>
       </c>
@@ -3227,7 +3227,7 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="59"/>
+      <c r="A27" s="60"/>
       <c r="B27" s="50" t="b">
         <v>0</v>
       </c>
@@ -3264,7 +3264,7 @@
       <c r="Y27" s="1"/>
     </row>
     <row r="28" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="59"/>
+      <c r="A28" s="60"/>
       <c r="B28" s="50" t="b">
         <v>0</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="29" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="59"/>
+      <c r="A29" s="60"/>
       <c r="B29" s="50" t="b">
         <v>0</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="59"/>
+      <c r="A30" s="60"/>
       <c r="B30" s="50" t="b">
         <v>1</v>
       </c>
@@ -3383,7 +3383,7 @@
       <c r="Y30" s="1"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="59"/>
+      <c r="A31" s="60"/>
       <c r="B31" s="50" t="b">
         <v>0</v>
       </c>
@@ -3426,7 +3426,7 @@
       <c r="Y31" s="1"/>
     </row>
     <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="59"/>
+      <c r="A32" s="60"/>
       <c r="B32" s="50" t="b">
         <v>0</v>
       </c>
@@ -3463,7 +3463,7 @@
       <c r="Y32" s="1"/>
     </row>
     <row r="33" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="59"/>
+      <c r="A33" s="60"/>
       <c r="B33" s="50" t="b">
         <v>0</v>
       </c>
@@ -3504,7 +3504,7 @@
       <c r="Y33" s="1"/>
     </row>
     <row r="34" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="59"/>
+      <c r="A34" s="60"/>
       <c r="B34" s="50" t="b">
         <v>1</v>
       </c>
@@ -3541,7 +3541,7 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="59"/>
+      <c r="A35" s="60"/>
       <c r="B35" s="50" t="b">
         <v>1</v>
       </c>
@@ -3582,7 +3582,7 @@
       <c r="Y35" s="1"/>
     </row>
     <row r="36" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="59"/>
+      <c r="A36" s="60"/>
       <c r="B36" s="50" t="b">
         <v>1</v>
       </c>
@@ -3623,7 +3623,7 @@
       <c r="Y36" s="1"/>
     </row>
     <row r="37" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="59"/>
+      <c r="A37" s="60"/>
       <c r="B37" s="50" t="b">
         <v>0</v>
       </c>
@@ -3664,7 +3664,7 @@
       <c r="Y37" s="1"/>
     </row>
     <row r="38" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="59"/>
+      <c r="A38" s="60"/>
       <c r="B38" s="50" t="b">
         <v>0</v>
       </c>
@@ -3705,7 +3705,7 @@
       <c r="Y38" s="1"/>
     </row>
     <row r="39" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="59"/>
+      <c r="A39" s="60"/>
       <c r="B39" s="50" t="b">
         <v>0</v>
       </c>
@@ -3742,7 +3742,7 @@
       <c r="Y39" s="1"/>
     </row>
     <row r="40" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="59"/>
+      <c r="A40" s="60"/>
       <c r="B40" s="50" t="b">
         <v>1</v>
       </c>
@@ -3779,7 +3779,7 @@
       <c r="Y40" s="1"/>
     </row>
     <row r="41" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="59"/>
+      <c r="A41" s="60"/>
       <c r="B41" s="50" t="b">
         <v>1</v>
       </c>
@@ -3818,7 +3818,7 @@
       <c r="Y41" s="1"/>
     </row>
     <row r="42" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="59"/>
+      <c r="A42" s="60"/>
       <c r="B42" s="50" t="b">
         <v>1</v>
       </c>
@@ -3861,7 +3861,7 @@
       <c r="Y42" s="1"/>
     </row>
     <row r="43" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="59"/>
+      <c r="A43" s="60"/>
       <c r="B43" s="50" t="b">
         <v>0</v>
       </c>
@@ -3898,7 +3898,7 @@
       <c r="Y43" s="1"/>
     </row>
     <row r="44" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="59"/>
+      <c r="A44" s="60"/>
       <c r="B44" s="50" t="b">
         <v>0</v>
       </c>
@@ -3939,7 +3939,7 @@
       <c r="Y44" s="1"/>
     </row>
     <row r="45" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="59"/>
+      <c r="A45" s="60"/>
       <c r="B45" s="50" t="b">
         <v>0</v>
       </c>
@@ -3982,7 +3982,7 @@
       <c r="Y45" s="1"/>
     </row>
     <row r="46" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="59"/>
+      <c r="A46" s="60"/>
       <c r="B46" s="50" t="b">
         <v>0</v>
       </c>
@@ -4021,7 +4021,7 @@
       <c r="Y46" s="1"/>
     </row>
     <row r="47" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="59"/>
+      <c r="A47" s="60"/>
       <c r="B47" s="50" t="b">
         <v>0</v>
       </c>
@@ -4058,7 +4058,7 @@
       <c r="Y47" s="1"/>
     </row>
     <row r="48" spans="1:25" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="59"/>
+      <c r="A48" s="60"/>
       <c r="B48" s="50" t="b">
         <v>0</v>
       </c>
@@ -4215,7 +4215,7 @@
       <c r="Y52" s="1"/>
     </row>
     <row r="53" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="60" t="s">
+      <c r="A53" s="61" t="s">
         <v>59</v>
       </c>
       <c r="B53" s="50" t="b">
@@ -4258,7 +4258,7 @@
       <c r="Y53" s="1"/>
     </row>
     <row r="54" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="61"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="50" t="b">
         <v>1</v>
       </c>
@@ -4295,7 +4295,7 @@
       <c r="Y54" s="1"/>
     </row>
     <row r="55" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="61"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="50" t="b">
         <v>1</v>
       </c>
@@ -4332,7 +4332,7 @@
       <c r="Y55" s="1"/>
     </row>
     <row r="56" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="61"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="50" t="b">
         <v>1</v>
       </c>
@@ -4369,7 +4369,7 @@
       <c r="Y56" s="1"/>
     </row>
     <row r="57" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="61"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="50" t="b">
         <v>1</v>
       </c>
@@ -4406,7 +4406,7 @@
       <c r="Y57" s="1"/>
     </row>
     <row r="58" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="61"/>
+      <c r="A58" s="62"/>
       <c r="B58" s="50" t="b">
         <v>1</v>
       </c>
@@ -4443,7 +4443,7 @@
       <c r="Y58" s="1"/>
     </row>
     <row r="59" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="62"/>
+      <c r="A59" s="63"/>
       <c r="B59" s="50" t="b">
         <v>1</v>
       </c>
@@ -4482,7 +4482,7 @@
       <c r="Y59" s="1"/>
     </row>
     <row r="60" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="62"/>
+      <c r="A60" s="63"/>
       <c r="B60" s="50" t="b">
         <v>1</v>
       </c>
@@ -4519,7 +4519,7 @@
       <c r="Y60" s="1"/>
     </row>
     <row r="61" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="62"/>
+      <c r="A61" s="63"/>
       <c r="B61" s="50" t="b">
         <v>1</v>
       </c>
@@ -4556,7 +4556,7 @@
       <c r="Y61" s="1"/>
     </row>
     <row r="62" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="62"/>
+      <c r="A62" s="63"/>
       <c r="B62" s="50" t="b">
         <v>0</v>
       </c>
@@ -4593,7 +4593,7 @@
       <c r="Y62" s="1"/>
     </row>
     <row r="63" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="62"/>
+      <c r="A63" s="63"/>
       <c r="B63" s="50" t="b">
         <v>0</v>
       </c>
@@ -4630,7 +4630,7 @@
       <c r="Y63" s="1"/>
     </row>
     <row r="64" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="62"/>
+      <c r="A64" s="63"/>
       <c r="B64" s="50" t="b">
         <v>0</v>
       </c>
@@ -4667,7 +4667,7 @@
       <c r="Y64" s="1"/>
     </row>
     <row r="65" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="62"/>
+      <c r="A65" s="63"/>
       <c r="B65" s="50" t="b">
         <v>0</v>
       </c>
@@ -4704,7 +4704,7 @@
       <c r="Y65" s="1"/>
     </row>
     <row r="66" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="62"/>
+      <c r="A66" s="63"/>
       <c r="B66" s="50" t="b">
         <v>1</v>
       </c>
@@ -4741,7 +4741,7 @@
       <c r="Y66" s="1"/>
     </row>
     <row r="67" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="62"/>
+      <c r="A67" s="63"/>
       <c r="B67" s="50" t="b">
         <v>1</v>
       </c>
@@ -4778,7 +4778,7 @@
       <c r="Y67" s="1"/>
     </row>
     <row r="68" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="62"/>
+      <c r="A68" s="63"/>
       <c r="B68" s="50" t="b">
         <v>1</v>
       </c>
@@ -4817,7 +4817,7 @@
       <c r="Y68" s="1"/>
     </row>
     <row r="69" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="62"/>
+      <c r="A69" s="63"/>
       <c r="B69" s="50" t="b">
         <v>0</v>
       </c>
@@ -4964,7 +4964,7 @@
       <c r="Y73" s="1"/>
     </row>
     <row r="74" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="64" t="s">
+      <c r="A74" s="65" t="s">
         <v>66</v>
       </c>
       <c r="B74" s="50" t="b">
@@ -5007,7 +5007,7 @@
       <c r="Y74" s="1"/>
     </row>
     <row r="75" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="62"/>
+      <c r="A75" s="63"/>
       <c r="B75" s="50" t="b">
         <v>0</v>
       </c>
@@ -5046,7 +5046,7 @@
       <c r="Y75" s="1"/>
     </row>
     <row r="76" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="62"/>
+      <c r="A76" s="63"/>
       <c r="B76" s="50" t="b">
         <v>0</v>
       </c>
@@ -5083,7 +5083,7 @@
       <c r="Y76" s="1"/>
     </row>
     <row r="77" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="62"/>
+      <c r="A77" s="63"/>
       <c r="B77" s="50" t="b">
         <v>1</v>
       </c>
@@ -5120,7 +5120,7 @@
       <c r="Y77" s="1"/>
     </row>
     <row r="78" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A78" s="62"/>
+      <c r="A78" s="63"/>
       <c r="B78" s="50" t="b">
         <v>1</v>
       </c>
@@ -5159,7 +5159,7 @@
       <c r="Y78" s="1"/>
     </row>
     <row r="79" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="62"/>
+      <c r="A79" s="63"/>
       <c r="B79" s="50" t="b">
         <v>0</v>
       </c>
@@ -5198,7 +5198,7 @@
       <c r="Y79" s="1"/>
     </row>
     <row r="80" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A80" s="62"/>
+      <c r="A80" s="63"/>
       <c r="B80" s="50" t="b">
         <v>0</v>
       </c>
@@ -5235,7 +5235,7 @@
       <c r="Y80" s="1"/>
     </row>
     <row r="81" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A81" s="62"/>
+      <c r="A81" s="63"/>
       <c r="B81" s="50" t="b">
         <v>0</v>
       </c>
@@ -5272,7 +5272,7 @@
       <c r="Y81" s="1"/>
     </row>
     <row r="82" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A82" s="62"/>
+      <c r="A82" s="63"/>
       <c r="B82" s="50" t="b">
         <v>0</v>
       </c>
@@ -5309,7 +5309,7 @@
       <c r="Y82" s="1"/>
     </row>
     <row r="83" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A83" s="62"/>
+      <c r="A83" s="63"/>
       <c r="B83" s="50" t="b">
         <v>1</v>
       </c>
@@ -5348,7 +5348,7 @@
       <c r="Y83" s="1"/>
     </row>
     <row r="84" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A84" s="62"/>
+      <c r="A84" s="63"/>
       <c r="B84" s="50" t="b">
         <v>0</v>
       </c>
@@ -5389,7 +5389,7 @@
       <c r="Y84" s="1"/>
     </row>
     <row r="85" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A85" s="62"/>
+      <c r="A85" s="63"/>
       <c r="B85" s="50" t="b">
         <v>0</v>
       </c>
@@ -5428,7 +5428,7 @@
       <c r="Y85" s="1"/>
     </row>
     <row r="86" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A86" s="62"/>
+      <c r="A86" s="63"/>
       <c r="B86" s="50" t="b">
         <v>0</v>
       </c>
@@ -5465,7 +5465,7 @@
       <c r="Y86" s="1"/>
     </row>
     <row r="87" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A87" s="62"/>
+      <c r="A87" s="63"/>
       <c r="B87" s="50" t="b">
         <v>1</v>
       </c>
@@ -5504,7 +5504,7 @@
       <c r="Y87" s="1"/>
     </row>
     <row r="88" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A88" s="62"/>
+      <c r="A88" s="63"/>
       <c r="B88" s="50" t="b">
         <v>0</v>
       </c>
@@ -5543,7 +5543,7 @@
       <c r="Y88" s="1"/>
     </row>
     <row r="89" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A89" s="62"/>
+      <c r="A89" s="63"/>
       <c r="B89" s="50" t="b">
         <v>0</v>
       </c>
@@ -5580,7 +5580,7 @@
       <c r="Y89" s="1"/>
     </row>
     <row r="90" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A90" s="62"/>
+      <c r="A90" s="63"/>
       <c r="B90" s="50" t="b">
         <v>0</v>
       </c>
@@ -5617,7 +5617,7 @@
       <c r="Y90" s="1"/>
     </row>
     <row r="91" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A91" s="62"/>
+      <c r="A91" s="63"/>
       <c r="B91" s="50" t="b">
         <v>0</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="Y95" s="1"/>
     </row>
     <row r="96" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A96" s="65" t="s">
+      <c r="A96" s="66" t="s">
         <v>84</v>
       </c>
       <c r="B96" s="50" t="b">
@@ -5797,7 +5797,7 @@
       <c r="Y96" s="1"/>
     </row>
     <row r="97" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A97" s="57"/>
+      <c r="A97" s="58"/>
       <c r="B97" s="50" t="b">
         <v>1</v>
       </c>
@@ -5837,7 +5837,7 @@
       <c r="Y97" s="1"/>
     </row>
     <row r="98" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A98" s="57"/>
+      <c r="A98" s="58"/>
       <c r="B98" s="50" t="b">
         <v>1</v>
       </c>
@@ -5879,7 +5879,7 @@
       <c r="Y98" s="1"/>
     </row>
     <row r="99" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A99" s="57"/>
+      <c r="A99" s="58"/>
       <c r="B99" s="50" t="b">
         <v>0</v>
       </c>
@@ -5919,7 +5919,7 @@
       <c r="Y99" s="1"/>
     </row>
     <row r="100" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A100" s="57"/>
+      <c r="A100" s="58"/>
       <c r="B100" s="50" t="b">
         <v>0</v>
       </c>
@@ -5959,7 +5959,7 @@
       <c r="Y100" s="1"/>
     </row>
     <row r="101" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A101" s="57"/>
+      <c r="A101" s="58"/>
       <c r="B101" s="50" t="b">
         <v>0</v>
       </c>
@@ -6001,7 +6001,7 @@
       <c r="Y101" s="1"/>
     </row>
     <row r="102" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A102" s="57"/>
+      <c r="A102" s="58"/>
       <c r="B102" s="50" t="b">
         <v>1</v>
       </c>
@@ -6039,7 +6039,7 @@
       <c r="Y102" s="1"/>
     </row>
     <row r="103" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A103" s="57"/>
+      <c r="A103" s="58"/>
       <c r="B103" s="50" t="b">
         <v>1</v>
       </c>
@@ -6077,7 +6077,7 @@
       <c r="Y103" s="1"/>
     </row>
     <row r="104" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A104" s="57"/>
+      <c r="A104" s="58"/>
       <c r="B104" s="50" t="b">
         <v>1</v>
       </c>
@@ -6119,7 +6119,7 @@
       <c r="Y104" s="1"/>
     </row>
     <row r="105" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A105" s="57"/>
+      <c r="A105" s="58"/>
       <c r="B105" s="50" t="b">
         <v>0</v>
       </c>
@@ -6159,7 +6159,7 @@
       <c r="Y105" s="1"/>
     </row>
     <row r="106" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A106" s="57"/>
+      <c r="A106" s="58"/>
       <c r="B106" s="50" t="b">
         <v>0</v>
       </c>
@@ -6201,7 +6201,7 @@
       <c r="Y106" s="1"/>
     </row>
     <row r="107" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A107" s="57"/>
+      <c r="A107" s="58"/>
       <c r="B107" s="50" t="b">
         <v>0</v>
       </c>
@@ -6239,7 +6239,7 @@
       <c r="Y107" s="1"/>
     </row>
     <row r="108" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A108" s="57"/>
+      <c r="A108" s="58"/>
       <c r="B108" s="50" t="b">
         <v>0</v>
       </c>
@@ -6277,7 +6277,7 @@
       <c r="Y108" s="1"/>
     </row>
     <row r="109" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A109" s="57"/>
+      <c r="A109" s="58"/>
       <c r="B109" s="50" t="b">
         <v>0</v>
       </c>
@@ -6373,7 +6373,7 @@
       <c r="Y111" s="1"/>
     </row>
     <row r="112" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A112" s="61" t="s">
+      <c r="A112" s="62" t="s">
         <v>103</v>
       </c>
       <c r="B112" s="50" t="b">
@@ -6416,7 +6416,7 @@
       <c r="Y112" s="1"/>
     </row>
     <row r="113" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A113" s="61"/>
+      <c r="A113" s="62"/>
       <c r="B113" s="50" t="b">
         <v>0</v>
       </c>
@@ -6449,7 +6449,7 @@
       <c r="Y113" s="1"/>
     </row>
     <row r="114" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A114" s="62"/>
+      <c r="A114" s="63"/>
       <c r="B114" s="50" t="b">
         <v>0</v>
       </c>
@@ -6490,7 +6490,7 @@
       <c r="Y114" s="1"/>
     </row>
     <row r="115" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A115" s="62"/>
+      <c r="A115" s="63"/>
       <c r="B115" s="50" t="b">
         <v>0</v>
       </c>
@@ -6531,7 +6531,7 @@
       <c r="Y115" s="1"/>
     </row>
     <row r="116" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="62"/>
+      <c r="A116" s="63"/>
       <c r="B116" s="50" t="b">
         <v>0</v>
       </c>
@@ -6570,7 +6570,7 @@
       <c r="Y116" s="1"/>
     </row>
     <row r="117" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="62"/>
+      <c r="A117" s="63"/>
       <c r="B117" s="50" t="b">
         <v>0</v>
       </c>
@@ -6611,7 +6611,7 @@
       <c r="Y117" s="1"/>
     </row>
     <row r="118" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A118" s="62"/>
+      <c r="A118" s="63"/>
       <c r="B118" s="50" t="b">
         <v>0</v>
       </c>
@@ -6652,7 +6652,7 @@
       <c r="Y118" s="1"/>
     </row>
     <row r="119" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A119" s="62"/>
+      <c r="A119" s="63"/>
       <c r="B119" s="50" t="b">
         <v>0</v>
       </c>
@@ -6693,7 +6693,7 @@
       <c r="Y119" s="1"/>
     </row>
     <row r="120" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A120" s="62"/>
+      <c r="A120" s="63"/>
       <c r="B120" s="50" t="b">
         <v>0</v>
       </c>
@@ -6734,7 +6734,7 @@
       <c r="Y120" s="1"/>
     </row>
     <row r="121" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A121" s="62"/>
+      <c r="A121" s="63"/>
       <c r="B121" s="50" t="b">
         <v>0</v>
       </c>
@@ -6771,7 +6771,7 @@
       <c r="Y121" s="1"/>
     </row>
     <row r="122" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A122" s="62"/>
+      <c r="A122" s="63"/>
       <c r="B122" s="50" t="b">
         <v>0</v>
       </c>
@@ -6810,7 +6810,7 @@
       <c r="Y122" s="1"/>
     </row>
     <row r="123" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A123" s="62"/>
+      <c r="A123" s="63"/>
       <c r="B123" s="50" t="b">
         <v>0</v>
       </c>
@@ -6849,7 +6849,7 @@
       <c r="Y123" s="1"/>
     </row>
     <row r="124" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A124" s="62"/>
+      <c r="A124" s="63"/>
       <c r="B124" s="50" t="b">
         <v>0</v>
       </c>
@@ -6886,7 +6886,7 @@
       <c r="Y124" s="1"/>
     </row>
     <row r="125" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A125" s="62"/>
+      <c r="A125" s="63"/>
       <c r="B125" s="50" t="b">
         <v>0</v>
       </c>
@@ -6923,7 +6923,7 @@
       <c r="Y125" s="1"/>
     </row>
     <row r="126" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A126" s="62"/>
+      <c r="A126" s="63"/>
       <c r="B126" s="50" t="b">
         <v>0</v>
       </c>
@@ -6960,7 +6960,7 @@
       <c r="Y126" s="1"/>
     </row>
     <row r="127" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A127" s="62"/>
+      <c r="A127" s="63"/>
       <c r="B127" s="50" t="b">
         <v>0</v>
       </c>
@@ -6999,7 +6999,7 @@
       <c r="Y127" s="1"/>
     </row>
     <row r="128" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A128" s="62"/>
+      <c r="A128" s="63"/>
       <c r="B128" s="50" t="b">
         <v>0</v>
       </c>
@@ -7036,7 +7036,7 @@
       <c r="Y128" s="1"/>
     </row>
     <row r="129" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A129" s="62"/>
+      <c r="A129" s="63"/>
       <c r="B129" s="50" t="b">
         <v>0</v>
       </c>
@@ -7141,7 +7141,7 @@
       <c r="Y131" s="1"/>
     </row>
     <row r="132" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A132" s="67" t="s">
+      <c r="A132" s="68" t="s">
         <v>121</v>
       </c>
       <c r="B132" s="50" t="b">
@@ -7184,7 +7184,7 @@
       <c r="Y132" s="1"/>
     </row>
     <row r="133" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A133" s="62"/>
+      <c r="A133" s="63"/>
       <c r="B133" s="50" t="b">
         <v>0</v>
       </c>
@@ -7225,7 +7225,7 @@
       <c r="Y133" s="1"/>
     </row>
     <row r="134" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A134" s="62"/>
+      <c r="A134" s="63"/>
       <c r="B134" s="50" t="b">
         <v>0</v>
       </c>
@@ -7266,7 +7266,7 @@
       <c r="Y134" s="1"/>
     </row>
     <row r="135" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A135" s="62"/>
+      <c r="A135" s="63"/>
       <c r="B135" s="50" t="b">
         <v>0</v>
       </c>
@@ -7307,7 +7307,7 @@
       <c r="Y135" s="1"/>
     </row>
     <row r="136" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A136" s="62"/>
+      <c r="A136" s="63"/>
       <c r="B136" s="50" t="b">
         <v>0</v>
       </c>
@@ -7348,7 +7348,7 @@
       <c r="Y136" s="1"/>
     </row>
     <row r="137" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A137" s="62"/>
+      <c r="A137" s="63"/>
       <c r="B137" s="50" t="b">
         <v>0</v>
       </c>
@@ -7387,7 +7387,7 @@
       <c r="Y137" s="1"/>
     </row>
     <row r="138" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A138" s="62"/>
+      <c r="A138" s="63"/>
       <c r="B138" s="50" t="b">
         <v>0</v>
       </c>
@@ -7426,7 +7426,7 @@
       <c r="Y138" s="1"/>
     </row>
     <row r="139" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A139" s="62"/>
+      <c r="A139" s="63"/>
       <c r="B139" s="50" t="b">
         <v>0</v>
       </c>
@@ -7463,7 +7463,7 @@
       <c r="Y139" s="1"/>
     </row>
     <row r="140" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A140" s="62"/>
+      <c r="A140" s="63"/>
       <c r="B140" s="50" t="b">
         <v>0</v>
       </c>
@@ -7504,7 +7504,7 @@
       <c r="Y140" s="1"/>
     </row>
     <row r="141" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A141" s="62"/>
+      <c r="A141" s="63"/>
       <c r="B141" s="50" t="b">
         <v>0</v>
       </c>
@@ -7541,7 +7541,7 @@
       <c r="Y141" s="1"/>
     </row>
     <row r="142" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A142" s="62"/>
+      <c r="A142" s="63"/>
       <c r="B142" s="50" t="b">
         <v>0</v>
       </c>
@@ -7578,7 +7578,7 @@
       <c r="Y142" s="1"/>
     </row>
     <row r="143" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A143" s="62"/>
+      <c r="A143" s="63"/>
       <c r="B143" s="50" t="b">
         <v>0</v>
       </c>
@@ -7615,7 +7615,7 @@
       <c r="Y143" s="1"/>
     </row>
     <row r="144" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A144" s="62"/>
+      <c r="A144" s="63"/>
       <c r="B144" s="50" t="b">
         <v>0</v>
       </c>
@@ -7656,7 +7656,7 @@
       <c r="Y144" s="1"/>
     </row>
     <row r="145" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A145" s="62"/>
+      <c r="A145" s="63"/>
       <c r="B145" s="50" t="b">
         <v>0</v>
       </c>
@@ -7697,7 +7697,7 @@
       <c r="Y145" s="1"/>
     </row>
     <row r="146" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A146" s="62"/>
+      <c r="A146" s="63"/>
       <c r="B146" s="50" t="b">
         <v>0</v>
       </c>
@@ -7738,7 +7738,7 @@
       <c r="Y146" s="1"/>
     </row>
     <row r="147" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A147" s="62"/>
+      <c r="A147" s="63"/>
       <c r="B147" s="50" t="b">
         <v>0</v>
       </c>
@@ -7779,7 +7779,7 @@
       <c r="Y147" s="1"/>
     </row>
     <row r="148" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A148" s="62"/>
+      <c r="A148" s="63"/>
       <c r="B148" s="50" t="b">
         <v>0</v>
       </c>
@@ -7874,7 +7874,7 @@
       <c r="Y150" s="1"/>
     </row>
     <row r="151" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A151" s="67" t="s">
+      <c r="A151" s="68" t="s">
         <v>149</v>
       </c>
       <c r="B151" s="50" t="b">
@@ -7917,7 +7917,7 @@
       <c r="Y151" s="1"/>
     </row>
     <row r="152" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A152" s="62"/>
+      <c r="A152" s="63"/>
       <c r="B152" s="50" t="b">
         <v>0</v>
       </c>
@@ -7958,7 +7958,7 @@
       <c r="Y152" s="1"/>
     </row>
     <row r="153" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A153" s="62"/>
+      <c r="A153" s="63"/>
       <c r="B153" s="50" t="b">
         <v>0</v>
       </c>
@@ -7999,7 +7999,7 @@
       <c r="Y153" s="1"/>
     </row>
     <row r="154" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A154" s="62"/>
+      <c r="A154" s="63"/>
       <c r="B154" s="50" t="b">
         <v>0</v>
       </c>
@@ -8034,7 +8034,7 @@
       <c r="Y154" s="1"/>
     </row>
     <row r="155" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A155" s="62"/>
+      <c r="A155" s="63"/>
       <c r="B155" s="50" t="b">
         <v>0</v>
       </c>
@@ -8073,7 +8073,7 @@
       <c r="Y155" s="1"/>
     </row>
     <row r="156" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A156" s="62"/>
+      <c r="A156" s="63"/>
       <c r="B156" s="50" t="b">
         <v>0</v>
       </c>
@@ -8114,7 +8114,7 @@
       <c r="Y156" s="1"/>
     </row>
     <row r="157" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A157" s="62"/>
+      <c r="A157" s="63"/>
       <c r="B157" s="50" t="b">
         <v>0</v>
       </c>
@@ -8155,7 +8155,7 @@
       <c r="Y157" s="1"/>
     </row>
     <row r="158" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A158" s="62"/>
+      <c r="A158" s="63"/>
       <c r="B158" s="50" t="b">
         <v>0</v>
       </c>
@@ -8196,7 +8196,7 @@
       <c r="Y158" s="1"/>
     </row>
     <row r="159" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A159" s="62"/>
+      <c r="A159" s="63"/>
       <c r="B159" s="50" t="b">
         <v>0</v>
       </c>
@@ -8237,7 +8237,7 @@
       <c r="Y159" s="1"/>
     </row>
     <row r="160" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A160" s="62"/>
+      <c r="A160" s="63"/>
       <c r="B160" s="50" t="b">
         <v>0</v>
       </c>
@@ -8276,7 +8276,7 @@
       <c r="Y160" s="1"/>
     </row>
     <row r="161" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A161" s="62"/>
+      <c r="A161" s="63"/>
       <c r="B161" s="50" t="b">
         <v>0</v>
       </c>
@@ -8317,7 +8317,7 @@
       <c r="Y161" s="1"/>
     </row>
     <row r="162" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A162" s="62"/>
+      <c r="A162" s="63"/>
       <c r="B162" s="50" t="b">
         <v>0</v>
       </c>
@@ -8356,7 +8356,7 @@
       <c r="Y162" s="1"/>
     </row>
     <row r="163" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A163" s="62"/>
+      <c r="A163" s="63"/>
       <c r="B163" s="50" t="b">
         <v>0</v>
       </c>
@@ -8397,7 +8397,7 @@
       <c r="Y163" s="1"/>
     </row>
     <row r="164" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A164" s="62"/>
+      <c r="A164" s="63"/>
       <c r="B164" s="50" t="b">
         <v>0</v>
       </c>
@@ -8436,7 +8436,7 @@
       <c r="Y164" s="1"/>
     </row>
     <row r="165" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A165" s="62"/>
+      <c r="A165" s="63"/>
       <c r="B165" s="50" t="b">
         <v>0</v>
       </c>
@@ -8473,7 +8473,7 @@
       <c r="Y165" s="1"/>
     </row>
     <row r="166" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A166" s="62"/>
+      <c r="A166" s="63"/>
       <c r="B166" s="50" t="b">
         <v>0</v>
       </c>
@@ -8510,7 +8510,7 @@
       <c r="Y166" s="1"/>
     </row>
     <row r="167" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A167" s="62"/>
+      <c r="A167" s="63"/>
       <c r="B167" s="50" t="b">
         <v>1</v>
       </c>
@@ -8549,7 +8549,7 @@
       <c r="Y167" s="1"/>
     </row>
     <row r="168" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A168" s="62"/>
+      <c r="A168" s="63"/>
       <c r="B168" s="50" t="b">
         <v>0</v>
       </c>
@@ -8590,7 +8590,7 @@
       <c r="Y168" s="1"/>
     </row>
     <row r="169" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A169" s="62"/>
+      <c r="A169" s="63"/>
       <c r="B169" s="50" t="b">
         <v>0</v>
       </c>
@@ -8627,7 +8627,7 @@
       <c r="Y169" s="1"/>
     </row>
     <row r="170" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A170" s="62"/>
+      <c r="A170" s="63"/>
       <c r="B170" s="50" t="b">
         <v>0</v>
       </c>
@@ -8668,7 +8668,7 @@
       <c r="Y170" s="1"/>
     </row>
     <row r="171" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A171" s="62"/>
+      <c r="A171" s="63"/>
       <c r="B171" s="50" t="b">
         <v>0</v>
       </c>
@@ -8709,7 +8709,7 @@
       <c r="Y171" s="1"/>
     </row>
     <row r="172" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A172" s="62"/>
+      <c r="A172" s="63"/>
       <c r="B172" s="50" t="b">
         <v>0</v>
       </c>
@@ -8750,7 +8750,7 @@
       <c r="Y172" s="1"/>
     </row>
     <row r="173" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A173" s="62"/>
+      <c r="A173" s="63"/>
       <c r="B173" s="50" t="b">
         <v>0</v>
       </c>
@@ -8789,7 +8789,7 @@
       <c r="Y173" s="1"/>
     </row>
     <row r="174" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A174" s="62"/>
+      <c r="A174" s="63"/>
       <c r="B174" s="50" t="b">
         <v>0</v>
       </c>
@@ -8830,7 +8830,7 @@
       <c r="Y174" s="1"/>
     </row>
     <row r="175" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A175" s="62"/>
+      <c r="A175" s="63"/>
       <c r="B175" s="50" t="b">
         <v>0</v>
       </c>
@@ -8871,7 +8871,7 @@
       <c r="Y175" s="1"/>
     </row>
     <row r="176" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A176" s="62"/>
+      <c r="A176" s="63"/>
       <c r="B176" s="50" t="b">
         <v>0</v>
       </c>
@@ -8910,7 +8910,7 @@
       <c r="Y176" s="1"/>
     </row>
     <row r="177" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A177" s="62"/>
+      <c r="A177" s="63"/>
       <c r="B177" s="50" t="b">
         <v>0</v>
       </c>
@@ -8949,7 +8949,7 @@
       <c r="Y177" s="1"/>
     </row>
     <row r="178" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A178" s="62"/>
+      <c r="A178" s="63"/>
       <c r="B178" s="50" t="b">
         <v>0</v>
       </c>
@@ -9089,7 +9089,7 @@
       <c r="Y181" s="1"/>
     </row>
     <row r="182" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A182" s="66" t="s">
+      <c r="A182" s="67" t="s">
         <v>181</v>
       </c>
       <c r="B182" s="50" t="b">
@@ -9130,7 +9130,7 @@
       <c r="Y182" s="1"/>
     </row>
     <row r="183" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A183" s="57"/>
+      <c r="A183" s="58"/>
       <c r="B183" s="50" t="b">
         <v>0</v>
       </c>
@@ -9171,7 +9171,7 @@
       <c r="Y183" s="1"/>
     </row>
     <row r="184" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A184" s="57"/>
+      <c r="A184" s="58"/>
       <c r="B184" s="50" t="b">
         <v>0</v>
       </c>
@@ -9212,7 +9212,7 @@
       <c r="Y184" s="1"/>
     </row>
     <row r="185" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A185" s="57"/>
+      <c r="A185" s="58"/>
       <c r="B185" s="50" t="b">
         <v>0</v>
       </c>
@@ -9253,7 +9253,7 @@
       <c r="Y185" s="1"/>
     </row>
     <row r="186" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A186" s="57"/>
+      <c r="A186" s="58"/>
       <c r="B186" s="50" t="b">
         <v>0</v>
       </c>
@@ -9294,7 +9294,7 @@
       <c r="Y186" s="1"/>
     </row>
     <row r="187" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A187" s="57"/>
+      <c r="A187" s="58"/>
       <c r="B187" s="50" t="b">
         <v>0</v>
       </c>
@@ -9335,7 +9335,7 @@
       <c r="Y187" s="1"/>
     </row>
     <row r="188" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A188" s="57"/>
+      <c r="A188" s="58"/>
       <c r="B188" s="50" t="b">
         <v>0</v>
       </c>
@@ -9376,7 +9376,7 @@
       <c r="Y188" s="1"/>
     </row>
     <row r="189" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A189" s="57"/>
+      <c r="A189" s="58"/>
       <c r="B189" s="50" t="b">
         <v>0</v>
       </c>
@@ -9417,7 +9417,7 @@
       <c r="Y189" s="1"/>
     </row>
     <row r="190" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A190" s="57"/>
+      <c r="A190" s="58"/>
       <c r="B190" s="50" t="b">
         <v>0</v>
       </c>
@@ -9458,7 +9458,7 @@
       <c r="Y190" s="1"/>
     </row>
     <row r="191" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A191" s="57"/>
+      <c r="A191" s="58"/>
       <c r="B191" s="50" t="b">
         <v>0</v>
       </c>
@@ -9499,7 +9499,7 @@
       <c r="Y191" s="1"/>
     </row>
     <row r="192" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A192" s="57"/>
+      <c r="A192" s="58"/>
       <c r="B192" s="50" t="b">
         <v>0</v>
       </c>
@@ -9540,7 +9540,7 @@
       <c r="Y192" s="1"/>
     </row>
     <row r="193" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A193" s="57"/>
+      <c r="A193" s="58"/>
       <c r="B193" s="50" t="b">
         <v>0</v>
       </c>
@@ -9579,7 +9579,7 @@
       <c r="Y193" s="1"/>
     </row>
     <row r="194" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A194" s="57"/>
+      <c r="A194" s="58"/>
       <c r="B194" s="50" t="b">
         <v>0</v>
       </c>
@@ -9674,7 +9674,7 @@
       <c r="Y196" s="1"/>
     </row>
     <row r="197" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A197" s="66" t="s">
+      <c r="A197" s="67" t="s">
         <v>208</v>
       </c>
       <c r="B197" s="50" t="b">
@@ -9715,7 +9715,7 @@
       <c r="Y197" s="1"/>
     </row>
     <row r="198" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A198" s="57"/>
+      <c r="A198" s="58"/>
       <c r="B198" s="50" t="b">
         <v>0</v>
       </c>
@@ -9754,7 +9754,7 @@
       <c r="Y198" s="1"/>
     </row>
     <row r="199" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A199" s="57"/>
+      <c r="A199" s="58"/>
       <c r="B199" s="50" t="b">
         <v>0</v>
       </c>
@@ -9793,7 +9793,7 @@
       <c r="Y199" s="1"/>
     </row>
     <row r="200" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A200" s="57"/>
+      <c r="A200" s="58"/>
       <c r="B200" s="50" t="b">
         <v>0</v>
       </c>
@@ -9832,7 +9832,7 @@
       <c r="Y200" s="1"/>
     </row>
     <row r="201" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A201" s="57"/>
+      <c r="A201" s="58"/>
       <c r="B201" s="50" t="b">
         <v>0</v>
       </c>
@@ -9871,7 +9871,7 @@
       <c r="Y201" s="1"/>
     </row>
     <row r="202" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A202" s="57"/>
+      <c r="A202" s="58"/>
       <c r="B202" s="50" t="b">
         <v>0</v>
       </c>
@@ -9968,7 +9968,7 @@
       <c r="Y204" s="1"/>
     </row>
     <row r="205" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A205" s="66" t="s">
+      <c r="A205" s="67" t="s">
         <v>227</v>
       </c>
       <c r="B205" s="50" t="b">
@@ -10009,7 +10009,7 @@
       <c r="Y205" s="1"/>
     </row>
     <row r="206" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A206" s="57"/>
+      <c r="A206" s="58"/>
       <c r="B206" s="50" t="b">
         <v>0</v>
       </c>
@@ -10048,7 +10048,7 @@
       <c r="Y206" s="1"/>
     </row>
     <row r="207" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A207" s="57"/>
+      <c r="A207" s="58"/>
       <c r="B207" s="50" t="b">
         <v>0</v>
       </c>
@@ -10087,7 +10087,7 @@
       <c r="Y207" s="1"/>
     </row>
     <row r="208" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A208" s="57"/>
+      <c r="A208" s="58"/>
       <c r="B208" s="50" t="b">
         <v>0</v>
       </c>
@@ -10126,7 +10126,7 @@
       <c r="Y208" s="1"/>
     </row>
     <row r="209" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A209" s="57"/>
+      <c r="A209" s="58"/>
       <c r="B209" s="50" t="b">
         <v>0</v>
       </c>
@@ -10219,11 +10219,11 @@
       <c r="Y211" s="1"/>
     </row>
     <row r="212" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A212" s="66" t="s">
+      <c r="A212" s="67" t="s">
         <v>241</v>
       </c>
       <c r="B212" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
@@ -10260,7 +10260,7 @@
       <c r="Y212" s="1"/>
     </row>
     <row r="213" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A213" s="66"/>
+      <c r="A213" s="67"/>
       <c r="B213" s="50" t="b">
         <v>0</v>
       </c>
@@ -10297,7 +10297,7 @@
       <c r="Y213" s="1"/>
     </row>
     <row r="214" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A214" s="57"/>
+      <c r="A214" s="58"/>
       <c r="B214" s="50" t="b">
         <v>0</v>
       </c>
@@ -10336,7 +10336,7 @@
       <c r="Y214" s="1"/>
     </row>
     <row r="215" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A215" s="57"/>
+      <c r="A215" s="58"/>
       <c r="B215" s="50" t="b">
         <v>0</v>
       </c>
@@ -10375,7 +10375,7 @@
       <c r="Y215" s="1"/>
     </row>
     <row r="216" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A216" s="57"/>
+      <c r="A216" s="58"/>
       <c r="B216" s="50" t="b">
         <v>0</v>
       </c>
@@ -10414,7 +10414,7 @@
       <c r="Y216" s="1"/>
     </row>
     <row r="217" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A217" s="57"/>
+      <c r="A217" s="58"/>
       <c r="B217" s="50" t="b">
         <v>0</v>
       </c>
@@ -10453,7 +10453,7 @@
       <c r="Y217" s="1"/>
     </row>
     <row r="218" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A218" s="57"/>
+      <c r="A218" s="58"/>
       <c r="B218" s="50" t="b">
         <v>0</v>
       </c>
@@ -10492,7 +10492,7 @@
       <c r="Y218" s="1"/>
     </row>
     <row r="219" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A219" s="57"/>
+      <c r="A219" s="58"/>
       <c r="B219" s="50" t="b">
         <v>0</v>
       </c>
@@ -10531,7 +10531,7 @@
       <c r="Y219" s="1"/>
     </row>
     <row r="220" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A220" s="57"/>
+      <c r="A220" s="58"/>
       <c r="B220" s="50" t="b">
         <v>0</v>
       </c>
@@ -10570,7 +10570,7 @@
       <c r="Y220" s="1"/>
     </row>
     <row r="221" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A221" s="57"/>
+      <c r="A221" s="58"/>
       <c r="B221" s="50" t="b">
         <v>0</v>
       </c>
@@ -10609,7 +10609,7 @@
       <c r="Y221" s="1"/>
     </row>
     <row r="222" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A222" s="57"/>
+      <c r="A222" s="58"/>
       <c r="B222" s="50" t="b">
         <v>0</v>
       </c>
@@ -10648,7 +10648,7 @@
       <c r="Y222" s="1"/>
     </row>
     <row r="223" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A223" s="57"/>
+      <c r="A223" s="58"/>
       <c r="B223" s="50" t="b">
         <v>0</v>
       </c>
@@ -10685,7 +10685,7 @@
       <c r="Y223" s="1"/>
     </row>
     <row r="224" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A224" s="57"/>
+      <c r="A224" s="58"/>
       <c r="B224" s="50" t="b">
         <v>0</v>
       </c>
@@ -10722,7 +10722,7 @@
       <c r="Y224" s="1"/>
     </row>
     <row r="225" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A225" s="57"/>
+      <c r="A225" s="58"/>
       <c r="B225" s="50" t="b">
         <v>0</v>
       </c>
@@ -10759,9 +10759,9 @@
       <c r="Y225" s="1"/>
     </row>
     <row r="226" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A226" s="57"/>
+      <c r="A226" s="58"/>
       <c r="B226" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226" s="2">
         <v>15</v>
@@ -10798,9 +10798,9 @@
       <c r="Y226" s="1"/>
     </row>
     <row r="227" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A227" s="57"/>
+      <c r="A227" s="58"/>
       <c r="B227" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C227" s="2">
         <v>16</v>
@@ -10837,7 +10837,7 @@
       <c r="Y227" s="1"/>
     </row>
     <row r="228" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A228" s="57"/>
+      <c r="A228" s="58"/>
       <c r="B228" s="50" t="b">
         <v>0</v>
       </c>
@@ -10874,7 +10874,7 @@
       <c r="Y228" s="1"/>
     </row>
     <row r="229" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A229" s="57"/>
+      <c r="A229" s="58"/>
       <c r="B229" s="50" t="b">
         <v>0</v>
       </c>
@@ -10913,7 +10913,7 @@
       <c r="Y229" s="1"/>
     </row>
     <row r="230" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A230" s="57"/>
+      <c r="A230" s="58"/>
       <c r="B230" s="50" t="b">
         <v>0</v>
       </c>
@@ -10952,7 +10952,7 @@
       <c r="Y230" s="1"/>
     </row>
     <row r="231" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A231" s="57"/>
+      <c r="A231" s="58"/>
       <c r="B231" s="50" t="b">
         <v>0</v>
       </c>
@@ -10991,7 +10991,7 @@
       <c r="Y231" s="1"/>
     </row>
     <row r="232" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A232" s="57"/>
+      <c r="A232" s="58"/>
       <c r="B232" s="50" t="b">
         <v>0</v>
       </c>
@@ -11030,7 +11030,7 @@
       <c r="Y232" s="1"/>
     </row>
     <row r="233" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A233" s="57"/>
+      <c r="A233" s="58"/>
       <c r="B233" s="50" t="b">
         <v>0</v>
       </c>
@@ -11067,7 +11067,7 @@
       <c r="Y233" s="1"/>
     </row>
     <row r="234" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A234" s="57"/>
+      <c r="A234" s="58"/>
       <c r="B234" s="50" t="b">
         <v>0</v>
       </c>
@@ -11104,7 +11104,7 @@
       <c r="Y234" s="1"/>
     </row>
     <row r="235" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A235" s="57"/>
+      <c r="A235" s="58"/>
       <c r="B235" s="50" t="b">
         <v>0</v>
       </c>
@@ -11141,7 +11141,7 @@
       <c r="Y235" s="1"/>
     </row>
     <row r="236" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A236" s="57"/>
+      <c r="A236" s="58"/>
       <c r="B236" s="50" t="b">
         <v>0</v>
       </c>
@@ -11180,7 +11180,7 @@
       <c r="Y236" s="1"/>
     </row>
     <row r="237" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A237" s="57"/>
+      <c r="A237" s="58"/>
       <c r="B237" s="50" t="b">
         <v>0</v>
       </c>
@@ -11217,7 +11217,7 @@
       <c r="Y237" s="1"/>
     </row>
     <row r="238" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A238" s="57"/>
+      <c r="A238" s="58"/>
       <c r="B238" s="50" t="b">
         <v>0</v>
       </c>
@@ -11254,7 +11254,7 @@
       <c r="Y238" s="1"/>
     </row>
     <row r="239" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A239" s="57"/>
+      <c r="A239" s="58"/>
       <c r="B239" s="50" t="b">
         <v>0</v>
       </c>
@@ -11291,7 +11291,7 @@
       <c r="Y239" s="1"/>
     </row>
     <row r="240" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A240" s="57"/>
+      <c r="A240" s="58"/>
       <c r="B240" s="50" t="b">
         <v>0</v>
       </c>
@@ -11330,7 +11330,7 @@
       <c r="Y240" s="1"/>
     </row>
     <row r="241" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A241" s="57"/>
+      <c r="A241" s="58"/>
       <c r="B241" s="50" t="b">
         <v>0</v>
       </c>
@@ -11367,9 +11367,9 @@
       <c r="Y241" s="1"/>
     </row>
     <row r="242" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A242" s="57"/>
+      <c r="A242" s="58"/>
       <c r="B242" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C242" s="2">
         <v>31</v>
@@ -11406,7 +11406,7 @@
       <c r="Y242" s="1"/>
     </row>
     <row r="243" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A243" s="57"/>
+      <c r="A243" s="58"/>
       <c r="B243" s="50" t="b">
         <v>0</v>
       </c>
@@ -11445,7 +11445,7 @@
       <c r="Y243" s="1"/>
     </row>
     <row r="244" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A244" s="57"/>
+      <c r="A244" s="58"/>
       <c r="B244" s="50" t="b">
         <v>0</v>
       </c>
@@ -11482,7 +11482,7 @@
       <c r="Y244" s="1"/>
     </row>
     <row r="245" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A245" s="57"/>
+      <c r="A245" s="58"/>
       <c r="B245" s="50" t="b">
         <v>0</v>
       </c>
@@ -11521,7 +11521,7 @@
       <c r="Y245" s="1"/>
     </row>
     <row r="246" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A246" s="57"/>
+      <c r="A246" s="58"/>
       <c r="B246" s="50" t="b">
         <v>0</v>
       </c>
@@ -11558,7 +11558,7 @@
       <c r="Y246" s="1"/>
     </row>
     <row r="247" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A247" s="57"/>
+      <c r="A247" s="58"/>
       <c r="B247" s="50" t="b">
         <v>0</v>
       </c>
@@ -11597,7 +11597,7 @@
       <c r="Y247" s="1"/>
     </row>
     <row r="248" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A248" s="57"/>
+      <c r="A248" s="58"/>
       <c r="B248" s="50" t="b">
         <v>0</v>
       </c>
@@ -11674,7 +11674,7 @@
     </row>
     <row r="250" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1"/>
-      <c r="B250" s="68"/>
+      <c r="B250" s="56"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="3"/>
@@ -11701,7 +11701,7 @@
     </row>
     <row r="251" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="1"/>
-      <c r="B251" s="68"/>
+      <c r="B251" s="56"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="3"/>
@@ -11727,7 +11727,7 @@
       <c r="Y251" s="1"/>
     </row>
     <row r="252" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A252" s="66" t="s">
+      <c r="A252" s="67" t="s">
         <v>303</v>
       </c>
       <c r="B252" s="50" t="b">
@@ -11768,7 +11768,7 @@
       <c r="Y252" s="1"/>
     </row>
     <row r="253" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A253" s="66"/>
+      <c r="A253" s="67"/>
       <c r="B253" s="50" t="b">
         <v>1</v>
       </c>
@@ -11805,7 +11805,7 @@
       <c r="Y253" s="1"/>
     </row>
     <row r="254" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A254" s="66"/>
+      <c r="A254" s="67"/>
       <c r="B254" s="50" t="b">
         <v>1</v>
       </c>
@@ -11842,7 +11842,7 @@
       <c r="Y254" s="1"/>
     </row>
     <row r="255" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A255" s="66"/>
+      <c r="A255" s="67"/>
       <c r="B255" s="50" t="b">
         <v>1</v>
       </c>
@@ -11879,7 +11879,7 @@
       <c r="Y255" s="1"/>
     </row>
     <row r="256" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A256" s="66"/>
+      <c r="A256" s="67"/>
       <c r="B256" s="50" t="b">
         <v>1</v>
       </c>
@@ -11916,7 +11916,7 @@
       <c r="Y256" s="1"/>
     </row>
     <row r="257" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A257" s="66"/>
+      <c r="A257" s="67"/>
       <c r="B257" s="50" t="b">
         <v>1</v>
       </c>
@@ -11953,7 +11953,7 @@
       <c r="Y257" s="1"/>
     </row>
     <row r="258" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A258" s="66"/>
+      <c r="A258" s="67"/>
       <c r="B258" s="50" t="b">
         <v>1</v>
       </c>
@@ -11990,7 +11990,7 @@
       <c r="Y258" s="1"/>
     </row>
     <row r="259" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A259" s="66"/>
+      <c r="A259" s="67"/>
       <c r="B259" s="50" t="b">
         <v>1</v>
       </c>
@@ -12027,7 +12027,7 @@
       <c r="Y259" s="1"/>
     </row>
     <row r="260" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A260" s="66"/>
+      <c r="A260" s="67"/>
       <c r="B260" s="50" t="b">
         <v>1</v>
       </c>
@@ -12064,7 +12064,7 @@
       <c r="Y260" s="1"/>
     </row>
     <row r="261" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A261" s="66"/>
+      <c r="A261" s="67"/>
       <c r="B261" s="50" t="b">
         <v>1</v>
       </c>
@@ -12101,7 +12101,7 @@
       <c r="Y261" s="1"/>
     </row>
     <row r="262" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A262" s="66"/>
+      <c r="A262" s="67"/>
       <c r="B262" s="50" t="b">
         <v>1</v>
       </c>
@@ -12138,7 +12138,7 @@
       <c r="Y262" s="1"/>
     </row>
     <row r="263" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A263" s="66"/>
+      <c r="A263" s="67"/>
       <c r="B263" s="50" t="b">
         <v>1</v>
       </c>
@@ -12175,7 +12175,7 @@
       <c r="Y263" s="1"/>
     </row>
     <row r="264" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A264" s="57"/>
+      <c r="A264" s="58"/>
       <c r="B264" s="50" t="b">
         <v>1</v>
       </c>
@@ -12214,7 +12214,7 @@
       <c r="Y264" s="1"/>
     </row>
     <row r="265" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A265" s="57"/>
+      <c r="A265" s="58"/>
       <c r="B265" s="50" t="b">
         <v>1</v>
       </c>
@@ -12253,7 +12253,7 @@
       <c r="Y265" s="1"/>
     </row>
     <row r="266" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A266" s="57"/>
+      <c r="A266" s="58"/>
       <c r="B266" s="50" t="b">
         <v>1</v>
       </c>
@@ -12292,7 +12292,7 @@
       <c r="Y266" s="1"/>
     </row>
     <row r="267" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A267" s="57"/>
+      <c r="A267" s="58"/>
       <c r="B267" s="50" t="b">
         <v>1</v>
       </c>
@@ -12329,7 +12329,7 @@
       <c r="Y267" s="1"/>
     </row>
     <row r="268" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A268" s="57"/>
+      <c r="A268" s="58"/>
       <c r="B268" s="50" t="b">
         <v>1</v>
       </c>
@@ -12368,7 +12368,7 @@
       <c r="Y268" s="1"/>
     </row>
     <row r="269" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A269" s="57"/>
+      <c r="A269" s="58"/>
       <c r="B269" s="50" t="b">
         <v>1</v>
       </c>
@@ -12407,7 +12407,7 @@
       <c r="Y269" s="1"/>
     </row>
     <row r="270" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A270" s="57"/>
+      <c r="A270" s="58"/>
       <c r="B270" s="50" t="b">
         <v>1</v>
       </c>
@@ -12444,7 +12444,7 @@
       <c r="Y270" s="1"/>
     </row>
     <row r="271" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A271" s="57"/>
+      <c r="A271" s="58"/>
       <c r="B271" s="50" t="b">
         <v>1</v>
       </c>
@@ -12483,7 +12483,7 @@
       <c r="Y271" s="1"/>
     </row>
     <row r="272" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A272" s="57"/>
+      <c r="A272" s="58"/>
       <c r="B272" s="50" t="b">
         <v>1</v>
       </c>
@@ -12522,7 +12522,7 @@
       <c r="Y272" s="1"/>
     </row>
     <row r="273" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A273" s="57"/>
+      <c r="A273" s="58"/>
       <c r="B273" s="50" t="b">
         <v>0</v>
       </c>
@@ -12561,7 +12561,7 @@
       <c r="Y273" s="1"/>
     </row>
     <row r="274" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A274" s="57"/>
+      <c r="A274" s="58"/>
       <c r="B274" s="50" t="b">
         <v>0</v>
       </c>
@@ -12600,7 +12600,7 @@
       <c r="Y274" s="1"/>
     </row>
     <row r="275" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A275" s="57"/>
+      <c r="A275" s="58"/>
       <c r="B275" s="50" t="b">
         <v>1</v>
       </c>
@@ -12639,7 +12639,7 @@
       <c r="Y275" s="1"/>
     </row>
     <row r="276" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A276" s="57"/>
+      <c r="A276" s="58"/>
       <c r="B276" s="50" t="b">
         <v>0</v>
       </c>
@@ -12678,7 +12678,7 @@
       <c r="Y276" s="1"/>
     </row>
     <row r="277" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A277" s="57"/>
+      <c r="A277" s="58"/>
       <c r="B277" s="50" t="b">
         <v>1</v>
       </c>
@@ -12717,7 +12717,7 @@
       <c r="Y277" s="1"/>
     </row>
     <row r="278" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A278" s="57"/>
+      <c r="A278" s="58"/>
       <c r="B278" s="50" t="b">
         <v>1</v>
       </c>
@@ -12756,7 +12756,7 @@
       <c r="Y278" s="1"/>
     </row>
     <row r="279" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A279" s="57"/>
+      <c r="A279" s="58"/>
       <c r="B279" s="50" t="b">
         <v>0</v>
       </c>
@@ -12795,7 +12795,7 @@
       <c r="Y279" s="1"/>
     </row>
     <row r="280" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A280" s="57"/>
+      <c r="A280" s="58"/>
       <c r="B280" s="50" t="b">
         <v>1</v>
       </c>
@@ -12832,7 +12832,7 @@
       <c r="Y280" s="1"/>
     </row>
     <row r="281" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A281" s="57"/>
+      <c r="A281" s="58"/>
       <c r="B281" s="50" t="b">
         <v>1</v>
       </c>
@@ -12869,7 +12869,7 @@
       <c r="Y281" s="1"/>
     </row>
     <row r="282" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A282" s="57"/>
+      <c r="A282" s="58"/>
       <c r="B282" s="50" t="b">
         <v>1</v>
       </c>
@@ -12906,7 +12906,7 @@
       <c r="Y282" s="1"/>
     </row>
     <row r="283" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A283" s="57"/>
+      <c r="A283" s="58"/>
       <c r="B283" s="50" t="b">
         <v>1</v>
       </c>
@@ -12943,7 +12943,7 @@
       <c r="Y283" s="1"/>
     </row>
     <row r="284" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A284" s="57"/>
+      <c r="A284" s="58"/>
       <c r="B284" s="50" t="b">
         <v>1</v>
       </c>
@@ -12980,7 +12980,7 @@
       <c r="Y284" s="1"/>
     </row>
     <row r="285" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A285" s="57"/>
+      <c r="A285" s="58"/>
       <c r="B285" s="50" t="b">
         <v>1</v>
       </c>
@@ -13013,7 +13013,7 @@
       <c r="Y285" s="1"/>
     </row>
     <row r="286" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A286" s="57"/>
+      <c r="A286" s="58"/>
       <c r="B286" s="50" t="b">
         <v>0</v>
       </c>
@@ -13052,7 +13052,7 @@
       <c r="Y286" s="1"/>
     </row>
     <row r="287" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A287" s="57"/>
+      <c r="A287" s="58"/>
       <c r="B287" s="50" t="b">
         <v>0</v>
       </c>
@@ -13091,7 +13091,7 @@
       <c r="Y287" s="1"/>
     </row>
     <row r="288" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A288" s="57"/>
+      <c r="A288" s="58"/>
       <c r="B288" s="50" t="b">
         <v>0</v>
       </c>
@@ -13130,7 +13130,7 @@
       <c r="Y288" s="1"/>
     </row>
     <row r="289" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A289" s="57"/>
+      <c r="A289" s="58"/>
       <c r="B289" s="50" t="b">
         <v>0</v>
       </c>
@@ -13169,7 +13169,7 @@
       <c r="Y289" s="1"/>
     </row>
     <row r="290" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A290" s="57"/>
+      <c r="A290" s="58"/>
       <c r="B290" s="50" t="b">
         <v>0</v>
       </c>
@@ -13208,7 +13208,7 @@
       <c r="Y290" s="1"/>
     </row>
     <row r="291" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A291" s="57"/>
+      <c r="A291" s="58"/>
       <c r="B291" s="50" t="b">
         <v>0</v>
       </c>
@@ -13301,7 +13301,7 @@
       <c r="Y293" s="1"/>
     </row>
     <row r="294" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A294" s="66" t="s">
+      <c r="A294" s="67" t="s">
         <v>346</v>
       </c>
       <c r="B294" s="50" t="b">
@@ -13342,7 +13342,7 @@
       <c r="Y294" s="1"/>
     </row>
     <row r="295" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A295" s="57"/>
+      <c r="A295" s="58"/>
       <c r="B295" s="50" t="b">
         <v>0</v>
       </c>
@@ -13381,7 +13381,7 @@
       <c r="Y295" s="1"/>
     </row>
     <row r="296" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A296" s="57"/>
+      <c r="A296" s="58"/>
       <c r="B296" s="50" t="b">
         <v>0</v>
       </c>
@@ -13420,7 +13420,7 @@
       <c r="Y296" s="1"/>
     </row>
     <row r="297" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A297" s="57"/>
+      <c r="A297" s="58"/>
       <c r="B297" s="50" t="b">
         <v>0</v>
       </c>
@@ -13459,7 +13459,7 @@
       <c r="Y297" s="1"/>
     </row>
     <row r="298" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A298" s="57"/>
+      <c r="A298" s="58"/>
       <c r="B298" s="50" t="b">
         <v>0</v>
       </c>
@@ -13498,7 +13498,7 @@
       <c r="Y298" s="1"/>
     </row>
     <row r="299" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A299" s="57"/>
+      <c r="A299" s="58"/>
       <c r="B299" s="50" t="b">
         <v>0</v>
       </c>
@@ -13595,7 +13595,7 @@
       <c r="Y301" s="1"/>
     </row>
     <row r="302" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A302" s="63" t="s">
+      <c r="A302" s="64" t="s">
         <v>392</v>
       </c>
       <c r="B302" s="50" t="b">
@@ -13634,7 +13634,7 @@
       <c r="Y302" s="1"/>
     </row>
     <row r="303" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A303" s="57"/>
+      <c r="A303" s="58"/>
       <c r="B303" s="50" t="b">
         <v>0</v>
       </c>
@@ -13671,7 +13671,7 @@
       <c r="Y303" s="1"/>
     </row>
     <row r="304" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A304" s="57"/>
+      <c r="A304" s="58"/>
       <c r="B304" s="50" t="b">
         <v>0</v>
       </c>
@@ -13708,7 +13708,7 @@
       <c r="Y304" s="1"/>
     </row>
     <row r="305" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A305" s="57"/>
+      <c r="A305" s="58"/>
       <c r="B305" s="50" t="b">
         <v>0</v>
       </c>
@@ -13745,7 +13745,7 @@
       <c r="Y305" s="1"/>
     </row>
     <row r="306" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A306" s="57"/>
+      <c r="A306" s="58"/>
       <c r="B306" s="50" t="b">
         <v>1</v>
       </c>
@@ -13782,7 +13782,7 @@
       <c r="Y306" s="1"/>
     </row>
     <row r="307" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A307" s="57"/>
+      <c r="A307" s="58"/>
       <c r="B307" s="50" t="b">
         <v>0</v>
       </c>
@@ -13817,7 +13817,7 @@
       <c r="Y307" s="1"/>
     </row>
     <row r="308" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A308" s="57"/>
+      <c r="A308" s="58"/>
       <c r="B308" s="50" t="b">
         <v>0</v>
       </c>
@@ -13848,7 +13848,7 @@
       <c r="Y308" s="1"/>
     </row>
     <row r="309" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A309" s="57"/>
+      <c r="A309" s="58"/>
       <c r="B309" s="50" t="b">
         <v>0</v>
       </c>
@@ -13879,7 +13879,7 @@
       <c r="Y309" s="1"/>
     </row>
     <row r="310" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A310" s="57"/>
+      <c r="A310" s="58"/>
       <c r="B310" s="50" t="b">
         <v>0</v>
       </c>
@@ -13910,7 +13910,7 @@
       <c r="Y310" s="1"/>
     </row>
     <row r="311" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A311" s="57"/>
+      <c r="A311" s="58"/>
       <c r="B311" s="50" t="b">
         <v>0</v>
       </c>
@@ -13941,7 +13941,7 @@
       <c r="Y311" s="1"/>
     </row>
     <row r="312" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A312" s="57"/>
+      <c r="A312" s="58"/>
       <c r="B312" s="50" t="b">
         <v>0</v>
       </c>
@@ -13972,7 +13972,7 @@
       <c r="Y312" s="1"/>
     </row>
     <row r="313" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A313" s="57"/>
+      <c r="A313" s="58"/>
       <c r="B313" s="50" t="b">
         <v>0</v>
       </c>
@@ -14003,7 +14003,7 @@
       <c r="Y313" s="1"/>
     </row>
     <row r="314" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A314" s="57"/>
+      <c r="A314" s="58"/>
       <c r="B314" s="50" t="b">
         <v>0</v>
       </c>
@@ -14034,7 +14034,7 @@
       <c r="Y314" s="1"/>
     </row>
     <row r="315" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A315" s="57"/>
+      <c r="A315" s="58"/>
       <c r="B315" s="50" t="b">
         <v>0</v>
       </c>
@@ -14065,7 +14065,7 @@
       <c r="Y315" s="1"/>
     </row>
     <row r="316" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A316" s="57"/>
+      <c r="A316" s="58"/>
       <c r="B316" s="50" t="b">
         <v>0</v>
       </c>
@@ -14096,7 +14096,7 @@
       <c r="Y316" s="1"/>
     </row>
     <row r="317" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A317" s="57"/>
+      <c r="A317" s="58"/>
       <c r="B317" s="1"/>
       <c r="C317" s="2"/>
       <c r="D317" s="1"/>
@@ -14123,7 +14123,7 @@
       <c r="Y317" s="1"/>
     </row>
     <row r="318" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A318" s="57"/>
+      <c r="A318" s="58"/>
       <c r="B318" s="1"/>
       <c r="C318" s="2"/>
       <c r="D318" s="1"/>
@@ -14150,7 +14150,7 @@
       <c r="Y318" s="1"/>
     </row>
     <row r="319" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A319" s="57"/>
+      <c r="A319" s="58"/>
       <c r="B319" s="1"/>
       <c r="C319" s="2"/>
       <c r="D319" s="1"/>
@@ -14177,7 +14177,7 @@
       <c r="Y319" s="1"/>
     </row>
     <row r="320" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A320" s="57"/>
+      <c r="A320" s="58"/>
       <c r="B320" s="1"/>
       <c r="C320" s="2"/>
       <c r="D320" s="1"/>
@@ -14204,7 +14204,7 @@
       <c r="Y320" s="1"/>
     </row>
     <row r="321" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A321" s="57"/>
+      <c r="A321" s="58"/>
       <c r="B321" s="1"/>
       <c r="C321" s="2"/>
       <c r="D321" s="1"/>

--- a/Strivers List + other Problems.xlsx
+++ b/Strivers List + other Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3220E384-019B-45EE-959A-25F9F337E0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF03261-8F2E-4493-BC16-2141E561C431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="510">
   <si>
     <t>Mark as Done</t>
   </si>
@@ -860,9 +860,6 @@
     <t xml:space="preserve">Sharechat  + Directi , Amazon , microsoft </t>
   </si>
   <si>
-    <t>01 Matrix</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/01-matrix/description/</t>
   </si>
   <si>
@@ -1557,6 +1554,15 @@
   </si>
   <si>
     <t>Distinct Subsequences</t>
+  </si>
+  <si>
+    <t>Distance of nearest cell having 1</t>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/problems/distance-of-nearest-cell-having-1-1587115620/1</t>
+  </si>
+  <si>
+    <t>01 Matrix (Distance to nearest cell having 0)</t>
   </si>
 </sst>
 </file>
@@ -2248,7 +2254,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y1079"/>
+  <dimension ref="A1:Y1080"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -2508,7 +2514,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>9</v>
@@ -2545,7 +2551,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>9</v>
@@ -2621,7 +2627,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>9</v>
@@ -2656,7 +2662,7 @@
       </c>
       <c r="C12" s="30"/>
       <c r="D12" s="29" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>9</v>
@@ -2732,7 +2738,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>9</v>
@@ -2769,7 +2775,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>9</v>
@@ -2806,7 +2812,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>9</v>
@@ -2884,7 +2890,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E18" s="21" t="s">
         <v>9</v>
@@ -2921,7 +2927,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E19" s="21" t="s">
         <v>9</v>
@@ -2958,7 +2964,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E20" s="21" t="s">
         <v>9</v>
@@ -2995,7 +3001,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E21" s="31" t="s">
         <v>9</v>
@@ -3071,7 +3077,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E23" s="21" t="s">
         <v>9</v>
@@ -3192,7 +3198,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E26" s="34" t="s">
         <v>9</v>
@@ -3235,7 +3241,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E27" s="21" t="s">
         <v>9</v>
@@ -3313,7 +3319,7 @@
         <v>23</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E29" s="25" t="s">
         <v>9</v>
@@ -3434,7 +3440,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E32" s="21" t="s">
         <v>9</v>
@@ -3512,7 +3518,7 @@
         <v>28</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E34" s="21" t="s">
         <v>9</v>
@@ -3713,7 +3719,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>9</v>
@@ -3750,7 +3756,7 @@
         <v>34</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E40" s="21" t="s">
         <v>9</v>
@@ -3787,7 +3793,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E41" s="34" t="s">
         <v>9</v>
@@ -3869,7 +3875,7 @@
         <v>37</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E43" s="31" t="s">
         <v>9</v>
@@ -4029,7 +4035,7 @@
         <v>41</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E47" s="21" t="s">
         <v>9</v>
@@ -4105,7 +4111,7 @@
         <v>43</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E49" s="21" t="s">
         <v>9</v>
@@ -4266,7 +4272,7 @@
         <v>2</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E54" s="21" t="s">
         <v>9</v>
@@ -4303,7 +4309,7 @@
         <v>3</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E55" s="21" t="s">
         <v>9</v>
@@ -4340,7 +4346,7 @@
         <v>4</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E56" s="21" t="s">
         <v>9</v>
@@ -4377,7 +4383,7 @@
         <v>5</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E57" s="21" t="s">
         <v>9</v>
@@ -4414,7 +4420,7 @@
         <v>6</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E58" s="21" t="s">
         <v>9</v>
@@ -4490,7 +4496,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>9</v>
@@ -4527,7 +4533,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E61" s="21" t="s">
         <v>9</v>
@@ -4564,7 +4570,7 @@
         <v>10</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E62" s="21" t="s">
         <v>9</v>
@@ -4601,7 +4607,7 @@
         <v>11</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>9</v>
@@ -4638,7 +4644,7 @@
         <v>12</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>9</v>
@@ -4675,7 +4681,7 @@
         <v>13</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E65" s="21" t="s">
         <v>9</v>
@@ -4712,7 +4718,7 @@
         <v>14</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E66" s="21" t="s">
         <v>9</v>
@@ -4749,7 +4755,7 @@
         <v>15</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E67" s="21" t="s">
         <v>9</v>
@@ -5054,7 +5060,7 @@
         <v>3</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E76" s="21" t="s">
         <v>9</v>
@@ -5091,7 +5097,7 @@
         <v>4</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E77" s="31" t="s">
         <v>9</v>
@@ -5206,7 +5212,7 @@
         <v>7</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E80" s="21" t="s">
         <v>9</v>
@@ -5243,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E81" s="21" t="s">
         <v>9</v>
@@ -5280,7 +5286,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E82" s="21" t="s">
         <v>9</v>
@@ -5436,7 +5442,7 @@
         <v>13</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E86" s="21" t="s">
         <v>9</v>
@@ -5551,7 +5557,7 @@
         <v>16</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E89" s="31" t="s">
         <v>9</v>
@@ -6010,7 +6016,7 @@
         <v>7</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>9</v>
@@ -6048,7 +6054,7 @@
         <v>8</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E103" s="21" t="s">
         <v>9</v>
@@ -6210,7 +6216,7 @@
         <v>13</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E107" s="21" t="s">
         <v>9</v>
@@ -6248,7 +6254,7 @@
         <v>14</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E108" s="21" t="s">
         <v>9</v>
@@ -6383,7 +6389,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E112" s="41" t="s">
         <v>9</v>
@@ -6422,7 +6428,7 @@
       </c>
       <c r="C113" s="30"/>
       <c r="D113" s="29" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E113" s="21" t="s">
         <v>9</v>
@@ -6457,7 +6463,7 @@
         <v>2</v>
       </c>
       <c r="D114" s="29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E114" s="41" t="s">
         <v>9</v>
@@ -6498,7 +6504,7 @@
         <v>3</v>
       </c>
       <c r="D115" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E115" s="41" t="s">
         <v>9</v>
@@ -6539,7 +6545,7 @@
         <v>4</v>
       </c>
       <c r="D116" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E116" s="41" t="s">
         <v>9</v>
@@ -6578,7 +6584,7 @@
         <v>5</v>
       </c>
       <c r="D117" s="29" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E117" s="41" t="s">
         <v>9</v>
@@ -6619,7 +6625,7 @@
         <v>6</v>
       </c>
       <c r="D118" s="29" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E118" s="41" t="s">
         <v>9</v>
@@ -6660,7 +6666,7 @@
         <v>7</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E119" s="41" t="s">
         <v>9</v>
@@ -6742,7 +6748,7 @@
         <v>9</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E121" s="31" t="s">
         <v>9</v>
@@ -6857,7 +6863,7 @@
         <v>12</v>
       </c>
       <c r="D124" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E124" s="31" t="s">
         <v>9</v>
@@ -6894,7 +6900,7 @@
         <v>13</v>
       </c>
       <c r="D125" s="29" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E125" s="31" t="s">
         <v>9</v>
@@ -6931,7 +6937,7 @@
         <v>14</v>
       </c>
       <c r="D126" s="29" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E126" s="31" t="s">
         <v>9</v>
@@ -7007,7 +7013,7 @@
         <v>16</v>
       </c>
       <c r="D128" s="29" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E128" s="21" t="s">
         <v>9</v>
@@ -7085,7 +7091,7 @@
         <v>18</v>
       </c>
       <c r="D130" s="29" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E130" s="31" t="s">
         <v>9</v>
@@ -7434,7 +7440,7 @@
         <v>8</v>
       </c>
       <c r="D139" s="29" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E139" s="21" t="s">
         <v>9</v>
@@ -7512,7 +7518,7 @@
         <v>10</v>
       </c>
       <c r="D141" s="29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E141" s="21" t="s">
         <v>9</v>
@@ -7549,7 +7555,7 @@
         <v>11</v>
       </c>
       <c r="D142" s="29" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E142" s="21" t="s">
         <v>9</v>
@@ -7586,7 +7592,7 @@
         <v>12</v>
       </c>
       <c r="D143" s="29" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E143" s="21" t="s">
         <v>9</v>
@@ -7884,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E151" s="41" t="s">
         <v>9</v>
@@ -7925,7 +7931,7 @@
         <v>2</v>
       </c>
       <c r="D152" s="29" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E152" s="41" t="s">
         <v>9</v>
@@ -7966,7 +7972,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="29" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E153" s="41" t="s">
         <v>9</v>
@@ -8005,7 +8011,7 @@
       </c>
       <c r="C154" s="30"/>
       <c r="D154" s="29" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E154" s="21" t="s">
         <v>9</v>
@@ -8042,7 +8048,7 @@
         <v>4</v>
       </c>
       <c r="D155" s="29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E155" s="41" t="s">
         <v>9</v>
@@ -8081,7 +8087,7 @@
         <v>5</v>
       </c>
       <c r="D156" s="29" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E156" s="41" t="s">
         <v>9</v>
@@ -8122,7 +8128,7 @@
         <v>6</v>
       </c>
       <c r="D157" s="29" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E157" s="41" t="s">
         <v>9</v>
@@ -8163,7 +8169,7 @@
         <v>7</v>
       </c>
       <c r="D158" s="29" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E158" s="41" t="s">
         <v>9</v>
@@ -8204,7 +8210,7 @@
         <v>8</v>
       </c>
       <c r="D159" s="29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E159" s="41" t="s">
         <v>9</v>
@@ -8245,7 +8251,7 @@
         <v>9</v>
       </c>
       <c r="D160" s="29" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E160" s="41" t="s">
         <v>9</v>
@@ -8284,7 +8290,7 @@
         <v>10</v>
       </c>
       <c r="D161" s="29" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E161" s="41" t="s">
         <v>9</v>
@@ -8325,7 +8331,7 @@
         <v>11</v>
       </c>
       <c r="D162" s="29" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E162" s="41" t="s">
         <v>9</v>
@@ -8364,7 +8370,7 @@
         <v>12</v>
       </c>
       <c r="D163" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E163" s="41" t="s">
         <v>9</v>
@@ -8405,7 +8411,7 @@
         <v>13</v>
       </c>
       <c r="D164" s="29" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E164" s="41" t="s">
         <v>9</v>
@@ -8444,7 +8450,7 @@
         <v>14</v>
       </c>
       <c r="D165" s="29" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E165" s="21" t="s">
         <v>9</v>
@@ -8481,7 +8487,7 @@
         <v>15</v>
       </c>
       <c r="D166" s="29" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E166" s="21" t="s">
         <v>9</v>
@@ -8518,7 +8524,7 @@
         <v>16</v>
       </c>
       <c r="D167" s="29" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E167" s="41" t="s">
         <v>9</v>
@@ -8557,7 +8563,7 @@
         <v>17</v>
       </c>
       <c r="D168" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E168" s="41" t="s">
         <v>9</v>
@@ -8598,7 +8604,7 @@
         <v>18</v>
       </c>
       <c r="D169" s="29" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E169" s="21" t="s">
         <v>9</v>
@@ -8676,7 +8682,7 @@
         <v>20</v>
       </c>
       <c r="D171" s="29" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E171" s="41" t="s">
         <v>9</v>
@@ -8797,7 +8803,7 @@
         <v>23</v>
       </c>
       <c r="D174" s="29" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E174" s="41" t="s">
         <v>9</v>
@@ -8918,7 +8924,7 @@
         <v>26</v>
       </c>
       <c r="D177" s="29" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E177" s="41" t="s">
         <v>9</v>
@@ -8996,7 +9002,7 @@
         <v>28</v>
       </c>
       <c r="D179" s="29" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E179" s="31" t="s">
         <v>9</v>
@@ -9033,7 +9039,7 @@
         <v>29</v>
       </c>
       <c r="D180" s="29" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E180" s="31" t="s">
         <v>9</v>
@@ -10268,10 +10274,10 @@
         <v>2</v>
       </c>
       <c r="D213" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E213" s="23" t="s">
         <v>414</v>
-      </c>
-      <c r="E213" s="23" t="s">
-        <v>415</v>
       </c>
       <c r="F213" s="27" t="s">
         <v>10</v>
@@ -10542,7 +10548,7 @@
         <v>262</v>
       </c>
       <c r="E220" s="51" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F220" s="26" t="s">
         <v>22</v>
@@ -10650,16 +10656,14 @@
     <row r="223" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A223" s="58"/>
       <c r="B223" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C223" s="2">
-        <v>12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C223" s="2"/>
       <c r="D223" s="1" t="s">
-        <v>460</v>
+        <v>507</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>461</v>
+        <v>508</v>
       </c>
       <c r="F223" s="26" t="s">
         <v>22</v>
@@ -10687,16 +10691,16 @@
     <row r="224" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A224" s="58"/>
       <c r="B224" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C224" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="F224" s="26" t="s">
         <v>22</v>
@@ -10724,16 +10728,16 @@
     <row r="225" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A225" s="58"/>
       <c r="B225" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C225" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F225" s="26" t="s">
         <v>22</v>
@@ -10761,24 +10765,22 @@
     <row r="226" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A226" s="58"/>
       <c r="B226" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E226" s="18" t="s">
-        <v>271</v>
+        <v>437</v>
+      </c>
+      <c r="E226" s="23" t="s">
+        <v>438</v>
       </c>
       <c r="F226" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G226" s="3"/>
-      <c r="H226" s="15" t="s">
-        <v>272</v>
-      </c>
+      <c r="H226" s="15"/>
       <c r="I226" s="3"/>
       <c r="J226" s="1"/>
       <c r="K226" s="1"/>
@@ -10803,20 +10805,20 @@
         <v>1</v>
       </c>
       <c r="C227" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="E227" s="18" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F227" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G227" s="3"/>
       <c r="H227" s="15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I227" s="3"/>
       <c r="J227" s="1"/>
@@ -10839,22 +10841,24 @@
     <row r="228" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A228" s="58"/>
       <c r="B228" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C228" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E228" s="23" t="s">
-        <v>441</v>
+        <v>144</v>
+      </c>
+      <c r="E228" s="18" t="s">
+        <v>273</v>
       </c>
       <c r="F228" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G228" s="3"/>
-      <c r="H228" s="15"/>
+      <c r="H228" s="15" t="s">
+        <v>274</v>
+      </c>
       <c r="I228" s="3"/>
       <c r="J228" s="1"/>
       <c r="K228" s="1"/>
@@ -10879,21 +10883,19 @@
         <v>0</v>
       </c>
       <c r="C229" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E229" s="18" t="s">
-        <v>276</v>
+        <v>439</v>
+      </c>
+      <c r="E229" s="23" t="s">
+        <v>440</v>
       </c>
       <c r="F229" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G229" s="3"/>
-      <c r="H229" s="15" t="s">
-        <v>277</v>
-      </c>
+      <c r="H229" s="15"/>
       <c r="I229" s="3"/>
       <c r="J229" s="1"/>
       <c r="K229" s="1"/>
@@ -10915,23 +10917,23 @@
     <row r="230" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A230" s="58"/>
       <c r="B230" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C230" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E230" s="23" t="s">
-        <v>253</v>
+        <v>509</v>
+      </c>
+      <c r="E230" s="18" t="s">
+        <v>275</v>
       </c>
       <c r="F230" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G230" s="3"/>
       <c r="H230" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I230" s="3"/>
       <c r="J230" s="1"/>
@@ -10951,26 +10953,26 @@
       <c r="X230" s="1"/>
       <c r="Y230" s="1"/>
     </row>
-    <row r="231" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A231" s="58"/>
       <c r="B231" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C231" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E231" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="F231" s="28" t="s">
-        <v>53</v>
+        <v>454</v>
+      </c>
+      <c r="E231" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="F231" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="G231" s="3"/>
-      <c r="H231" s="16" t="s">
-        <v>281</v>
+      <c r="H231" s="15" t="s">
+        <v>277</v>
       </c>
       <c r="I231" s="3"/>
       <c r="J231" s="1"/>
@@ -10990,26 +10992,26 @@
       <c r="X231" s="1"/>
       <c r="Y231" s="1"/>
     </row>
-    <row r="232" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="58"/>
       <c r="B232" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C232" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E232" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="F232" s="26" t="s">
-        <v>22</v>
+        <v>279</v>
+      </c>
+      <c r="F232" s="28" t="s">
+        <v>53</v>
       </c>
       <c r="G232" s="3"/>
-      <c r="H232" s="15" t="s">
-        <v>284</v>
+      <c r="H232" s="16" t="s">
+        <v>280</v>
       </c>
       <c r="I232" s="3"/>
       <c r="J232" s="1"/>
@@ -11035,19 +11037,21 @@
         <v>0</v>
       </c>
       <c r="C233" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E233" s="23" t="s">
-        <v>412</v>
+        <v>281</v>
+      </c>
+      <c r="E233" s="18" t="s">
+        <v>282</v>
       </c>
       <c r="F233" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G233" s="3"/>
-      <c r="H233" s="15"/>
+      <c r="H233" s="15" t="s">
+        <v>283</v>
+      </c>
       <c r="I233" s="3"/>
       <c r="J233" s="1"/>
       <c r="K233" s="1"/>
@@ -11072,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="C234" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>451</v>
+        <v>412</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>452</v>
+        <v>411</v>
       </c>
       <c r="F234" s="26" t="s">
         <v>22</v>
@@ -11109,13 +11113,13 @@
         <v>0</v>
       </c>
       <c r="C235" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="F235" s="26" t="s">
         <v>22</v>
@@ -11146,21 +11150,19 @@
         <v>0</v>
       </c>
       <c r="C236" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E236" s="18" t="s">
-        <v>246</v>
+        <v>435</v>
+      </c>
+      <c r="E236" s="23" t="s">
+        <v>434</v>
       </c>
       <c r="F236" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G236" s="3"/>
-      <c r="H236" s="15" t="s">
-        <v>286</v>
-      </c>
+      <c r="H236" s="15"/>
       <c r="I236" s="3"/>
       <c r="J236" s="1"/>
       <c r="K236" s="1"/>
@@ -11185,19 +11187,21 @@
         <v>0</v>
       </c>
       <c r="C237" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E237" s="23" t="s">
-        <v>432</v>
+        <v>284</v>
+      </c>
+      <c r="E237" s="18" t="s">
+        <v>246</v>
       </c>
       <c r="F237" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G237" s="3"/>
-      <c r="H237" s="15"/>
+      <c r="H237" s="15" t="s">
+        <v>285</v>
+      </c>
       <c r="I237" s="3"/>
       <c r="J237" s="1"/>
       <c r="K237" s="1"/>
@@ -11222,10 +11226,10 @@
         <v>0</v>
       </c>
       <c r="C238" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E238" s="23" t="s">
         <v>431</v>
@@ -11259,16 +11263,16 @@
         <v>0</v>
       </c>
       <c r="C239" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="E239" s="23" t="s">
-        <v>417</v>
-      </c>
-      <c r="F239" s="52" t="s">
-        <v>53</v>
+        <v>430</v>
+      </c>
+      <c r="F239" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="G239" s="3"/>
       <c r="H239" s="15"/>
@@ -11296,21 +11300,19 @@
         <v>0</v>
       </c>
       <c r="C240" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E240" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="F240" s="26" t="s">
-        <v>22</v>
+        <v>415</v>
+      </c>
+      <c r="E240" s="23" t="s">
+        <v>416</v>
+      </c>
+      <c r="F240" s="52" t="s">
+        <v>53</v>
       </c>
       <c r="G240" s="3"/>
-      <c r="H240" s="15" t="s">
-        <v>289</v>
-      </c>
+      <c r="H240" s="15"/>
       <c r="I240" s="3"/>
       <c r="J240" s="1"/>
       <c r="K240" s="1"/>
@@ -11335,19 +11337,21 @@
         <v>0</v>
       </c>
       <c r="C241" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="E241" s="23" t="s">
-        <v>410</v>
+        <v>286</v>
+      </c>
+      <c r="E241" s="18" t="s">
+        <v>287</v>
       </c>
       <c r="F241" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G241" s="3"/>
-      <c r="H241" s="15"/>
+      <c r="H241" s="15" t="s">
+        <v>288</v>
+      </c>
       <c r="I241" s="3"/>
       <c r="J241" s="1"/>
       <c r="K241" s="1"/>
@@ -11369,24 +11373,22 @@
     <row r="242" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A242" s="58"/>
       <c r="B242" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C242" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E242" s="18" t="s">
-        <v>291</v>
+        <v>408</v>
+      </c>
+      <c r="E242" s="23" t="s">
+        <v>409</v>
       </c>
       <c r="F242" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G242" s="3"/>
-      <c r="H242" s="15" t="s">
-        <v>292</v>
-      </c>
+      <c r="H242" s="15"/>
       <c r="I242" s="3"/>
       <c r="J242" s="1"/>
       <c r="K242" s="1"/>
@@ -11405,26 +11407,26 @@
       <c r="X242" s="1"/>
       <c r="Y242" s="1"/>
     </row>
-    <row r="243" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A243" s="58"/>
       <c r="B243" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C243" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E243" s="18" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F243" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G243" s="3"/>
-      <c r="H243" s="16" t="s">
-        <v>295</v>
+      <c r="H243" s="15" t="s">
+        <v>291</v>
       </c>
       <c r="I243" s="3"/>
       <c r="J243" s="1"/>
@@ -11450,19 +11452,21 @@
         <v>0</v>
       </c>
       <c r="C244" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="E244" s="23" t="s">
-        <v>453</v>
-      </c>
-      <c r="F244" s="52" t="s">
-        <v>53</v>
+        <v>292</v>
+      </c>
+      <c r="E244" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="F244" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="G244" s="3"/>
-      <c r="H244" s="16"/>
+      <c r="H244" s="16" t="s">
+        <v>294</v>
+      </c>
       <c r="I244" s="3"/>
       <c r="J244" s="1"/>
       <c r="K244" s="1"/>
@@ -11487,21 +11491,19 @@
         <v>0</v>
       </c>
       <c r="C245" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="E245" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="F245" s="28" t="s">
+        <v>453</v>
+      </c>
+      <c r="E245" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="F245" s="52" t="s">
         <v>53</v>
       </c>
       <c r="G245" s="3"/>
-      <c r="H245" s="16" t="s">
-        <v>297</v>
-      </c>
+      <c r="H245" s="16"/>
       <c r="I245" s="3"/>
       <c r="J245" s="1"/>
       <c r="K245" s="1"/>
@@ -11526,19 +11528,21 @@
         <v>0</v>
       </c>
       <c r="C246" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E246" s="23" t="s">
-        <v>447</v>
+        <v>410</v>
+      </c>
+      <c r="E246" s="18" t="s">
+        <v>295</v>
       </c>
       <c r="F246" s="28" t="s">
         <v>53</v>
       </c>
       <c r="G246" s="3"/>
-      <c r="H246" s="16"/>
+      <c r="H246" s="16" t="s">
+        <v>296</v>
+      </c>
       <c r="I246" s="3"/>
       <c r="J246" s="1"/>
       <c r="K246" s="1"/>
@@ -11563,21 +11567,19 @@
         <v>0</v>
       </c>
       <c r="C247" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E247" s="18" t="s">
-        <v>299</v>
+        <v>447</v>
+      </c>
+      <c r="E247" s="23" t="s">
+        <v>446</v>
       </c>
       <c r="F247" s="28" t="s">
         <v>53</v>
       </c>
       <c r="G247" s="3"/>
-      <c r="H247" s="16" t="s">
-        <v>300</v>
-      </c>
+      <c r="H247" s="16"/>
       <c r="I247" s="3"/>
       <c r="J247" s="1"/>
       <c r="K247" s="1"/>
@@ -11596,26 +11598,26 @@
       <c r="X247" s="1"/>
       <c r="Y247" s="1"/>
     </row>
-    <row r="248" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="58"/>
       <c r="B248" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C248" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E248" s="18" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="F248" s="28" t="s">
         <v>53</v>
       </c>
       <c r="G248" s="3"/>
-      <c r="H248" s="15" t="s">
-        <v>302</v>
+      <c r="H248" s="16" t="s">
+        <v>299</v>
       </c>
       <c r="I248" s="3"/>
       <c r="J248" s="1"/>
@@ -11635,25 +11637,27 @@
       <c r="X248" s="1"/>
       <c r="Y248" s="1"/>
     </row>
-    <row r="249" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A249" s="1"/>
+    <row r="249" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+      <c r="A249" s="58"/>
       <c r="B249" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C249" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="E249" s="23" t="s">
-        <v>362</v>
-      </c>
-      <c r="F249" s="47" t="s">
-        <v>10</v>
+        <v>300</v>
+      </c>
+      <c r="E249" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="F249" s="28" t="s">
+        <v>53</v>
       </c>
       <c r="G249" s="3"/>
-      <c r="H249" s="4"/>
+      <c r="H249" s="15" t="s">
+        <v>301</v>
+      </c>
       <c r="I249" s="3"/>
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
@@ -11674,11 +11678,21 @@
     </row>
     <row r="250" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1"/>
-      <c r="B250" s="56"/>
-      <c r="C250" s="1"/>
-      <c r="D250" s="1"/>
-      <c r="E250" s="3"/>
-      <c r="F250" s="1"/>
+      <c r="B250" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="C250" s="2">
+        <v>38</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E250" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="F250" s="47" t="s">
+        <v>10</v>
+      </c>
       <c r="G250" s="3"/>
       <c r="H250" s="4"/>
       <c r="I250" s="3"/>
@@ -11726,29 +11740,15 @@
       <c r="X251" s="1"/>
       <c r="Y251" s="1"/>
     </row>
-    <row r="252" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A252" s="67" t="s">
-        <v>303</v>
-      </c>
-      <c r="B252" s="50" t="b">
-        <v>1</v>
-      </c>
-      <c r="C252" s="2">
-        <v>1</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E252" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F252" s="27" t="s">
-        <v>10</v>
-      </c>
+    <row r="252" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A252" s="1"/>
+      <c r="B252" s="56"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
+      <c r="E252" s="3"/>
+      <c r="F252" s="1"/>
       <c r="G252" s="3"/>
-      <c r="H252" s="15" t="s">
-        <v>305</v>
-      </c>
+      <c r="H252" s="4"/>
       <c r="I252" s="3"/>
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
@@ -11768,24 +11768,28 @@
       <c r="Y252" s="1"/>
     </row>
     <row r="253" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A253" s="67"/>
+      <c r="A253" s="67" t="s">
+        <v>302</v>
+      </c>
       <c r="B253" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C253" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="E253" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="E253" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F253" s="27" t="s">
         <v>10</v>
       </c>
       <c r="G253" s="3"/>
-      <c r="H253" s="15"/>
+      <c r="H253" s="15" t="s">
+        <v>304</v>
+      </c>
       <c r="I253" s="3"/>
       <c r="J253" s="1"/>
       <c r="K253" s="1"/>
@@ -11810,7 +11814,7 @@
         <v>1</v>
       </c>
       <c r="C254" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>449</v>
@@ -11847,16 +11851,16 @@
         <v>1</v>
       </c>
       <c r="C255" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>489</v>
+        <v>448</v>
       </c>
       <c r="E255" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F255" s="54" t="s">
-        <v>22</v>
+      <c r="F255" s="27" t="s">
+        <v>10</v>
       </c>
       <c r="G255" s="3"/>
       <c r="H255" s="15"/>
@@ -11884,10 +11888,10 @@
         <v>1</v>
       </c>
       <c r="C256" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E256" s="21" t="s">
         <v>9</v>
@@ -11921,10 +11925,10 @@
         <v>1</v>
       </c>
       <c r="C257" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E257" s="21" t="s">
         <v>9</v>
@@ -11958,10 +11962,10 @@
         <v>1</v>
       </c>
       <c r="C258" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E258" s="21" t="s">
         <v>9</v>
@@ -11995,7 +11999,7 @@
         <v>1</v>
       </c>
       <c r="C259" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>492</v>
@@ -12032,10 +12036,10 @@
         <v>1</v>
       </c>
       <c r="C260" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E260" s="21" t="s">
         <v>9</v>
@@ -12069,10 +12073,10 @@
         <v>1</v>
       </c>
       <c r="C261" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E261" s="21" t="s">
         <v>9</v>
@@ -12106,10 +12110,10 @@
         <v>1</v>
       </c>
       <c r="C262" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E262" s="21" t="s">
         <v>9</v>
@@ -12143,16 +12147,16 @@
         <v>1</v>
       </c>
       <c r="C263" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E263" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F263" s="55" t="s">
-        <v>53</v>
+      <c r="F263" s="54" t="s">
+        <v>22</v>
       </c>
       <c r="G263" s="3"/>
       <c r="H263" s="15"/>
@@ -12175,26 +12179,24 @@
       <c r="Y263" s="1"/>
     </row>
     <row r="264" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A264" s="58"/>
+      <c r="A264" s="67"/>
       <c r="B264" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C264" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E264" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E264" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F264" s="54" t="s">
-        <v>22</v>
+      <c r="F264" s="55" t="s">
+        <v>53</v>
       </c>
       <c r="G264" s="3"/>
-      <c r="H264" s="15" t="s">
-        <v>307</v>
-      </c>
+      <c r="H264" s="15"/>
       <c r="I264" s="3"/>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -12213,26 +12215,26 @@
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
     </row>
-    <row r="265" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A265" s="58"/>
       <c r="B265" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C265" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E265" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="E265" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F265" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G265" s="3"/>
-      <c r="H265" s="16" t="s">
-        <v>309</v>
+      <c r="H265" s="15" t="s">
+        <v>306</v>
       </c>
       <c r="I265" s="3"/>
       <c r="J265" s="1"/>
@@ -12258,12 +12260,12 @@
         <v>1</v>
       </c>
       <c r="C266" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E266" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="E266" s="46" t="s">
         <v>9</v>
       </c>
       <c r="F266" s="54" t="s">
@@ -12271,7 +12273,7 @@
       </c>
       <c r="G266" s="3"/>
       <c r="H266" s="16" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I266" s="3"/>
       <c r="J266" s="1"/>
@@ -12297,10 +12299,10 @@
         <v>1</v>
       </c>
       <c r="C267" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>500</v>
+        <v>309</v>
       </c>
       <c r="E267" s="21" t="s">
         <v>9</v>
@@ -12309,7 +12311,9 @@
         <v>22</v>
       </c>
       <c r="G267" s="3"/>
-      <c r="H267" s="16"/>
+      <c r="H267" s="16" t="s">
+        <v>310</v>
+      </c>
       <c r="I267" s="3"/>
       <c r="J267" s="1"/>
       <c r="K267" s="1"/>
@@ -12328,27 +12332,25 @@
       <c r="X267" s="1"/>
       <c r="Y267" s="1"/>
     </row>
-    <row r="268" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="58"/>
       <c r="B268" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C268" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E268" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="E268" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F268" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G268" s="3"/>
-      <c r="H268" s="15" t="s">
-        <v>313</v>
-      </c>
+      <c r="H268" s="16"/>
       <c r="I268" s="3"/>
       <c r="J268" s="1"/>
       <c r="K268" s="1"/>
@@ -12373,10 +12375,10 @@
         <v>1</v>
       </c>
       <c r="C269" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E269" s="8" t="s">
         <v>9</v>
@@ -12386,7 +12388,7 @@
       </c>
       <c r="G269" s="3"/>
       <c r="H269" s="15" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I269" s="3"/>
       <c r="J269" s="1"/>
@@ -12412,19 +12414,21 @@
         <v>1</v>
       </c>
       <c r="C270" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E270" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E270" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F270" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G270" s="3"/>
-      <c r="H270" s="15"/>
+      <c r="H270" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I270" s="3"/>
       <c r="J270" s="1"/>
       <c r="K270" s="1"/>
@@ -12449,21 +12453,19 @@
         <v>1</v>
       </c>
       <c r="C271" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E271" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="E271" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F271" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G271" s="3"/>
-      <c r="H271" s="15" t="s">
-        <v>317</v>
-      </c>
+      <c r="H271" s="15"/>
       <c r="I271" s="3"/>
       <c r="J271" s="1"/>
       <c r="K271" s="1"/>
@@ -12482,26 +12484,26 @@
       <c r="X271" s="1"/>
       <c r="Y271" s="1"/>
     </row>
-    <row r="272" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A272" s="58"/>
       <c r="B272" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C272" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>318</v>
+        <v>500</v>
       </c>
       <c r="E272" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F272" s="55" t="s">
+      <c r="F272" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G272" s="3"/>
-      <c r="H272" s="16" t="s">
-        <v>319</v>
+      <c r="H272" s="15" t="s">
+        <v>316</v>
       </c>
       <c r="I272" s="3"/>
       <c r="J272" s="1"/>
@@ -12521,26 +12523,26 @@
       <c r="X272" s="1"/>
       <c r="Y272" s="1"/>
     </row>
-    <row r="273" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A273" s="58"/>
       <c r="B273" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C273" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E273" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F273" s="54" t="s">
+      <c r="F273" s="55" t="s">
         <v>22</v>
       </c>
       <c r="G273" s="3"/>
-      <c r="H273" s="15" t="s">
-        <v>321</v>
+      <c r="H273" s="16" t="s">
+        <v>318</v>
       </c>
       <c r="I273" s="3"/>
       <c r="J273" s="1"/>
@@ -12566,10 +12568,10 @@
         <v>0</v>
       </c>
       <c r="C274" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E274" s="8" t="s">
         <v>9</v>
@@ -12579,7 +12581,7 @@
       </c>
       <c r="G274" s="3"/>
       <c r="H274" s="15" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I274" s="3"/>
       <c r="J274" s="1"/>
@@ -12599,16 +12601,16 @@
       <c r="X274" s="1"/>
       <c r="Y274" s="1"/>
     </row>
-    <row r="275" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A275" s="58"/>
       <c r="B275" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C275" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E275" s="8" t="s">
         <v>9</v>
@@ -12617,8 +12619,8 @@
         <v>22</v>
       </c>
       <c r="G275" s="3"/>
-      <c r="H275" s="16" t="s">
-        <v>325</v>
+      <c r="H275" s="15" t="s">
+        <v>322</v>
       </c>
       <c r="I275" s="3"/>
       <c r="J275" s="1"/>
@@ -12638,16 +12640,16 @@
       <c r="X275" s="1"/>
       <c r="Y275" s="1"/>
     </row>
-    <row r="276" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="58"/>
       <c r="B276" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C276" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E276" s="8" t="s">
         <v>9</v>
@@ -12656,8 +12658,8 @@
         <v>22</v>
       </c>
       <c r="G276" s="3"/>
-      <c r="H276" s="15" t="s">
-        <v>327</v>
+      <c r="H276" s="16" t="s">
+        <v>324</v>
       </c>
       <c r="I276" s="3"/>
       <c r="J276" s="1"/>
@@ -12680,13 +12682,13 @@
     <row r="277" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A277" s="58"/>
       <c r="B277" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C277" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E277" s="8" t="s">
         <v>9</v>
@@ -12696,7 +12698,7 @@
       </c>
       <c r="G277" s="3"/>
       <c r="H277" s="15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I277" s="3"/>
       <c r="J277" s="1"/>
@@ -12722,10 +12724,10 @@
         <v>1</v>
       </c>
       <c r="C278" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E278" s="8" t="s">
         <v>9</v>
@@ -12735,7 +12737,7 @@
       </c>
       <c r="G278" s="3"/>
       <c r="H278" s="15" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I278" s="3"/>
       <c r="J278" s="1"/>
@@ -12755,16 +12757,16 @@
       <c r="X278" s="1"/>
       <c r="Y278" s="1"/>
     </row>
-    <row r="279" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A279" s="58"/>
       <c r="B279" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C279" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E279" s="8" t="s">
         <v>9</v>
@@ -12773,8 +12775,8 @@
         <v>22</v>
       </c>
       <c r="G279" s="3"/>
-      <c r="H279" s="16" t="s">
-        <v>333</v>
+      <c r="H279" s="15" t="s">
+        <v>330</v>
       </c>
       <c r="I279" s="3"/>
       <c r="J279" s="1"/>
@@ -12797,22 +12799,24 @@
     <row r="280" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="58"/>
       <c r="B280" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C280" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E280" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="E280" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F280" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G280" s="3"/>
-      <c r="H280" s="16"/>
+      <c r="H280" s="16" t="s">
+        <v>332</v>
+      </c>
       <c r="I280" s="3"/>
       <c r="J280" s="1"/>
       <c r="K280" s="1"/>
@@ -12837,10 +12841,10 @@
         <v>1</v>
       </c>
       <c r="C281" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E281" s="21" t="s">
         <v>9</v>
@@ -12874,10 +12878,10 @@
         <v>1</v>
       </c>
       <c r="C282" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E282" s="21" t="s">
         <v>9</v>
@@ -12911,16 +12915,16 @@
         <v>1</v>
       </c>
       <c r="C283" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E283" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F283" s="55" t="s">
-        <v>53</v>
+      <c r="F283" s="54" t="s">
+        <v>22</v>
       </c>
       <c r="G283" s="3"/>
       <c r="H283" s="16"/>
@@ -12948,10 +12952,10 @@
         <v>1</v>
       </c>
       <c r="C284" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E284" s="21" t="s">
         <v>9</v>
@@ -12984,14 +12988,18 @@
       <c r="B285" s="50" t="b">
         <v>1</v>
       </c>
-      <c r="C285" s="2"/>
+      <c r="C285" s="2">
+        <v>33</v>
+      </c>
       <c r="D285" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E285" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F285" s="55"/>
+      <c r="F285" s="55" t="s">
+        <v>53</v>
+      </c>
       <c r="G285" s="3"/>
       <c r="H285" s="16"/>
       <c r="I285" s="3"/>
@@ -13015,24 +13023,18 @@
     <row r="286" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="58"/>
       <c r="B286" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C286" s="2">
-        <v>34</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C286" s="2"/>
       <c r="D286" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="E286" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="E286" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F286" s="28" t="s">
-        <v>53</v>
-      </c>
+      <c r="F286" s="55"/>
       <c r="G286" s="3"/>
-      <c r="H286" s="16" t="s">
-        <v>335</v>
-      </c>
+      <c r="H286" s="16"/>
       <c r="I286" s="3"/>
       <c r="J286" s="1"/>
       <c r="K286" s="1"/>
@@ -13057,10 +13059,10 @@
         <v>0</v>
       </c>
       <c r="C287" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E287" s="8" t="s">
         <v>9</v>
@@ -13070,7 +13072,7 @@
       </c>
       <c r="G287" s="3"/>
       <c r="H287" s="16" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I287" s="3"/>
       <c r="J287" s="1"/>
@@ -13096,10 +13098,10 @@
         <v>0</v>
       </c>
       <c r="C288" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E288" s="8" t="s">
         <v>9</v>
@@ -13109,7 +13111,7 @@
       </c>
       <c r="G288" s="3"/>
       <c r="H288" s="16" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I288" s="3"/>
       <c r="J288" s="1"/>
@@ -13129,16 +13131,16 @@
       <c r="X288" s="1"/>
       <c r="Y288" s="1"/>
     </row>
-    <row r="289" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A289" s="58"/>
       <c r="B289" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C289" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E289" s="8" t="s">
         <v>9</v>
@@ -13147,8 +13149,8 @@
         <v>53</v>
       </c>
       <c r="G289" s="3"/>
-      <c r="H289" s="15" t="s">
-        <v>341</v>
+      <c r="H289" s="16" t="s">
+        <v>338</v>
       </c>
       <c r="I289" s="3"/>
       <c r="J289" s="1"/>
@@ -13174,10 +13176,10 @@
         <v>0</v>
       </c>
       <c r="C290" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E290" s="8" t="s">
         <v>9</v>
@@ -13187,7 +13189,7 @@
       </c>
       <c r="G290" s="3"/>
       <c r="H290" s="15" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I290" s="3"/>
       <c r="J290" s="1"/>
@@ -13207,16 +13209,16 @@
       <c r="X290" s="1"/>
       <c r="Y290" s="1"/>
     </row>
-    <row r="291" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A291" s="58"/>
       <c r="B291" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C291" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E291" s="8" t="s">
         <v>9</v>
@@ -13225,8 +13227,8 @@
         <v>53</v>
       </c>
       <c r="G291" s="3"/>
-      <c r="H291" s="16" t="s">
-        <v>345</v>
+      <c r="H291" s="15" t="s">
+        <v>342</v>
       </c>
       <c r="I291" s="3"/>
       <c r="J291" s="1"/>
@@ -13246,15 +13248,27 @@
       <c r="X291" s="1"/>
       <c r="Y291" s="1"/>
     </row>
-    <row r="292" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A292" s="1"/>
-      <c r="B292" s="1"/>
-      <c r="C292" s="2"/>
-      <c r="D292" s="1"/>
-      <c r="E292" s="3"/>
-      <c r="F292" s="1"/>
+    <row r="292" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A292" s="58"/>
+      <c r="B292" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="C292" s="2">
+        <v>39</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E292" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F292" s="28" t="s">
+        <v>53</v>
+      </c>
       <c r="G292" s="3"/>
-      <c r="H292" s="4"/>
+      <c r="H292" s="16" t="s">
+        <v>344</v>
+      </c>
       <c r="I292" s="3"/>
       <c r="J292" s="1"/>
       <c r="K292" s="1"/>
@@ -13300,29 +13314,15 @@
       <c r="X293" s="1"/>
       <c r="Y293" s="1"/>
     </row>
-    <row r="294" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A294" s="67" t="s">
-        <v>346</v>
-      </c>
-      <c r="B294" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C294" s="2">
-        <v>1</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E294" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F294" s="27" t="s">
-        <v>10</v>
-      </c>
+    <row r="294" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A294" s="1"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="1"/>
+      <c r="E294" s="3"/>
+      <c r="F294" s="1"/>
       <c r="G294" s="3"/>
-      <c r="H294" s="16" t="s">
-        <v>348</v>
-      </c>
+      <c r="H294" s="4"/>
       <c r="I294" s="3"/>
       <c r="J294" s="1"/>
       <c r="K294" s="1"/>
@@ -13341,26 +13341,28 @@
       <c r="X294" s="1"/>
       <c r="Y294" s="1"/>
     </row>
-    <row r="295" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A295" s="58"/>
+    <row r="295" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A295" s="67" t="s">
+        <v>345</v>
+      </c>
       <c r="B295" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C295" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E295" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E295" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F295" s="26" t="s">
-        <v>22</v>
+      <c r="F295" s="27" t="s">
+        <v>10</v>
       </c>
       <c r="G295" s="3"/>
-      <c r="H295" s="15" t="s">
-        <v>350</v>
+      <c r="H295" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="I295" s="3"/>
       <c r="J295" s="1"/>
@@ -13386,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="C296" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E296" s="8" t="s">
         <v>9</v>
@@ -13399,7 +13401,7 @@
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="15" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I296" s="3"/>
       <c r="J296" s="1"/>
@@ -13425,10 +13427,10 @@
         <v>0</v>
       </c>
       <c r="C297" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E297" s="8" t="s">
         <v>9</v>
@@ -13438,7 +13440,7 @@
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="15" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I297" s="3"/>
       <c r="J297" s="1"/>
@@ -13464,10 +13466,10 @@
         <v>0</v>
       </c>
       <c r="C298" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E298" s="8" t="s">
         <v>9</v>
@@ -13476,8 +13478,8 @@
         <v>22</v>
       </c>
       <c r="G298" s="3"/>
-      <c r="H298" s="20" t="s">
-        <v>356</v>
+      <c r="H298" s="15" t="s">
+        <v>353</v>
       </c>
       <c r="I298" s="3"/>
       <c r="J298" s="1"/>
@@ -13503,20 +13505,20 @@
         <v>0</v>
       </c>
       <c r="C299" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E299" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F299" s="28" t="s">
-        <v>53</v>
+      <c r="F299" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="G299" s="3"/>
-      <c r="H299" s="15" t="s">
-        <v>358</v>
+      <c r="H299" s="20" t="s">
+        <v>355</v>
       </c>
       <c r="I299" s="3"/>
       <c r="J299" s="1"/>
@@ -13536,17 +13538,27 @@
       <c r="X299" s="1"/>
       <c r="Y299" s="1"/>
     </row>
-    <row r="300" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A300" s="1"/>
+    <row r="300" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+      <c r="A300" s="58"/>
       <c r="B300" s="50" t="b">
         <v>0</v>
       </c>
-      <c r="C300" s="2"/>
-      <c r="D300" s="1"/>
-      <c r="E300" s="3"/>
-      <c r="F300" s="1"/>
+      <c r="C300" s="2">
+        <v>6</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E300" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F300" s="28" t="s">
+        <v>53</v>
+      </c>
       <c r="G300" s="3"/>
-      <c r="H300" s="4"/>
+      <c r="H300" s="15" t="s">
+        <v>357</v>
+      </c>
       <c r="I300" s="3"/>
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
@@ -13595,24 +13607,14 @@
       <c r="Y301" s="1"/>
     </row>
     <row r="302" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A302" s="64" t="s">
-        <v>392</v>
-      </c>
+      <c r="A302" s="1"/>
       <c r="B302" s="50" t="b">
         <v>0</v>
       </c>
-      <c r="C302" s="2">
-        <v>1</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="E302" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F302" s="40" t="s">
-        <v>401</v>
-      </c>
+      <c r="C302" s="2"/>
+      <c r="D302" s="1"/>
+      <c r="E302" s="3"/>
+      <c r="F302" s="1"/>
       <c r="G302" s="3"/>
       <c r="H302" s="4"/>
       <c r="I302" s="3"/>
@@ -13634,21 +13636,23 @@
       <c r="Y302" s="1"/>
     </row>
     <row r="303" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A303" s="58"/>
+      <c r="A303" s="64" t="s">
+        <v>391</v>
+      </c>
       <c r="B303" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C303" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E303" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F303" s="40" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G303" s="3"/>
       <c r="H303" s="4"/>
@@ -13676,16 +13680,16 @@
         <v>0</v>
       </c>
       <c r="C304" s="2">
-        <v>3</v>
-      </c>
-      <c r="D304" s="24" t="s">
-        <v>405</v>
+        <v>2</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="E304" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F304" s="40" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G304" s="3"/>
       <c r="H304" s="4"/>
@@ -13713,16 +13717,16 @@
         <v>0</v>
       </c>
       <c r="C305" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D305" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E305" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F305" s="40" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G305" s="3"/>
       <c r="H305" s="4"/>
@@ -13747,19 +13751,19 @@
     <row r="306" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="58"/>
       <c r="B306" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C306" s="2">
-        <v>5</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>481</v>
+        <v>4</v>
+      </c>
+      <c r="D306" s="24" t="s">
+        <v>405</v>
       </c>
       <c r="E306" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F306" s="40" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G306" s="3"/>
       <c r="H306" s="4"/>
@@ -13784,18 +13788,20 @@
     <row r="307" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="58"/>
       <c r="B307" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C307" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="E307" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F307" s="1"/>
+      <c r="F307" s="40" t="s">
+        <v>400</v>
+      </c>
       <c r="G307" s="3"/>
       <c r="H307" s="4"/>
       <c r="I307" s="3"/>
@@ -13822,10 +13828,14 @@
         <v>0</v>
       </c>
       <c r="C308" s="2">
-        <v>7</v>
-      </c>
-      <c r="D308" s="1"/>
-      <c r="E308" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="E308" s="21" t="s">
+        <v>9</v>
+      </c>
       <c r="F308" s="1"/>
       <c r="G308" s="3"/>
       <c r="H308" s="4"/>
@@ -13853,7 +13863,7 @@
         <v>0</v>
       </c>
       <c r="C309" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D309" s="1"/>
       <c r="E309" s="3"/>
@@ -13884,7 +13894,7 @@
         <v>0</v>
       </c>
       <c r="C310" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D310" s="1"/>
       <c r="E310" s="3"/>
@@ -13915,7 +13925,7 @@
         <v>0</v>
       </c>
       <c r="C311" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D311" s="1"/>
       <c r="E311" s="3"/>
@@ -13946,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="C312" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D312" s="1"/>
       <c r="E312" s="3"/>
@@ -13977,7 +13987,7 @@
         <v>0</v>
       </c>
       <c r="C313" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D313" s="1"/>
       <c r="E313" s="3"/>
@@ -14008,7 +14018,7 @@
         <v>0</v>
       </c>
       <c r="C314" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D314" s="1"/>
       <c r="E314" s="3"/>
@@ -14039,7 +14049,7 @@
         <v>0</v>
       </c>
       <c r="C315" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D315" s="1"/>
       <c r="E315" s="3"/>
@@ -14070,7 +14080,7 @@
         <v>0</v>
       </c>
       <c r="C316" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D316" s="1"/>
       <c r="E316" s="3"/>
@@ -14095,10 +14105,14 @@
       <c r="X316" s="1"/>
       <c r="Y316" s="1"/>
     </row>
-    <row r="317" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="58"/>
-      <c r="B317" s="1"/>
-      <c r="C317" s="2"/>
+      <c r="B317" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="C317" s="2">
+        <v>15</v>
+      </c>
       <c r="D317" s="1"/>
       <c r="E317" s="3"/>
       <c r="F317" s="1"/>
@@ -14231,7 +14245,7 @@
       <c r="Y321" s="1"/>
     </row>
     <row r="322" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A322" s="1"/>
+      <c r="A322" s="58"/>
       <c r="B322" s="1"/>
       <c r="C322" s="2"/>
       <c r="D322" s="1"/>
@@ -34696,23 +34710,50 @@
       <c r="X1079" s="1"/>
       <c r="Y1079" s="1"/>
     </row>
+    <row r="1080" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A1080" s="1"/>
+      <c r="B1080" s="1"/>
+      <c r="C1080" s="2"/>
+      <c r="D1080" s="1"/>
+      <c r="E1080" s="3"/>
+      <c r="F1080" s="1"/>
+      <c r="G1080" s="3"/>
+      <c r="H1080" s="4"/>
+      <c r="I1080" s="3"/>
+      <c r="J1080" s="1"/>
+      <c r="K1080" s="1"/>
+      <c r="L1080" s="1"/>
+      <c r="M1080" s="1"/>
+      <c r="N1080" s="1"/>
+      <c r="O1080" s="1"/>
+      <c r="P1080" s="1"/>
+      <c r="Q1080" s="1"/>
+      <c r="R1080" s="1"/>
+      <c r="S1080" s="1"/>
+      <c r="T1080" s="1"/>
+      <c r="U1080" s="1"/>
+      <c r="V1080" s="1"/>
+      <c r="W1080" s="1"/>
+      <c r="X1080" s="1"/>
+      <c r="Y1080" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="A6:A48"/>
     <mergeCell ref="A53:A69"/>
-    <mergeCell ref="A302:A321"/>
+    <mergeCell ref="A303:A322"/>
     <mergeCell ref="A74:A91"/>
     <mergeCell ref="A96:A109"/>
-    <mergeCell ref="A252:A291"/>
-    <mergeCell ref="A294:A299"/>
+    <mergeCell ref="A253:A292"/>
+    <mergeCell ref="A295:A300"/>
     <mergeCell ref="A112:A129"/>
     <mergeCell ref="A132:A148"/>
     <mergeCell ref="A151:A178"/>
     <mergeCell ref="A182:A194"/>
     <mergeCell ref="A197:A202"/>
     <mergeCell ref="A205:A209"/>
-    <mergeCell ref="A212:A248"/>
+    <mergeCell ref="A212:A249"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E53" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
@@ -34878,44 +34919,44 @@
     <hyperlink ref="E219" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
     <hyperlink ref="E221" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
     <hyperlink ref="E222" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="E226" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="E227" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="E229" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="E230" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="E231" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="E232" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="E236" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="E240" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="E242" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="E243" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="E245" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="E247" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="E248" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="E265" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="E268" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="E269" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="E271" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="E272" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="E273" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="E274" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="E275" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="E276" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="E277" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="E278" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="E279" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="E286" r:id="rId189" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="E287" r:id="rId190" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="E288" r:id="rId191" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="E289" r:id="rId192" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="E290" r:id="rId193" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="E291" r:id="rId194" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="E294" r:id="rId195" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="E295" r:id="rId196" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="E296" r:id="rId197" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="E297" r:id="rId198" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="E298" r:id="rId199" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="E299" r:id="rId200" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="E249" r:id="rId201" xr:uid="{38535620-DA2F-45B6-BE53-7BE35BAD917E}"/>
+    <hyperlink ref="E227" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="E228" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="E230" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="E231" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="E232" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="E233" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="E237" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="E241" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="E243" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="E244" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="E246" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="E248" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="E249" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="E266" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="E269" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="E270" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="E272" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="E273" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="E274" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="E275" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="E276" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="E277" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="E278" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="E279" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="E280" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="E287" r:id="rId189" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="E288" r:id="rId190" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="E289" r:id="rId191" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="E290" r:id="rId192" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="E291" r:id="rId193" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="E292" r:id="rId194" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="E295" r:id="rId195" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="E296" r:id="rId196" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="E297" r:id="rId197" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="E298" r:id="rId198" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="E299" r:id="rId199" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="E300" r:id="rId200" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="E250" r:id="rId201" xr:uid="{38535620-DA2F-45B6-BE53-7BE35BAD917E}"/>
     <hyperlink ref="E180" r:id="rId202" xr:uid="{52A62708-7A1B-4947-8125-51CD78E69CDC}"/>
     <hyperlink ref="E179" r:id="rId203" xr:uid="{90A2CCC4-C963-4688-BF93-898F1AB744EB}"/>
     <hyperlink ref="G104" r:id="rId204" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
@@ -34969,19 +35010,19 @@
     <hyperlink ref="E10" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="G7" r:id="rId253" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="E7" r:id="rId254" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E302" r:id="rId255" xr:uid="{49C446A4-86D9-438E-8C85-C2CBF2D0C601}"/>
+    <hyperlink ref="E303" r:id="rId255" xr:uid="{49C446A4-86D9-438E-8C85-C2CBF2D0C601}"/>
     <hyperlink ref="E29" r:id="rId256" xr:uid="{15B4076B-7C29-451C-A0E0-E0CDB84955C7}"/>
-    <hyperlink ref="E303" r:id="rId257" xr:uid="{5897208F-5F6C-4E1B-8B0F-03D62428448A}"/>
+    <hyperlink ref="E304" r:id="rId257" xr:uid="{5897208F-5F6C-4E1B-8B0F-03D62428448A}"/>
     <hyperlink ref="E41" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
     <hyperlink ref="E15" r:id="rId259" xr:uid="{36657CEA-F972-477D-AC24-77B031A0C947}"/>
-    <hyperlink ref="E304" r:id="rId260" xr:uid="{0B318E6F-5375-45A5-A623-A5D070F4F786}"/>
-    <hyperlink ref="E305" r:id="rId261" xr:uid="{28A35100-95C6-4598-8EAE-4903F97A507B}"/>
+    <hyperlink ref="E305" r:id="rId260" xr:uid="{0B318E6F-5375-45A5-A623-A5D070F4F786}"/>
+    <hyperlink ref="E306" r:id="rId261" xr:uid="{28A35100-95C6-4598-8EAE-4903F97A507B}"/>
     <hyperlink ref="E32" r:id="rId262" xr:uid="{A642EB9F-9B4D-467C-AA82-CE1A728B251C}"/>
     <hyperlink ref="E27" r:id="rId263" xr:uid="{A1884A7B-6025-4BC0-B0A7-10DF9BA889E7}"/>
-    <hyperlink ref="E241" r:id="rId264" xr:uid="{DD148482-9331-495D-A315-B2667528DE27}"/>
-    <hyperlink ref="E233" r:id="rId265" xr:uid="{9AFBA357-2FAE-42C6-BAC6-9567300CA7EB}"/>
+    <hyperlink ref="E242" r:id="rId264" xr:uid="{DD148482-9331-495D-A315-B2667528DE27}"/>
+    <hyperlink ref="E234" r:id="rId265" xr:uid="{9AFBA357-2FAE-42C6-BAC6-9567300CA7EB}"/>
     <hyperlink ref="E213" r:id="rId266" xr:uid="{222EEF32-42E7-41DB-92A2-B7E1E19CBDFD}"/>
-    <hyperlink ref="E239" r:id="rId267" xr:uid="{7EFFF805-CE73-433D-8429-8C55CEC7C072}"/>
+    <hyperlink ref="E240" r:id="rId267" xr:uid="{7EFFF805-CE73-433D-8429-8C55CEC7C072}"/>
     <hyperlink ref="E139" r:id="rId268" xr:uid="{397DA75B-3BBC-4F89-A9DA-27EB8A53151E}"/>
     <hyperlink ref="E143" r:id="rId269" xr:uid="{ACEE0CD9-D250-46A6-9BEB-25465E3F5877}"/>
     <hyperlink ref="E142" r:id="rId270" xr:uid="{726ABE82-32B2-45DF-86E4-D4B65D08B99B}"/>
@@ -34996,27 +35037,27 @@
     <hyperlink ref="E81" r:id="rId279" xr:uid="{27F80336-44DE-477D-A42B-75FF0BEAEB14}"/>
     <hyperlink ref="E80" r:id="rId280" xr:uid="{CBD0C4A3-4F0E-49C4-B907-E32F28123DAA}"/>
     <hyperlink ref="E82" r:id="rId281" xr:uid="{3496D658-F7DB-469C-8D98-A524DB1BB47C}"/>
-    <hyperlink ref="E238" r:id="rId282" xr:uid="{8C4590C0-E71B-4B6F-928F-91CDE3276DD9}"/>
-    <hyperlink ref="E237" r:id="rId283" xr:uid="{9D29C97A-A6D3-48A4-9664-8DCE5B234FAB}"/>
-    <hyperlink ref="E235" r:id="rId284" xr:uid="{9921A962-A113-4002-BDE2-4F4E4320B387}"/>
+    <hyperlink ref="E239" r:id="rId282" xr:uid="{8C4590C0-E71B-4B6F-928F-91CDE3276DD9}"/>
+    <hyperlink ref="E238" r:id="rId283" xr:uid="{9D29C97A-A6D3-48A4-9664-8DCE5B234FAB}"/>
+    <hyperlink ref="E236" r:id="rId284" xr:uid="{9921A962-A113-4002-BDE2-4F4E4320B387}"/>
     <hyperlink ref="E220" r:id="rId285" xr:uid="{2401C9CC-8D34-433A-BAAD-C1FD2BC14D49}"/>
-    <hyperlink ref="E225" r:id="rId286" xr:uid="{D146BB8F-137F-4456-BBA2-EC755F8EBC46}"/>
-    <hyperlink ref="E228" r:id="rId287" xr:uid="{E360B755-600F-4776-B306-2E5CFACE17ED}"/>
-    <hyperlink ref="E224" r:id="rId288" xr:uid="{A5B75A0D-986A-4F1A-B094-7B65E143FDE2}"/>
+    <hyperlink ref="E226" r:id="rId286" xr:uid="{D146BB8F-137F-4456-BBA2-EC755F8EBC46}"/>
+    <hyperlink ref="E229" r:id="rId287" xr:uid="{E360B755-600F-4776-B306-2E5CFACE17ED}"/>
+    <hyperlink ref="E225" r:id="rId288" xr:uid="{A5B75A0D-986A-4F1A-B094-7B65E143FDE2}"/>
     <hyperlink ref="E107" r:id="rId289" xr:uid="{F858A3E3-5FB0-420A-93A4-648662EF60EA}"/>
     <hyperlink ref="E108" r:id="rId290" xr:uid="{E4B29D74-9296-485B-83BA-F2FBF277CAEE}"/>
     <hyperlink ref="E47" r:id="rId291" xr:uid="{AFD749B1-917D-4B9C-A4A3-C3DEE02AC2C0}"/>
-    <hyperlink ref="E246" r:id="rId292" xr:uid="{0CCBA335-85C5-47D0-ABB1-7AD15CE9C6BE}"/>
-    <hyperlink ref="E254" r:id="rId293" xr:uid="{0556EF01-FFEF-410A-8AA8-8CA7BB356178}"/>
-    <hyperlink ref="E252" r:id="rId294" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="E253" r:id="rId295" xr:uid="{CEDFA42B-F516-4AB2-AC3C-789EA49C621B}"/>
-    <hyperlink ref="E234" r:id="rId296" xr:uid="{B1CD58B6-DF33-4CD0-8D2C-935BE832C573}"/>
-    <hyperlink ref="E244" r:id="rId297" xr:uid="{F18D1A45-C38D-44C9-8381-31675C618684}"/>
+    <hyperlink ref="E247" r:id="rId292" xr:uid="{0CCBA335-85C5-47D0-ABB1-7AD15CE9C6BE}"/>
+    <hyperlink ref="E255" r:id="rId293" xr:uid="{0556EF01-FFEF-410A-8AA8-8CA7BB356178}"/>
+    <hyperlink ref="E253" r:id="rId294" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="E254" r:id="rId295" xr:uid="{CEDFA42B-F516-4AB2-AC3C-789EA49C621B}"/>
+    <hyperlink ref="E235" r:id="rId296" xr:uid="{B1CD58B6-DF33-4CD0-8D2C-935BE832C573}"/>
+    <hyperlink ref="E245" r:id="rId297" xr:uid="{F18D1A45-C38D-44C9-8381-31675C618684}"/>
     <hyperlink ref="E56" r:id="rId298" xr:uid="{DD79BAA1-3570-429D-B5E3-B3B22125D45D}"/>
     <hyperlink ref="E55" r:id="rId299" xr:uid="{AA3B5FD0-ABB7-481B-A828-1CEE4B997FFD}"/>
     <hyperlink ref="E54" r:id="rId300" xr:uid="{BF9D025F-FFAE-4B6F-BE59-85E6A492D964}"/>
     <hyperlink ref="E57" r:id="rId301" xr:uid="{25BF0BAB-C327-4860-BE43-460DA2024CB4}"/>
-    <hyperlink ref="E223" r:id="rId302" xr:uid="{A4991D16-BC46-4421-9733-4A0B675397D5}"/>
+    <hyperlink ref="E224" r:id="rId302" xr:uid="{A4991D16-BC46-4421-9733-4A0B675397D5}"/>
     <hyperlink ref="E61" r:id="rId303" xr:uid="{3F28325A-419D-479F-A2CB-A6026E9C1738}"/>
     <hyperlink ref="E62" r:id="rId304" xr:uid="{B55832FE-CDC8-476F-BFB2-210023AFDA15}"/>
     <hyperlink ref="E64" r:id="rId305" xr:uid="{B0548B46-2425-4209-B406-7C5E06BB0B37}"/>
@@ -35034,7 +35075,7 @@
     <hyperlink ref="E154" r:id="rId317" xr:uid="{3F9A6173-1CC2-4924-8DCB-DA0907EBC497}"/>
     <hyperlink ref="E23" r:id="rId318" xr:uid="{CFCB346F-57BF-4E1F-A83E-1ECF2056F264}"/>
     <hyperlink ref="E102" r:id="rId319" xr:uid="{2356458E-6B22-49DA-9E6A-10397CF5FFCB}"/>
-    <hyperlink ref="E306" r:id="rId320" xr:uid="{4E26D969-664E-4EA5-BCDD-C0244659BD80}"/>
+    <hyperlink ref="E307" r:id="rId320" xr:uid="{4E26D969-664E-4EA5-BCDD-C0244659BD80}"/>
     <hyperlink ref="E11" r:id="rId321" xr:uid="{79FBDA3E-6FA8-4642-9106-ECA30BC0F184}"/>
     <hyperlink ref="E16" r:id="rId322" xr:uid="{76475329-A2A3-4832-B080-9DF1FCF7B69C}"/>
     <hyperlink ref="E34" r:id="rId323" xr:uid="{712331F6-B9ED-461A-B3A4-361688CBC32C}"/>
@@ -35042,29 +35083,30 @@
     <hyperlink ref="E20" r:id="rId325" xr:uid="{7983D009-F451-44FD-810F-30FF2A3718BA}"/>
     <hyperlink ref="E19" r:id="rId326" xr:uid="{CD31F41D-EA1B-403F-8D0D-B77515C1536B}"/>
     <hyperlink ref="E113" r:id="rId327" xr:uid="{127B98B1-79F3-43C9-B7FF-4FBC27351376}"/>
-    <hyperlink ref="E255" r:id="rId328" xr:uid="{2D7D988B-76D9-4BEC-8F29-806C1E841434}"/>
-    <hyperlink ref="E264" r:id="rId329" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="E256" r:id="rId330" xr:uid="{243B74CF-B5C2-468E-9F2F-0DA78790403B}"/>
-    <hyperlink ref="E257" r:id="rId331" xr:uid="{9E359A2D-80A4-4440-B6F6-E0BD637BE478}"/>
-    <hyperlink ref="E259" r:id="rId332" xr:uid="{92D99966-CAE9-4A3E-8110-212EFFA305D9}"/>
-    <hyperlink ref="E258" r:id="rId333" xr:uid="{82293A7C-C43B-41FD-91B1-86521EAC11D6}"/>
+    <hyperlink ref="E256" r:id="rId328" xr:uid="{2D7D988B-76D9-4BEC-8F29-806C1E841434}"/>
+    <hyperlink ref="E265" r:id="rId329" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="E257" r:id="rId330" xr:uid="{243B74CF-B5C2-468E-9F2F-0DA78790403B}"/>
+    <hyperlink ref="E258" r:id="rId331" xr:uid="{9E359A2D-80A4-4440-B6F6-E0BD637BE478}"/>
+    <hyperlink ref="E260" r:id="rId332" xr:uid="{92D99966-CAE9-4A3E-8110-212EFFA305D9}"/>
+    <hyperlink ref="E259" r:id="rId333" xr:uid="{82293A7C-C43B-41FD-91B1-86521EAC11D6}"/>
     <hyperlink ref="E12" r:id="rId334" xr:uid="{68E8B6A2-6017-4405-9549-B2377AC5DEDF}"/>
-    <hyperlink ref="E260" r:id="rId335" xr:uid="{9E27F39A-FC85-46E5-98FF-497FB0860FA7}"/>
-    <hyperlink ref="E261" r:id="rId336" xr:uid="{3BF3C81C-57C8-46D6-BC82-B24998AE425F}"/>
-    <hyperlink ref="E262" r:id="rId337" xr:uid="{D60890AA-5FFE-44F0-AA27-28E4BFB644F6}"/>
-    <hyperlink ref="E263" r:id="rId338" xr:uid="{BEBCCD33-BF2B-422C-8302-61C8E85BEDED}"/>
-    <hyperlink ref="E307" r:id="rId339" xr:uid="{FC2672B5-6248-497C-B62C-4B7547222ED5}"/>
-    <hyperlink ref="E267" r:id="rId340" xr:uid="{98B6A04A-6AA6-4AC2-974B-16AADA142558}"/>
-    <hyperlink ref="E270" r:id="rId341" xr:uid="{8F938C70-22E3-4D8B-80C3-A2EDD6B55F32}"/>
-    <hyperlink ref="E284" r:id="rId342" xr:uid="{C19ECC48-6755-42E3-93AC-1AF2A6E16C8B}"/>
-    <hyperlink ref="E282" r:id="rId343" xr:uid="{96721404-CCF2-44A2-9BCC-E8604D34595E}"/>
-    <hyperlink ref="E280" r:id="rId344" xr:uid="{C4C7ED52-DB44-4C33-BB8E-35BEB7281A83}"/>
-    <hyperlink ref="E281" r:id="rId345" xr:uid="{5173BA28-5956-4E15-A77A-2EC7E30FC1EA}"/>
-    <hyperlink ref="E283" r:id="rId346" xr:uid="{74251C99-B647-4AF5-90FF-984998C44E82}"/>
-    <hyperlink ref="E285" r:id="rId347" xr:uid="{43E38533-4E5E-4A3A-B028-87FFDAEA95AF}"/>
-    <hyperlink ref="E266" r:id="rId348" xr:uid="{D8B34417-E714-44C5-92E5-677B9CA2E5A8}"/>
+    <hyperlink ref="E261" r:id="rId335" xr:uid="{9E27F39A-FC85-46E5-98FF-497FB0860FA7}"/>
+    <hyperlink ref="E262" r:id="rId336" xr:uid="{3BF3C81C-57C8-46D6-BC82-B24998AE425F}"/>
+    <hyperlink ref="E263" r:id="rId337" xr:uid="{D60890AA-5FFE-44F0-AA27-28E4BFB644F6}"/>
+    <hyperlink ref="E264" r:id="rId338" xr:uid="{BEBCCD33-BF2B-422C-8302-61C8E85BEDED}"/>
+    <hyperlink ref="E308" r:id="rId339" xr:uid="{FC2672B5-6248-497C-B62C-4B7547222ED5}"/>
+    <hyperlink ref="E268" r:id="rId340" xr:uid="{98B6A04A-6AA6-4AC2-974B-16AADA142558}"/>
+    <hyperlink ref="E271" r:id="rId341" xr:uid="{8F938C70-22E3-4D8B-80C3-A2EDD6B55F32}"/>
+    <hyperlink ref="E285" r:id="rId342" xr:uid="{C19ECC48-6755-42E3-93AC-1AF2A6E16C8B}"/>
+    <hyperlink ref="E283" r:id="rId343" xr:uid="{96721404-CCF2-44A2-9BCC-E8604D34595E}"/>
+    <hyperlink ref="E281" r:id="rId344" xr:uid="{C4C7ED52-DB44-4C33-BB8E-35BEB7281A83}"/>
+    <hyperlink ref="E282" r:id="rId345" xr:uid="{5173BA28-5956-4E15-A77A-2EC7E30FC1EA}"/>
+    <hyperlink ref="E284" r:id="rId346" xr:uid="{74251C99-B647-4AF5-90FF-984998C44E82}"/>
+    <hyperlink ref="E286" r:id="rId347" xr:uid="{43E38533-4E5E-4A3A-B028-87FFDAEA95AF}"/>
+    <hyperlink ref="E267" r:id="rId348" xr:uid="{D8B34417-E714-44C5-92E5-677B9CA2E5A8}"/>
+    <hyperlink ref="E223" r:id="rId349" xr:uid="{CA41E718-82EA-4AAD-BE4C-17139F6C8FCA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId349"/>
+  <pageSetup orientation="portrait" r:id="rId350"/>
 </worksheet>
 </file>
--- a/Strivers List + other Problems.xlsx
+++ b/Strivers List + other Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF03261-8F2E-4493-BC16-2141E561C431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3059B7-02D3-44EA-9678-D90E9E6A8CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10617,7 +10617,7 @@
     <row r="222" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A222" s="58"/>
       <c r="B222" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C222" s="2">
         <v>11</v>
@@ -10765,7 +10765,7 @@
     <row r="226" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A226" s="58"/>
       <c r="B226" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226" s="2">
         <v>14</v>
@@ -11073,7 +11073,7 @@
     <row r="234" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A234" s="58"/>
       <c r="B234" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C234" s="2">
         <v>22</v>

--- a/Strivers List + other Problems.xlsx
+++ b/Strivers List + other Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3059B7-02D3-44EA-9678-D90E9E6A8CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA9A1EA-C9CD-4172-9C36-4B6A49ADD0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="507">
   <si>
     <t>Mark as Done</t>
   </si>
@@ -1385,18 +1385,6 @@
     <t>Frog jump</t>
   </si>
   <si>
-    <t>Find Safest path in grid</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/find-the-safest-path-in-a-grid/description/</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/build-a-matrix-with-conditions/description/</t>
-  </si>
-  <si>
-    <t>Topo sort</t>
-  </si>
-  <si>
     <t>Course Schedule</t>
   </si>
   <si>
@@ -1563,6 +1551,9 @@
   </si>
   <si>
     <t>01 Matrix (Distance to nearest cell having 0)</t>
+  </si>
+  <si>
+    <t>Longest increasing path in the matrix</t>
   </si>
 </sst>
 </file>
@@ -2254,7 +2245,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y1080"/>
+  <dimension ref="A1:Y1079"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -2514,7 +2505,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>9</v>
@@ -2551,7 +2542,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>9</v>
@@ -2627,7 +2618,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>9</v>
@@ -2662,7 +2653,7 @@
       </c>
       <c r="C12" s="30"/>
       <c r="D12" s="29" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>9</v>
@@ -2812,7 +2803,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>9</v>
@@ -2890,7 +2881,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="E18" s="21" t="s">
         <v>9</v>
@@ -2927,7 +2918,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E19" s="21" t="s">
         <v>9</v>
@@ -2964,7 +2955,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E20" s="21" t="s">
         <v>9</v>
@@ -3077,7 +3068,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E23" s="21" t="s">
         <v>9</v>
@@ -3198,7 +3189,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E26" s="34" t="s">
         <v>9</v>
@@ -3518,7 +3509,7 @@
         <v>28</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E34" s="21" t="s">
         <v>9</v>
@@ -3719,7 +3710,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>9</v>
@@ -3756,7 +3747,7 @@
         <v>34</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E40" s="21" t="s">
         <v>9</v>
@@ -3793,7 +3784,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E41" s="34" t="s">
         <v>9</v>
@@ -4111,7 +4102,7 @@
         <v>43</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E49" s="21" t="s">
         <v>9</v>
@@ -4272,7 +4263,7 @@
         <v>2</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E54" s="21" t="s">
         <v>9</v>
@@ -4309,7 +4300,7 @@
         <v>3</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E55" s="21" t="s">
         <v>9</v>
@@ -4346,7 +4337,7 @@
         <v>4</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E56" s="21" t="s">
         <v>9</v>
@@ -4383,7 +4374,7 @@
         <v>5</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E57" s="21" t="s">
         <v>9</v>
@@ -4420,7 +4411,7 @@
         <v>6</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E58" s="21" t="s">
         <v>9</v>
@@ -4496,7 +4487,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>9</v>
@@ -4533,7 +4524,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E61" s="21" t="s">
         <v>9</v>
@@ -4570,7 +4561,7 @@
         <v>10</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E62" s="21" t="s">
         <v>9</v>
@@ -4607,7 +4598,7 @@
         <v>11</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>9</v>
@@ -4644,7 +4635,7 @@
         <v>12</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>9</v>
@@ -4681,7 +4672,7 @@
         <v>13</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E65" s="21" t="s">
         <v>9</v>
@@ -4718,7 +4709,7 @@
         <v>14</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E66" s="21" t="s">
         <v>9</v>
@@ -4755,7 +4746,7 @@
         <v>15</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E67" s="21" t="s">
         <v>9</v>
@@ -6016,7 +6007,7 @@
         <v>7</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>9</v>
@@ -6428,7 +6419,7 @@
       </c>
       <c r="C113" s="30"/>
       <c r="D113" s="29" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E113" s="21" t="s">
         <v>9</v>
@@ -8011,7 +8002,7 @@
       </c>
       <c r="C154" s="30"/>
       <c r="D154" s="29" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E154" s="21" t="s">
         <v>9</v>
@@ -10461,7 +10452,7 @@
     <row r="218" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A218" s="58"/>
       <c r="B218" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C218" s="2">
         <v>7</v>
@@ -10660,10 +10651,10 @@
       </c>
       <c r="C223" s="2"/>
       <c r="D223" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F223" s="26" t="s">
         <v>22</v>
@@ -10697,10 +10688,10 @@
         <v>12</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F224" s="26" t="s">
         <v>22</v>
@@ -10923,7 +10914,7 @@
         <v>18</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E230" s="18" t="s">
         <v>275</v>
@@ -10956,13 +10947,13 @@
     <row r="231" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A231" s="58"/>
       <c r="B231" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C231" s="2">
         <v>19</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E231" s="23" t="s">
         <v>253</v>
@@ -10995,7 +10986,7 @@
     <row r="232" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="58"/>
       <c r="B232" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C232" s="2">
         <v>20</v>
@@ -11034,7 +11025,7 @@
     <row r="233" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A233" s="58"/>
       <c r="B233" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C233" s="2">
         <v>21</v>
@@ -11110,16 +11101,16 @@
     <row r="235" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A235" s="58"/>
       <c r="B235" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C235" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="F235" s="26" t="s">
         <v>22</v>
@@ -11150,19 +11141,21 @@
         <v>0</v>
       </c>
       <c r="C236" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="E236" s="23" t="s">
-        <v>434</v>
+        <v>284</v>
+      </c>
+      <c r="E236" s="18" t="s">
+        <v>246</v>
       </c>
       <c r="F236" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G236" s="3"/>
-      <c r="H236" s="15"/>
+      <c r="H236" s="15" t="s">
+        <v>285</v>
+      </c>
       <c r="I236" s="3"/>
       <c r="J236" s="1"/>
       <c r="K236" s="1"/>
@@ -11184,24 +11177,22 @@
     <row r="237" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A237" s="58"/>
       <c r="B237" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C237" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E237" s="18" t="s">
-        <v>246</v>
+        <v>432</v>
+      </c>
+      <c r="E237" s="23" t="s">
+        <v>431</v>
       </c>
       <c r="F237" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G237" s="3"/>
-      <c r="H237" s="15" t="s">
-        <v>285</v>
-      </c>
+      <c r="H237" s="15"/>
       <c r="I237" s="3"/>
       <c r="J237" s="1"/>
       <c r="K237" s="1"/>
@@ -11223,16 +11214,16 @@
     <row r="238" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A238" s="58"/>
       <c r="B238" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C238" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E238" s="23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F238" s="26" t="s">
         <v>22</v>
@@ -11263,16 +11254,16 @@
         <v>0</v>
       </c>
       <c r="C239" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="E239" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="F239" s="26" t="s">
-        <v>22</v>
+        <v>416</v>
+      </c>
+      <c r="F239" s="52" t="s">
+        <v>53</v>
       </c>
       <c r="G239" s="3"/>
       <c r="H239" s="15"/>
@@ -11300,19 +11291,21 @@
         <v>0</v>
       </c>
       <c r="C240" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="E240" s="23" t="s">
-        <v>416</v>
-      </c>
-      <c r="F240" s="52" t="s">
-        <v>53</v>
+        <v>286</v>
+      </c>
+      <c r="E240" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="F240" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="G240" s="3"/>
-      <c r="H240" s="15"/>
+      <c r="H240" s="15" t="s">
+        <v>288</v>
+      </c>
       <c r="I240" s="3"/>
       <c r="J240" s="1"/>
       <c r="K240" s="1"/>
@@ -11337,21 +11330,19 @@
         <v>0</v>
       </c>
       <c r="C241" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E241" s="18" t="s">
-        <v>287</v>
+        <v>408</v>
+      </c>
+      <c r="E241" s="23" t="s">
+        <v>409</v>
       </c>
       <c r="F241" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G241" s="3"/>
-      <c r="H241" s="15" t="s">
-        <v>288</v>
-      </c>
+      <c r="H241" s="15"/>
       <c r="I241" s="3"/>
       <c r="J241" s="1"/>
       <c r="K241" s="1"/>
@@ -11373,22 +11364,24 @@
     <row r="242" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A242" s="58"/>
       <c r="B242" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C242" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E242" s="23" t="s">
-        <v>409</v>
+        <v>289</v>
+      </c>
+      <c r="E242" s="18" t="s">
+        <v>290</v>
       </c>
       <c r="F242" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G242" s="3"/>
-      <c r="H242" s="15"/>
+      <c r="H242" s="15" t="s">
+        <v>291</v>
+      </c>
       <c r="I242" s="3"/>
       <c r="J242" s="1"/>
       <c r="K242" s="1"/>
@@ -11407,26 +11400,26 @@
       <c r="X242" s="1"/>
       <c r="Y242" s="1"/>
     </row>
-    <row r="243" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A243" s="58"/>
       <c r="B243" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C243" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E243" s="18" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F243" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G243" s="3"/>
-      <c r="H243" s="15" t="s">
-        <v>291</v>
+      <c r="H243" s="16" t="s">
+        <v>294</v>
       </c>
       <c r="I243" s="3"/>
       <c r="J243" s="1"/>
@@ -11452,20 +11445,20 @@
         <v>0</v>
       </c>
       <c r="C244" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>292</v>
+        <v>410</v>
       </c>
       <c r="E244" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="F244" s="26" t="s">
-        <v>22</v>
+        <v>295</v>
+      </c>
+      <c r="F244" s="28" t="s">
+        <v>53</v>
       </c>
       <c r="G244" s="3"/>
       <c r="H244" s="16" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I244" s="3"/>
       <c r="J244" s="1"/>
@@ -11491,15 +11484,15 @@
         <v>0</v>
       </c>
       <c r="C245" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E245" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="F245" s="52" t="s">
+        <v>446</v>
+      </c>
+      <c r="F245" s="28" t="s">
         <v>53</v>
       </c>
       <c r="G245" s="3"/>
@@ -11528,20 +11521,20 @@
         <v>0</v>
       </c>
       <c r="C246" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>410</v>
+        <v>297</v>
       </c>
       <c r="E246" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F246" s="28" t="s">
         <v>53</v>
       </c>
       <c r="G246" s="3"/>
       <c r="H246" s="16" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I246" s="3"/>
       <c r="J246" s="1"/>
@@ -11561,25 +11554,27 @@
       <c r="X246" s="1"/>
       <c r="Y246" s="1"/>
     </row>
-    <row r="247" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A247" s="58"/>
       <c r="B247" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C247" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E247" s="23" t="s">
-        <v>446</v>
+        <v>300</v>
+      </c>
+      <c r="E247" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="F247" s="28" t="s">
         <v>53</v>
       </c>
       <c r="G247" s="3"/>
-      <c r="H247" s="16"/>
+      <c r="H247" s="15" t="s">
+        <v>301</v>
+      </c>
       <c r="I247" s="3"/>
       <c r="J247" s="1"/>
       <c r="K247" s="1"/>
@@ -11599,26 +11594,24 @@
       <c r="Y247" s="1"/>
     </row>
     <row r="248" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A248" s="58"/>
+      <c r="A248" s="1"/>
       <c r="B248" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C248" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E248" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="F248" s="28" t="s">
-        <v>53</v>
+        <v>360</v>
+      </c>
+      <c r="E248" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="F248" s="47" t="s">
+        <v>10</v>
       </c>
       <c r="G248" s="3"/>
-      <c r="H248" s="16" t="s">
-        <v>299</v>
-      </c>
+      <c r="H248" s="4"/>
       <c r="I248" s="3"/>
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
@@ -11637,27 +11630,15 @@
       <c r="X248" s="1"/>
       <c r="Y248" s="1"/>
     </row>
-    <row r="249" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A249" s="58"/>
-      <c r="B249" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C249" s="2">
-        <v>37</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E249" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="F249" s="28" t="s">
-        <v>53</v>
-      </c>
+    <row r="249" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A249" s="1"/>
+      <c r="B249" s="56"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="3"/>
+      <c r="F249" s="1"/>
       <c r="G249" s="3"/>
-      <c r="H249" s="15" t="s">
-        <v>301</v>
-      </c>
+      <c r="H249" s="4"/>
       <c r="I249" s="3"/>
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
@@ -11678,21 +11659,11 @@
     </row>
     <row r="250" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1"/>
-      <c r="B250" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C250" s="2">
-        <v>38</v>
-      </c>
-      <c r="D250" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="E250" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="F250" s="47" t="s">
-        <v>10</v>
-      </c>
+      <c r="B250" s="56"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
+      <c r="E250" s="3"/>
+      <c r="F250" s="1"/>
       <c r="G250" s="3"/>
       <c r="H250" s="4"/>
       <c r="I250" s="3"/>
@@ -11713,15 +11684,29 @@
       <c r="X250" s="1"/>
       <c r="Y250" s="1"/>
     </row>
-    <row r="251" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A251" s="1"/>
-      <c r="B251" s="56"/>
-      <c r="C251" s="1"/>
-      <c r="D251" s="1"/>
-      <c r="E251" s="3"/>
-      <c r="F251" s="1"/>
+    <row r="251" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+      <c r="A251" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="B251" s="50" t="b">
+        <v>1</v>
+      </c>
+      <c r="C251" s="2">
+        <v>1</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E251" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F251" s="27" t="s">
+        <v>10</v>
+      </c>
       <c r="G251" s="3"/>
-      <c r="H251" s="4"/>
+      <c r="H251" s="15" t="s">
+        <v>304</v>
+      </c>
       <c r="I251" s="3"/>
       <c r="J251" s="1"/>
       <c r="K251" s="1"/>
@@ -11740,15 +11725,25 @@
       <c r="X251" s="1"/>
       <c r="Y251" s="1"/>
     </row>
-    <row r="252" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A252" s="1"/>
-      <c r="B252" s="56"/>
-      <c r="C252" s="1"/>
-      <c r="D252" s="1"/>
-      <c r="E252" s="3"/>
-      <c r="F252" s="1"/>
+    <row r="252" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+      <c r="A252" s="67"/>
+      <c r="B252" s="50" t="b">
+        <v>1</v>
+      </c>
+      <c r="C252" s="2">
+        <v>2</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E252" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F252" s="27" t="s">
+        <v>10</v>
+      </c>
       <c r="G252" s="3"/>
-      <c r="H252" s="4"/>
+      <c r="H252" s="15"/>
       <c r="I252" s="3"/>
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
@@ -11768,28 +11763,24 @@
       <c r="Y252" s="1"/>
     </row>
     <row r="253" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A253" s="67" t="s">
-        <v>302</v>
-      </c>
+      <c r="A253" s="67"/>
       <c r="B253" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C253" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E253" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="E253" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F253" s="27" t="s">
         <v>10</v>
       </c>
       <c r="G253" s="3"/>
-      <c r="H253" s="15" t="s">
-        <v>304</v>
-      </c>
+      <c r="H253" s="15"/>
       <c r="I253" s="3"/>
       <c r="J253" s="1"/>
       <c r="K253" s="1"/>
@@ -11814,16 +11805,16 @@
         <v>1</v>
       </c>
       <c r="C254" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>449</v>
+        <v>484</v>
       </c>
       <c r="E254" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F254" s="27" t="s">
-        <v>10</v>
+      <c r="F254" s="54" t="s">
+        <v>22</v>
       </c>
       <c r="G254" s="3"/>
       <c r="H254" s="15"/>
@@ -11851,16 +11842,16 @@
         <v>1</v>
       </c>
       <c r="C255" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="E255" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F255" s="27" t="s">
-        <v>10</v>
+      <c r="F255" s="54" t="s">
+        <v>22</v>
       </c>
       <c r="G255" s="3"/>
       <c r="H255" s="15"/>
@@ -11888,10 +11879,10 @@
         <v>1</v>
       </c>
       <c r="C256" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E256" s="21" t="s">
         <v>9</v>
@@ -11925,10 +11916,10 @@
         <v>1</v>
       </c>
       <c r="C257" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E257" s="21" t="s">
         <v>9</v>
@@ -11962,10 +11953,10 @@
         <v>1</v>
       </c>
       <c r="C258" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E258" s="21" t="s">
         <v>9</v>
@@ -11999,10 +11990,10 @@
         <v>1</v>
       </c>
       <c r="C259" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E259" s="21" t="s">
         <v>9</v>
@@ -12036,7 +12027,7 @@
         <v>1</v>
       </c>
       <c r="C260" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>491</v>
@@ -12073,10 +12064,10 @@
         <v>1</v>
       </c>
       <c r="C261" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E261" s="21" t="s">
         <v>9</v>
@@ -12110,16 +12101,16 @@
         <v>1</v>
       </c>
       <c r="C262" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E262" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F262" s="54" t="s">
-        <v>22</v>
+      <c r="F262" s="55" t="s">
+        <v>53</v>
       </c>
       <c r="G262" s="3"/>
       <c r="H262" s="15"/>
@@ -12142,24 +12133,26 @@
       <c r="Y262" s="1"/>
     </row>
     <row r="263" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A263" s="67"/>
+      <c r="A263" s="58"/>
       <c r="B263" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C263" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="E263" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="E263" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F263" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G263" s="3"/>
-      <c r="H263" s="15"/>
+      <c r="H263" s="15" t="s">
+        <v>306</v>
+      </c>
       <c r="I263" s="3"/>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
@@ -12178,25 +12171,27 @@
       <c r="X263" s="1"/>
       <c r="Y263" s="1"/>
     </row>
-    <row r="264" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A264" s="67"/>
+    <row r="264" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A264" s="58"/>
       <c r="B264" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C264" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="E264" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="E264" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="F264" s="55" t="s">
-        <v>53</v>
+      <c r="F264" s="54" t="s">
+        <v>22</v>
       </c>
       <c r="G264" s="3"/>
-      <c r="H264" s="15"/>
+      <c r="H264" s="16" t="s">
+        <v>308</v>
+      </c>
       <c r="I264" s="3"/>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -12215,26 +12210,26 @@
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
     </row>
-    <row r="265" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A265" s="58"/>
       <c r="B265" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C265" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E265" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E265" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F265" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G265" s="3"/>
-      <c r="H265" s="15" t="s">
-        <v>306</v>
+      <c r="H265" s="16" t="s">
+        <v>310</v>
       </c>
       <c r="I265" s="3"/>
       <c r="J265" s="1"/>
@@ -12260,21 +12255,19 @@
         <v>1</v>
       </c>
       <c r="C266" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E266" s="46" t="s">
+        <v>495</v>
+      </c>
+      <c r="E266" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F266" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G266" s="3"/>
-      <c r="H266" s="16" t="s">
-        <v>308</v>
-      </c>
+      <c r="H266" s="16"/>
       <c r="I266" s="3"/>
       <c r="J266" s="1"/>
       <c r="K266" s="1"/>
@@ -12293,26 +12286,26 @@
       <c r="X266" s="1"/>
       <c r="Y266" s="1"/>
     </row>
-    <row r="267" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A267" s="58"/>
       <c r="B267" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C267" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E267" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="E267" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F267" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G267" s="3"/>
-      <c r="H267" s="16" t="s">
-        <v>310</v>
+      <c r="H267" s="15" t="s">
+        <v>312</v>
       </c>
       <c r="I267" s="3"/>
       <c r="J267" s="1"/>
@@ -12332,25 +12325,27 @@
       <c r="X267" s="1"/>
       <c r="Y267" s="1"/>
     </row>
-    <row r="268" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A268" s="58"/>
       <c r="B268" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C268" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="E268" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E268" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F268" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G268" s="3"/>
-      <c r="H268" s="16"/>
+      <c r="H268" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I268" s="3"/>
       <c r="J268" s="1"/>
       <c r="K268" s="1"/>
@@ -12375,21 +12370,19 @@
         <v>1</v>
       </c>
       <c r="C269" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E269" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="E269" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F269" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G269" s="3"/>
-      <c r="H269" s="15" t="s">
-        <v>312</v>
-      </c>
+      <c r="H269" s="15"/>
       <c r="I269" s="3"/>
       <c r="J269" s="1"/>
       <c r="K269" s="1"/>
@@ -12414,10 +12407,10 @@
         <v>1</v>
       </c>
       <c r="C270" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>313</v>
+        <v>496</v>
       </c>
       <c r="E270" s="8" t="s">
         <v>9</v>
@@ -12427,7 +12420,7 @@
       </c>
       <c r="G270" s="3"/>
       <c r="H270" s="15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I270" s="3"/>
       <c r="J270" s="1"/>
@@ -12447,25 +12440,27 @@
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
     </row>
-    <row r="271" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="58"/>
       <c r="B271" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C271" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E271" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="E271" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F271" s="54" t="s">
+      <c r="F271" s="55" t="s">
         <v>22</v>
       </c>
       <c r="G271" s="3"/>
-      <c r="H271" s="15"/>
+      <c r="H271" s="16" t="s">
+        <v>318</v>
+      </c>
       <c r="I271" s="3"/>
       <c r="J271" s="1"/>
       <c r="K271" s="1"/>
@@ -12487,13 +12482,13 @@
     <row r="272" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A272" s="58"/>
       <c r="B272" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C272" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>500</v>
+        <v>319</v>
       </c>
       <c r="E272" s="8" t="s">
         <v>9</v>
@@ -12503,7 +12498,7 @@
       </c>
       <c r="G272" s="3"/>
       <c r="H272" s="15" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I272" s="3"/>
       <c r="J272" s="1"/>
@@ -12523,26 +12518,26 @@
       <c r="X272" s="1"/>
       <c r="Y272" s="1"/>
     </row>
-    <row r="273" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A273" s="58"/>
       <c r="B273" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C273" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E273" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F273" s="55" t="s">
+      <c r="F273" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G273" s="3"/>
-      <c r="H273" s="16" t="s">
-        <v>318</v>
+      <c r="H273" s="15" t="s">
+        <v>322</v>
       </c>
       <c r="I273" s="3"/>
       <c r="J273" s="1"/>
@@ -12562,16 +12557,16 @@
       <c r="X273" s="1"/>
       <c r="Y273" s="1"/>
     </row>
-    <row r="274" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A274" s="58"/>
       <c r="B274" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C274" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E274" s="8" t="s">
         <v>9</v>
@@ -12580,8 +12575,8 @@
         <v>22</v>
       </c>
       <c r="G274" s="3"/>
-      <c r="H274" s="15" t="s">
-        <v>320</v>
+      <c r="H274" s="16" t="s">
+        <v>324</v>
       </c>
       <c r="I274" s="3"/>
       <c r="J274" s="1"/>
@@ -12607,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="C275" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E275" s="8" t="s">
         <v>9</v>
@@ -12620,7 +12615,7 @@
       </c>
       <c r="G275" s="3"/>
       <c r="H275" s="15" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I275" s="3"/>
       <c r="J275" s="1"/>
@@ -12640,16 +12635,16 @@
       <c r="X275" s="1"/>
       <c r="Y275" s="1"/>
     </row>
-    <row r="276" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A276" s="58"/>
       <c r="B276" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C276" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E276" s="8" t="s">
         <v>9</v>
@@ -12658,8 +12653,8 @@
         <v>22</v>
       </c>
       <c r="G276" s="3"/>
-      <c r="H276" s="16" t="s">
-        <v>324</v>
+      <c r="H276" s="15" t="s">
+        <v>328</v>
       </c>
       <c r="I276" s="3"/>
       <c r="J276" s="1"/>
@@ -12682,13 +12677,13 @@
     <row r="277" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A277" s="58"/>
       <c r="B277" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C277" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E277" s="8" t="s">
         <v>9</v>
@@ -12698,7 +12693,7 @@
       </c>
       <c r="G277" s="3"/>
       <c r="H277" s="15" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I277" s="3"/>
       <c r="J277" s="1"/>
@@ -12718,16 +12713,16 @@
       <c r="X277" s="1"/>
       <c r="Y277" s="1"/>
     </row>
-    <row r="278" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A278" s="58"/>
       <c r="B278" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C278" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E278" s="8" t="s">
         <v>9</v>
@@ -12736,8 +12731,8 @@
         <v>22</v>
       </c>
       <c r="G278" s="3"/>
-      <c r="H278" s="15" t="s">
-        <v>328</v>
+      <c r="H278" s="16" t="s">
+        <v>332</v>
       </c>
       <c r="I278" s="3"/>
       <c r="J278" s="1"/>
@@ -12757,27 +12752,25 @@
       <c r="X278" s="1"/>
       <c r="Y278" s="1"/>
     </row>
-    <row r="279" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="58"/>
       <c r="B279" s="50" t="b">
         <v>1</v>
       </c>
       <c r="C279" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="E279" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="E279" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F279" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G279" s="3"/>
-      <c r="H279" s="15" t="s">
-        <v>330</v>
-      </c>
+      <c r="H279" s="16"/>
       <c r="I279" s="3"/>
       <c r="J279" s="1"/>
       <c r="K279" s="1"/>
@@ -12799,24 +12792,22 @@
     <row r="280" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="58"/>
       <c r="B280" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C280" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E280" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="E280" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F280" s="54" t="s">
         <v>22</v>
       </c>
       <c r="G280" s="3"/>
-      <c r="H280" s="16" t="s">
-        <v>332</v>
-      </c>
+      <c r="H280" s="16"/>
       <c r="I280" s="3"/>
       <c r="J280" s="1"/>
       <c r="K280" s="1"/>
@@ -12841,10 +12832,10 @@
         <v>1</v>
       </c>
       <c r="C281" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="E281" s="21" t="s">
         <v>9</v>
@@ -12878,16 +12869,16 @@
         <v>1</v>
       </c>
       <c r="C282" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E282" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F282" s="54" t="s">
-        <v>22</v>
+      <c r="F282" s="55" t="s">
+        <v>53</v>
       </c>
       <c r="G282" s="3"/>
       <c r="H282" s="16"/>
@@ -12915,16 +12906,16 @@
         <v>1</v>
       </c>
       <c r="C283" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E283" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F283" s="54" t="s">
-        <v>22</v>
+      <c r="F283" s="55" t="s">
+        <v>53</v>
       </c>
       <c r="G283" s="3"/>
       <c r="H283" s="16"/>
@@ -12949,13 +12940,11 @@
     <row r="284" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="58"/>
       <c r="B284" s="50" t="b">
-        <v>1</v>
-      </c>
-      <c r="C284" s="2">
-        <v>32</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C284" s="2"/>
       <c r="D284" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E284" s="21" t="s">
         <v>9</v>
@@ -12988,11 +12977,9 @@
       <c r="B285" s="50" t="b">
         <v>1</v>
       </c>
-      <c r="C285" s="2">
-        <v>33</v>
-      </c>
+      <c r="C285" s="2"/>
       <c r="D285" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E285" s="21" t="s">
         <v>9</v>
@@ -13023,18 +13010,24 @@
     <row r="286" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="58"/>
       <c r="B286" s="50" t="b">
-        <v>1</v>
-      </c>
-      <c r="C286" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="C286" s="2">
+        <v>34</v>
+      </c>
       <c r="D286" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E286" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="E286" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F286" s="55"/>
+      <c r="F286" s="55" t="s">
+        <v>53</v>
+      </c>
       <c r="G286" s="3"/>
-      <c r="H286" s="16"/>
+      <c r="H286" s="16" t="s">
+        <v>334</v>
+      </c>
       <c r="I286" s="3"/>
       <c r="J286" s="1"/>
       <c r="K286" s="1"/>
@@ -13059,10 +13052,10 @@
         <v>0</v>
       </c>
       <c r="C287" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E287" s="8" t="s">
         <v>9</v>
@@ -13072,7 +13065,7 @@
       </c>
       <c r="G287" s="3"/>
       <c r="H287" s="16" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I287" s="3"/>
       <c r="J287" s="1"/>
@@ -13098,10 +13091,10 @@
         <v>0</v>
       </c>
       <c r="C288" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E288" s="8" t="s">
         <v>9</v>
@@ -13111,7 +13104,7 @@
       </c>
       <c r="G288" s="3"/>
       <c r="H288" s="16" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I288" s="3"/>
       <c r="J288" s="1"/>
@@ -13131,16 +13124,16 @@
       <c r="X288" s="1"/>
       <c r="Y288" s="1"/>
     </row>
-    <row r="289" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A289" s="58"/>
       <c r="B289" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C289" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E289" s="8" t="s">
         <v>9</v>
@@ -13149,8 +13142,8 @@
         <v>53</v>
       </c>
       <c r="G289" s="3"/>
-      <c r="H289" s="16" t="s">
-        <v>338</v>
+      <c r="H289" s="15" t="s">
+        <v>340</v>
       </c>
       <c r="I289" s="3"/>
       <c r="J289" s="1"/>
@@ -13176,10 +13169,10 @@
         <v>0</v>
       </c>
       <c r="C290" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E290" s="8" t="s">
         <v>9</v>
@@ -13189,7 +13182,7 @@
       </c>
       <c r="G290" s="3"/>
       <c r="H290" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I290" s="3"/>
       <c r="J290" s="1"/>
@@ -13209,16 +13202,16 @@
       <c r="X290" s="1"/>
       <c r="Y290" s="1"/>
     </row>
-    <row r="291" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="58"/>
       <c r="B291" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C291" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E291" s="8" t="s">
         <v>9</v>
@@ -13227,8 +13220,8 @@
         <v>53</v>
       </c>
       <c r="G291" s="3"/>
-      <c r="H291" s="15" t="s">
-        <v>342</v>
+      <c r="H291" s="16" t="s">
+        <v>344</v>
       </c>
       <c r="I291" s="3"/>
       <c r="J291" s="1"/>
@@ -13248,27 +13241,15 @@
       <c r="X291" s="1"/>
       <c r="Y291" s="1"/>
     </row>
-    <row r="292" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A292" s="58"/>
-      <c r="B292" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C292" s="2">
-        <v>39</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="E292" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F292" s="28" t="s">
-        <v>53</v>
-      </c>
+    <row r="292" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A292" s="1"/>
+      <c r="B292" s="1"/>
+      <c r="C292" s="2"/>
+      <c r="D292" s="1"/>
+      <c r="E292" s="3"/>
+      <c r="F292" s="1"/>
       <c r="G292" s="3"/>
-      <c r="H292" s="16" t="s">
-        <v>344</v>
-      </c>
+      <c r="H292" s="4"/>
       <c r="I292" s="3"/>
       <c r="J292" s="1"/>
       <c r="K292" s="1"/>
@@ -13314,15 +13295,29 @@
       <c r="X293" s="1"/>
       <c r="Y293" s="1"/>
     </row>
-    <row r="294" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A294" s="1"/>
-      <c r="B294" s="1"/>
-      <c r="C294" s="2"/>
-      <c r="D294" s="1"/>
-      <c r="E294" s="3"/>
-      <c r="F294" s="1"/>
+    <row r="294" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A294" s="67" t="s">
+        <v>345</v>
+      </c>
+      <c r="B294" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="C294" s="2">
+        <v>1</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E294" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F294" s="27" t="s">
+        <v>10</v>
+      </c>
       <c r="G294" s="3"/>
-      <c r="H294" s="4"/>
+      <c r="H294" s="16" t="s">
+        <v>347</v>
+      </c>
       <c r="I294" s="3"/>
       <c r="J294" s="1"/>
       <c r="K294" s="1"/>
@@ -13341,28 +13336,26 @@
       <c r="X294" s="1"/>
       <c r="Y294" s="1"/>
     </row>
-    <row r="295" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A295" s="67" t="s">
-        <v>345</v>
-      </c>
+    <row r="295" spans="1:25" ht="15" x14ac:dyDescent="0.35">
+      <c r="A295" s="58"/>
       <c r="B295" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C295" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E295" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="E295" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F295" s="27" t="s">
-        <v>10</v>
+      <c r="F295" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="G295" s="3"/>
-      <c r="H295" s="16" t="s">
-        <v>347</v>
+      <c r="H295" s="15" t="s">
+        <v>349</v>
       </c>
       <c r="I295" s="3"/>
       <c r="J295" s="1"/>
@@ -13388,10 +13381,10 @@
         <v>0</v>
       </c>
       <c r="C296" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E296" s="8" t="s">
         <v>9</v>
@@ -13401,7 +13394,7 @@
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I296" s="3"/>
       <c r="J296" s="1"/>
@@ -13427,10 +13420,10 @@
         <v>0</v>
       </c>
       <c r="C297" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E297" s="8" t="s">
         <v>9</v>
@@ -13440,7 +13433,7 @@
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I297" s="3"/>
       <c r="J297" s="1"/>
@@ -13466,10 +13459,10 @@
         <v>0</v>
       </c>
       <c r="C298" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E298" s="8" t="s">
         <v>9</v>
@@ -13478,8 +13471,8 @@
         <v>22</v>
       </c>
       <c r="G298" s="3"/>
-      <c r="H298" s="15" t="s">
-        <v>353</v>
+      <c r="H298" s="20" t="s">
+        <v>355</v>
       </c>
       <c r="I298" s="3"/>
       <c r="J298" s="1"/>
@@ -13505,20 +13498,20 @@
         <v>0</v>
       </c>
       <c r="C299" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E299" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F299" s="26" t="s">
-        <v>22</v>
+      <c r="F299" s="28" t="s">
+        <v>53</v>
       </c>
       <c r="G299" s="3"/>
-      <c r="H299" s="20" t="s">
-        <v>355</v>
+      <c r="H299" s="15" t="s">
+        <v>357</v>
       </c>
       <c r="I299" s="3"/>
       <c r="J299" s="1"/>
@@ -13538,27 +13531,17 @@
       <c r="X299" s="1"/>
       <c r="Y299" s="1"/>
     </row>
-    <row r="300" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A300" s="58"/>
+    <row r="300" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A300" s="1"/>
       <c r="B300" s="50" t="b">
         <v>0</v>
       </c>
-      <c r="C300" s="2">
-        <v>6</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E300" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F300" s="28" t="s">
-        <v>53</v>
-      </c>
+      <c r="C300" s="2"/>
+      <c r="D300" s="1"/>
+      <c r="E300" s="3"/>
+      <c r="F300" s="1"/>
       <c r="G300" s="3"/>
-      <c r="H300" s="15" t="s">
-        <v>357</v>
-      </c>
+      <c r="H300" s="4"/>
       <c r="I300" s="3"/>
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
@@ -13607,14 +13590,24 @@
       <c r="Y301" s="1"/>
     </row>
     <row r="302" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A302" s="1"/>
+      <c r="A302" s="64" t="s">
+        <v>391</v>
+      </c>
       <c r="B302" s="50" t="b">
         <v>0</v>
       </c>
-      <c r="C302" s="2"/>
-      <c r="D302" s="1"/>
-      <c r="E302" s="3"/>
-      <c r="F302" s="1"/>
+      <c r="C302" s="2">
+        <v>1</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E302" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F302" s="40" t="s">
+        <v>400</v>
+      </c>
       <c r="G302" s="3"/>
       <c r="H302" s="4"/>
       <c r="I302" s="3"/>
@@ -13636,17 +13629,15 @@
       <c r="Y302" s="1"/>
     </row>
     <row r="303" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A303" s="64" t="s">
-        <v>391</v>
-      </c>
+      <c r="A303" s="58"/>
       <c r="B303" s="50" t="b">
         <v>0</v>
       </c>
       <c r="C303" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E303" s="21" t="s">
         <v>9</v>
@@ -13680,10 +13671,10 @@
         <v>0</v>
       </c>
       <c r="C304" s="2">
-        <v>2</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>402</v>
+        <v>3</v>
+      </c>
+      <c r="D304" s="24" t="s">
+        <v>404</v>
       </c>
       <c r="E304" s="21" t="s">
         <v>9</v>
@@ -13717,10 +13708,10 @@
         <v>0</v>
       </c>
       <c r="C305" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D305" s="24" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E305" s="21" t="s">
         <v>9</v>
@@ -13751,13 +13742,13 @@
     <row r="306" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="58"/>
       <c r="B306" s="50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C306" s="2">
-        <v>4</v>
-      </c>
-      <c r="D306" s="24" t="s">
-        <v>405</v>
+        <v>5</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="E306" s="21" t="s">
         <v>9</v>
@@ -13788,20 +13779,18 @@
     <row r="307" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="58"/>
       <c r="B307" s="50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C307" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="E307" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F307" s="40" t="s">
-        <v>400</v>
-      </c>
+      <c r="F307" s="1"/>
       <c r="G307" s="3"/>
       <c r="H307" s="4"/>
       <c r="I307" s="3"/>
@@ -13828,14 +13817,10 @@
         <v>0</v>
       </c>
       <c r="C308" s="2">
-        <v>6</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="E308" s="21" t="s">
-        <v>9</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D308" s="1"/>
+      <c r="E308" s="3"/>
       <c r="F308" s="1"/>
       <c r="G308" s="3"/>
       <c r="H308" s="4"/>
@@ -13863,7 +13848,7 @@
         <v>0</v>
       </c>
       <c r="C309" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D309" s="1"/>
       <c r="E309" s="3"/>
@@ -13894,7 +13879,7 @@
         <v>0</v>
       </c>
       <c r="C310" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D310" s="1"/>
       <c r="E310" s="3"/>
@@ -13925,7 +13910,7 @@
         <v>0</v>
       </c>
       <c r="C311" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D311" s="1"/>
       <c r="E311" s="3"/>
@@ -13956,7 +13941,7 @@
         <v>0</v>
       </c>
       <c r="C312" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D312" s="1"/>
       <c r="E312" s="3"/>
@@ -13987,7 +13972,7 @@
         <v>0</v>
       </c>
       <c r="C313" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D313" s="1"/>
       <c r="E313" s="3"/>
@@ -14018,7 +14003,7 @@
         <v>0</v>
       </c>
       <c r="C314" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D314" s="1"/>
       <c r="E314" s="3"/>
@@ -14049,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="C315" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D315" s="1"/>
       <c r="E315" s="3"/>
@@ -14080,7 +14065,7 @@
         <v>0</v>
       </c>
       <c r="C316" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D316" s="1"/>
       <c r="E316" s="3"/>
@@ -14105,14 +14090,10 @@
       <c r="X316" s="1"/>
       <c r="Y316" s="1"/>
     </row>
-    <row r="317" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A317" s="58"/>
-      <c r="B317" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C317" s="2">
-        <v>15</v>
-      </c>
+      <c r="B317" s="1"/>
+      <c r="C317" s="2"/>
       <c r="D317" s="1"/>
       <c r="E317" s="3"/>
       <c r="F317" s="1"/>
@@ -14245,7 +14226,7 @@
       <c r="Y321" s="1"/>
     </row>
     <row r="322" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A322" s="58"/>
+      <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="2"/>
       <c r="D322" s="1"/>
@@ -34710,50 +34691,23 @@
       <c r="X1079" s="1"/>
       <c r="Y1079" s="1"/>
     </row>
-    <row r="1080" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1080" s="1"/>
-      <c r="B1080" s="1"/>
-      <c r="C1080" s="2"/>
-      <c r="D1080" s="1"/>
-      <c r="E1080" s="3"/>
-      <c r="F1080" s="1"/>
-      <c r="G1080" s="3"/>
-      <c r="H1080" s="4"/>
-      <c r="I1080" s="3"/>
-      <c r="J1080" s="1"/>
-      <c r="K1080" s="1"/>
-      <c r="L1080" s="1"/>
-      <c r="M1080" s="1"/>
-      <c r="N1080" s="1"/>
-      <c r="O1080" s="1"/>
-      <c r="P1080" s="1"/>
-      <c r="Q1080" s="1"/>
-      <c r="R1080" s="1"/>
-      <c r="S1080" s="1"/>
-      <c r="T1080" s="1"/>
-      <c r="U1080" s="1"/>
-      <c r="V1080" s="1"/>
-      <c r="W1080" s="1"/>
-      <c r="X1080" s="1"/>
-      <c r="Y1080" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="A6:A48"/>
     <mergeCell ref="A53:A69"/>
-    <mergeCell ref="A303:A322"/>
+    <mergeCell ref="A302:A321"/>
     <mergeCell ref="A74:A91"/>
     <mergeCell ref="A96:A109"/>
-    <mergeCell ref="A253:A292"/>
-    <mergeCell ref="A295:A300"/>
+    <mergeCell ref="A251:A291"/>
+    <mergeCell ref="A294:A299"/>
     <mergeCell ref="A112:A129"/>
     <mergeCell ref="A132:A148"/>
     <mergeCell ref="A151:A178"/>
     <mergeCell ref="A182:A194"/>
     <mergeCell ref="A197:A202"/>
     <mergeCell ref="A205:A209"/>
-    <mergeCell ref="A212:A249"/>
+    <mergeCell ref="A212:A247"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E53" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
@@ -34925,38 +34879,38 @@
     <hyperlink ref="E231" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
     <hyperlink ref="E232" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
     <hyperlink ref="E233" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="E237" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="E241" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="E243" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="E244" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="E246" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="E248" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="E249" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="E266" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="E269" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="E270" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="E272" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="E273" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="E274" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="E275" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="E276" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="E277" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="E278" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="E279" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="E280" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="E287" r:id="rId189" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="E288" r:id="rId190" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="E289" r:id="rId191" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="E290" r:id="rId192" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="E291" r:id="rId193" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="E292" r:id="rId194" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="E295" r:id="rId195" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="E296" r:id="rId196" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="E297" r:id="rId197" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="E298" r:id="rId198" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="E299" r:id="rId199" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="E300" r:id="rId200" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="E250" r:id="rId201" xr:uid="{38535620-DA2F-45B6-BE53-7BE35BAD917E}"/>
+    <hyperlink ref="E236" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="E240" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="E242" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="E243" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="E244" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="E246" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="E247" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="E264" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="E267" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="E268" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="E270" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="E271" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="E272" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="E273" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="E274" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="E275" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="E276" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="E277" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="E278" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="E286" r:id="rId189" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="E287" r:id="rId190" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="E288" r:id="rId191" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="E289" r:id="rId192" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="E290" r:id="rId193" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="E291" r:id="rId194" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="E294" r:id="rId195" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="E295" r:id="rId196" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="E296" r:id="rId197" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="E297" r:id="rId198" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="E298" r:id="rId199" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="E299" r:id="rId200" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="E248" r:id="rId201" xr:uid="{38535620-DA2F-45B6-BE53-7BE35BAD917E}"/>
     <hyperlink ref="E180" r:id="rId202" xr:uid="{52A62708-7A1B-4947-8125-51CD78E69CDC}"/>
     <hyperlink ref="E179" r:id="rId203" xr:uid="{90A2CCC4-C963-4688-BF93-898F1AB744EB}"/>
     <hyperlink ref="G104" r:id="rId204" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
@@ -35010,19 +34964,19 @@
     <hyperlink ref="E10" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="G7" r:id="rId253" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="E7" r:id="rId254" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E303" r:id="rId255" xr:uid="{49C446A4-86D9-438E-8C85-C2CBF2D0C601}"/>
+    <hyperlink ref="E302" r:id="rId255" xr:uid="{49C446A4-86D9-438E-8C85-C2CBF2D0C601}"/>
     <hyperlink ref="E29" r:id="rId256" xr:uid="{15B4076B-7C29-451C-A0E0-E0CDB84955C7}"/>
-    <hyperlink ref="E304" r:id="rId257" xr:uid="{5897208F-5F6C-4E1B-8B0F-03D62428448A}"/>
+    <hyperlink ref="E303" r:id="rId257" xr:uid="{5897208F-5F6C-4E1B-8B0F-03D62428448A}"/>
     <hyperlink ref="E41" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
     <hyperlink ref="E15" r:id="rId259" xr:uid="{36657CEA-F972-477D-AC24-77B031A0C947}"/>
-    <hyperlink ref="E305" r:id="rId260" xr:uid="{0B318E6F-5375-45A5-A623-A5D070F4F786}"/>
-    <hyperlink ref="E306" r:id="rId261" xr:uid="{28A35100-95C6-4598-8EAE-4903F97A507B}"/>
+    <hyperlink ref="E304" r:id="rId260" xr:uid="{0B318E6F-5375-45A5-A623-A5D070F4F786}"/>
+    <hyperlink ref="E305" r:id="rId261" xr:uid="{28A35100-95C6-4598-8EAE-4903F97A507B}"/>
     <hyperlink ref="E32" r:id="rId262" xr:uid="{A642EB9F-9B4D-467C-AA82-CE1A728B251C}"/>
     <hyperlink ref="E27" r:id="rId263" xr:uid="{A1884A7B-6025-4BC0-B0A7-10DF9BA889E7}"/>
-    <hyperlink ref="E242" r:id="rId264" xr:uid="{DD148482-9331-495D-A315-B2667528DE27}"/>
+    <hyperlink ref="E241" r:id="rId264" xr:uid="{DD148482-9331-495D-A315-B2667528DE27}"/>
     <hyperlink ref="E234" r:id="rId265" xr:uid="{9AFBA357-2FAE-42C6-BAC6-9567300CA7EB}"/>
     <hyperlink ref="E213" r:id="rId266" xr:uid="{222EEF32-42E7-41DB-92A2-B7E1E19CBDFD}"/>
-    <hyperlink ref="E240" r:id="rId267" xr:uid="{7EFFF805-CE73-433D-8429-8C55CEC7C072}"/>
+    <hyperlink ref="E239" r:id="rId267" xr:uid="{7EFFF805-CE73-433D-8429-8C55CEC7C072}"/>
     <hyperlink ref="E139" r:id="rId268" xr:uid="{397DA75B-3BBC-4F89-A9DA-27EB8A53151E}"/>
     <hyperlink ref="E143" r:id="rId269" xr:uid="{ACEE0CD9-D250-46A6-9BEB-25465E3F5877}"/>
     <hyperlink ref="E142" r:id="rId270" xr:uid="{726ABE82-32B2-45DF-86E4-D4B65D08B99B}"/>
@@ -35037,9 +34991,9 @@
     <hyperlink ref="E81" r:id="rId279" xr:uid="{27F80336-44DE-477D-A42B-75FF0BEAEB14}"/>
     <hyperlink ref="E80" r:id="rId280" xr:uid="{CBD0C4A3-4F0E-49C4-B907-E32F28123DAA}"/>
     <hyperlink ref="E82" r:id="rId281" xr:uid="{3496D658-F7DB-469C-8D98-A524DB1BB47C}"/>
-    <hyperlink ref="E239" r:id="rId282" xr:uid="{8C4590C0-E71B-4B6F-928F-91CDE3276DD9}"/>
-    <hyperlink ref="E238" r:id="rId283" xr:uid="{9D29C97A-A6D3-48A4-9664-8DCE5B234FAB}"/>
-    <hyperlink ref="E236" r:id="rId284" xr:uid="{9921A962-A113-4002-BDE2-4F4E4320B387}"/>
+    <hyperlink ref="E238" r:id="rId282" xr:uid="{8C4590C0-E71B-4B6F-928F-91CDE3276DD9}"/>
+    <hyperlink ref="E237" r:id="rId283" xr:uid="{9D29C97A-A6D3-48A4-9664-8DCE5B234FAB}"/>
+    <hyperlink ref="E235" r:id="rId284" xr:uid="{9921A962-A113-4002-BDE2-4F4E4320B387}"/>
     <hyperlink ref="E220" r:id="rId285" xr:uid="{2401C9CC-8D34-433A-BAAD-C1FD2BC14D49}"/>
     <hyperlink ref="E226" r:id="rId286" xr:uid="{D146BB8F-137F-4456-BBA2-EC755F8EBC46}"/>
     <hyperlink ref="E229" r:id="rId287" xr:uid="{E360B755-600F-4776-B306-2E5CFACE17ED}"/>
@@ -35047,66 +35001,65 @@
     <hyperlink ref="E107" r:id="rId289" xr:uid="{F858A3E3-5FB0-420A-93A4-648662EF60EA}"/>
     <hyperlink ref="E108" r:id="rId290" xr:uid="{E4B29D74-9296-485B-83BA-F2FBF277CAEE}"/>
     <hyperlink ref="E47" r:id="rId291" xr:uid="{AFD749B1-917D-4B9C-A4A3-C3DEE02AC2C0}"/>
-    <hyperlink ref="E247" r:id="rId292" xr:uid="{0CCBA335-85C5-47D0-ABB1-7AD15CE9C6BE}"/>
-    <hyperlink ref="E255" r:id="rId293" xr:uid="{0556EF01-FFEF-410A-8AA8-8CA7BB356178}"/>
-    <hyperlink ref="E253" r:id="rId294" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="E254" r:id="rId295" xr:uid="{CEDFA42B-F516-4AB2-AC3C-789EA49C621B}"/>
-    <hyperlink ref="E235" r:id="rId296" xr:uid="{B1CD58B6-DF33-4CD0-8D2C-935BE832C573}"/>
-    <hyperlink ref="E245" r:id="rId297" xr:uid="{F18D1A45-C38D-44C9-8381-31675C618684}"/>
-    <hyperlink ref="E56" r:id="rId298" xr:uid="{DD79BAA1-3570-429D-B5E3-B3B22125D45D}"/>
-    <hyperlink ref="E55" r:id="rId299" xr:uid="{AA3B5FD0-ABB7-481B-A828-1CEE4B997FFD}"/>
-    <hyperlink ref="E54" r:id="rId300" xr:uid="{BF9D025F-FFAE-4B6F-BE59-85E6A492D964}"/>
-    <hyperlink ref="E57" r:id="rId301" xr:uid="{25BF0BAB-C327-4860-BE43-460DA2024CB4}"/>
-    <hyperlink ref="E224" r:id="rId302" xr:uid="{A4991D16-BC46-4421-9733-4A0B675397D5}"/>
-    <hyperlink ref="E61" r:id="rId303" xr:uid="{3F28325A-419D-479F-A2CB-A6026E9C1738}"/>
-    <hyperlink ref="E62" r:id="rId304" xr:uid="{B55832FE-CDC8-476F-BFB2-210023AFDA15}"/>
-    <hyperlink ref="E64" r:id="rId305" xr:uid="{B0548B46-2425-4209-B406-7C5E06BB0B37}"/>
-    <hyperlink ref="E63" r:id="rId306" xr:uid="{7E1F57C3-1645-40A6-A0AB-E7D49C5BC286}"/>
-    <hyperlink ref="E67" r:id="rId307" xr:uid="{7F35F4C4-5217-404F-805D-AF7E847E2C3D}"/>
-    <hyperlink ref="E65" r:id="rId308" xr:uid="{492B5D03-5AAD-427D-BE79-33C2CF3C4B10}"/>
-    <hyperlink ref="E66" r:id="rId309" xr:uid="{DA981BF7-21C6-460F-8AB8-B7AC55085F27}"/>
-    <hyperlink ref="E49" r:id="rId310" xr:uid="{AC9DF199-9137-4950-AC5B-3422838E7898}"/>
-    <hyperlink ref="E60" r:id="rId311" xr:uid="{2F280586-B20D-4605-BEDE-548C581301E3}"/>
-    <hyperlink ref="E9" r:id="rId312" xr:uid="{B603EF92-ABB1-43FC-B014-BB1CE6C5F001}"/>
-    <hyperlink ref="E40" r:id="rId313" xr:uid="{7D969BE7-A6DA-49DE-A64E-EEB8E1A4033B}"/>
-    <hyperlink ref="E58" r:id="rId314" xr:uid="{80EB2D2F-2CD1-4A85-B0E5-21F5B54DC575}"/>
-    <hyperlink ref="E8" r:id="rId315" xr:uid="{3EDBF06D-E052-4275-A527-5A8869D64CDF}"/>
-    <hyperlink ref="E39" r:id="rId316" xr:uid="{131947D2-EAB0-4D8C-9AEF-22FB74118A82}"/>
-    <hyperlink ref="E154" r:id="rId317" xr:uid="{3F9A6173-1CC2-4924-8DCB-DA0907EBC497}"/>
-    <hyperlink ref="E23" r:id="rId318" xr:uid="{CFCB346F-57BF-4E1F-A83E-1ECF2056F264}"/>
-    <hyperlink ref="E102" r:id="rId319" xr:uid="{2356458E-6B22-49DA-9E6A-10397CF5FFCB}"/>
-    <hyperlink ref="E307" r:id="rId320" xr:uid="{4E26D969-664E-4EA5-BCDD-C0244659BD80}"/>
-    <hyperlink ref="E11" r:id="rId321" xr:uid="{79FBDA3E-6FA8-4642-9106-ECA30BC0F184}"/>
-    <hyperlink ref="E16" r:id="rId322" xr:uid="{76475329-A2A3-4832-B080-9DF1FCF7B69C}"/>
-    <hyperlink ref="E34" r:id="rId323" xr:uid="{712331F6-B9ED-461A-B3A4-361688CBC32C}"/>
-    <hyperlink ref="E18" r:id="rId324" xr:uid="{AF5DD662-70AC-4699-9546-0F375CEB30DD}"/>
-    <hyperlink ref="E20" r:id="rId325" xr:uid="{7983D009-F451-44FD-810F-30FF2A3718BA}"/>
-    <hyperlink ref="E19" r:id="rId326" xr:uid="{CD31F41D-EA1B-403F-8D0D-B77515C1536B}"/>
-    <hyperlink ref="E113" r:id="rId327" xr:uid="{127B98B1-79F3-43C9-B7FF-4FBC27351376}"/>
-    <hyperlink ref="E256" r:id="rId328" xr:uid="{2D7D988B-76D9-4BEC-8F29-806C1E841434}"/>
-    <hyperlink ref="E265" r:id="rId329" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="E257" r:id="rId330" xr:uid="{243B74CF-B5C2-468E-9F2F-0DA78790403B}"/>
-    <hyperlink ref="E258" r:id="rId331" xr:uid="{9E359A2D-80A4-4440-B6F6-E0BD637BE478}"/>
-    <hyperlink ref="E260" r:id="rId332" xr:uid="{92D99966-CAE9-4A3E-8110-212EFFA305D9}"/>
-    <hyperlink ref="E259" r:id="rId333" xr:uid="{82293A7C-C43B-41FD-91B1-86521EAC11D6}"/>
-    <hyperlink ref="E12" r:id="rId334" xr:uid="{68E8B6A2-6017-4405-9549-B2377AC5DEDF}"/>
-    <hyperlink ref="E261" r:id="rId335" xr:uid="{9E27F39A-FC85-46E5-98FF-497FB0860FA7}"/>
-    <hyperlink ref="E262" r:id="rId336" xr:uid="{3BF3C81C-57C8-46D6-BC82-B24998AE425F}"/>
-    <hyperlink ref="E263" r:id="rId337" xr:uid="{D60890AA-5FFE-44F0-AA27-28E4BFB644F6}"/>
-    <hyperlink ref="E264" r:id="rId338" xr:uid="{BEBCCD33-BF2B-422C-8302-61C8E85BEDED}"/>
-    <hyperlink ref="E308" r:id="rId339" xr:uid="{FC2672B5-6248-497C-B62C-4B7547222ED5}"/>
-    <hyperlink ref="E268" r:id="rId340" xr:uid="{98B6A04A-6AA6-4AC2-974B-16AADA142558}"/>
-    <hyperlink ref="E271" r:id="rId341" xr:uid="{8F938C70-22E3-4D8B-80C3-A2EDD6B55F32}"/>
-    <hyperlink ref="E285" r:id="rId342" xr:uid="{C19ECC48-6755-42E3-93AC-1AF2A6E16C8B}"/>
-    <hyperlink ref="E283" r:id="rId343" xr:uid="{96721404-CCF2-44A2-9BCC-E8604D34595E}"/>
-    <hyperlink ref="E281" r:id="rId344" xr:uid="{C4C7ED52-DB44-4C33-BB8E-35BEB7281A83}"/>
-    <hyperlink ref="E282" r:id="rId345" xr:uid="{5173BA28-5956-4E15-A77A-2EC7E30FC1EA}"/>
-    <hyperlink ref="E284" r:id="rId346" xr:uid="{74251C99-B647-4AF5-90FF-984998C44E82}"/>
-    <hyperlink ref="E286" r:id="rId347" xr:uid="{43E38533-4E5E-4A3A-B028-87FFDAEA95AF}"/>
-    <hyperlink ref="E267" r:id="rId348" xr:uid="{D8B34417-E714-44C5-92E5-677B9CA2E5A8}"/>
-    <hyperlink ref="E223" r:id="rId349" xr:uid="{CA41E718-82EA-4AAD-BE4C-17139F6C8FCA}"/>
+    <hyperlink ref="E245" r:id="rId292" xr:uid="{0CCBA335-85C5-47D0-ABB1-7AD15CE9C6BE}"/>
+    <hyperlink ref="E253" r:id="rId293" xr:uid="{0556EF01-FFEF-410A-8AA8-8CA7BB356178}"/>
+    <hyperlink ref="E251" r:id="rId294" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="E252" r:id="rId295" xr:uid="{CEDFA42B-F516-4AB2-AC3C-789EA49C621B}"/>
+    <hyperlink ref="E56" r:id="rId296" xr:uid="{DD79BAA1-3570-429D-B5E3-B3B22125D45D}"/>
+    <hyperlink ref="E55" r:id="rId297" xr:uid="{AA3B5FD0-ABB7-481B-A828-1CEE4B997FFD}"/>
+    <hyperlink ref="E54" r:id="rId298" xr:uid="{BF9D025F-FFAE-4B6F-BE59-85E6A492D964}"/>
+    <hyperlink ref="E57" r:id="rId299" xr:uid="{25BF0BAB-C327-4860-BE43-460DA2024CB4}"/>
+    <hyperlink ref="E224" r:id="rId300" xr:uid="{A4991D16-BC46-4421-9733-4A0B675397D5}"/>
+    <hyperlink ref="E61" r:id="rId301" xr:uid="{3F28325A-419D-479F-A2CB-A6026E9C1738}"/>
+    <hyperlink ref="E62" r:id="rId302" xr:uid="{B55832FE-CDC8-476F-BFB2-210023AFDA15}"/>
+    <hyperlink ref="E64" r:id="rId303" xr:uid="{B0548B46-2425-4209-B406-7C5E06BB0B37}"/>
+    <hyperlink ref="E63" r:id="rId304" xr:uid="{7E1F57C3-1645-40A6-A0AB-E7D49C5BC286}"/>
+    <hyperlink ref="E67" r:id="rId305" xr:uid="{7F35F4C4-5217-404F-805D-AF7E847E2C3D}"/>
+    <hyperlink ref="E65" r:id="rId306" xr:uid="{492B5D03-5AAD-427D-BE79-33C2CF3C4B10}"/>
+    <hyperlink ref="E66" r:id="rId307" xr:uid="{DA981BF7-21C6-460F-8AB8-B7AC55085F27}"/>
+    <hyperlink ref="E49" r:id="rId308" xr:uid="{AC9DF199-9137-4950-AC5B-3422838E7898}"/>
+    <hyperlink ref="E60" r:id="rId309" xr:uid="{2F280586-B20D-4605-BEDE-548C581301E3}"/>
+    <hyperlink ref="E9" r:id="rId310" xr:uid="{B603EF92-ABB1-43FC-B014-BB1CE6C5F001}"/>
+    <hyperlink ref="E40" r:id="rId311" xr:uid="{7D969BE7-A6DA-49DE-A64E-EEB8E1A4033B}"/>
+    <hyperlink ref="E58" r:id="rId312" xr:uid="{80EB2D2F-2CD1-4A85-B0E5-21F5B54DC575}"/>
+    <hyperlink ref="E8" r:id="rId313" xr:uid="{3EDBF06D-E052-4275-A527-5A8869D64CDF}"/>
+    <hyperlink ref="E39" r:id="rId314" xr:uid="{131947D2-EAB0-4D8C-9AEF-22FB74118A82}"/>
+    <hyperlink ref="E154" r:id="rId315" xr:uid="{3F9A6173-1CC2-4924-8DCB-DA0907EBC497}"/>
+    <hyperlink ref="E23" r:id="rId316" xr:uid="{CFCB346F-57BF-4E1F-A83E-1ECF2056F264}"/>
+    <hyperlink ref="E102" r:id="rId317" xr:uid="{2356458E-6B22-49DA-9E6A-10397CF5FFCB}"/>
+    <hyperlink ref="E306" r:id="rId318" xr:uid="{4E26D969-664E-4EA5-BCDD-C0244659BD80}"/>
+    <hyperlink ref="E11" r:id="rId319" xr:uid="{79FBDA3E-6FA8-4642-9106-ECA30BC0F184}"/>
+    <hyperlink ref="E16" r:id="rId320" xr:uid="{76475329-A2A3-4832-B080-9DF1FCF7B69C}"/>
+    <hyperlink ref="E34" r:id="rId321" xr:uid="{712331F6-B9ED-461A-B3A4-361688CBC32C}"/>
+    <hyperlink ref="E18" r:id="rId322" xr:uid="{AF5DD662-70AC-4699-9546-0F375CEB30DD}"/>
+    <hyperlink ref="E20" r:id="rId323" xr:uid="{7983D009-F451-44FD-810F-30FF2A3718BA}"/>
+    <hyperlink ref="E19" r:id="rId324" xr:uid="{CD31F41D-EA1B-403F-8D0D-B77515C1536B}"/>
+    <hyperlink ref="E113" r:id="rId325" xr:uid="{127B98B1-79F3-43C9-B7FF-4FBC27351376}"/>
+    <hyperlink ref="E254" r:id="rId326" xr:uid="{2D7D988B-76D9-4BEC-8F29-806C1E841434}"/>
+    <hyperlink ref="E263" r:id="rId327" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="E255" r:id="rId328" xr:uid="{243B74CF-B5C2-468E-9F2F-0DA78790403B}"/>
+    <hyperlink ref="E256" r:id="rId329" xr:uid="{9E359A2D-80A4-4440-B6F6-E0BD637BE478}"/>
+    <hyperlink ref="E258" r:id="rId330" xr:uid="{92D99966-CAE9-4A3E-8110-212EFFA305D9}"/>
+    <hyperlink ref="E257" r:id="rId331" xr:uid="{82293A7C-C43B-41FD-91B1-86521EAC11D6}"/>
+    <hyperlink ref="E12" r:id="rId332" xr:uid="{68E8B6A2-6017-4405-9549-B2377AC5DEDF}"/>
+    <hyperlink ref="E259" r:id="rId333" xr:uid="{9E27F39A-FC85-46E5-98FF-497FB0860FA7}"/>
+    <hyperlink ref="E260" r:id="rId334" xr:uid="{3BF3C81C-57C8-46D6-BC82-B24998AE425F}"/>
+    <hyperlink ref="E261" r:id="rId335" xr:uid="{D60890AA-5FFE-44F0-AA27-28E4BFB644F6}"/>
+    <hyperlink ref="E262" r:id="rId336" xr:uid="{BEBCCD33-BF2B-422C-8302-61C8E85BEDED}"/>
+    <hyperlink ref="E307" r:id="rId337" xr:uid="{FC2672B5-6248-497C-B62C-4B7547222ED5}"/>
+    <hyperlink ref="E266" r:id="rId338" xr:uid="{98B6A04A-6AA6-4AC2-974B-16AADA142558}"/>
+    <hyperlink ref="E269" r:id="rId339" xr:uid="{8F938C70-22E3-4D8B-80C3-A2EDD6B55F32}"/>
+    <hyperlink ref="E283" r:id="rId340" xr:uid="{C19ECC48-6755-42E3-93AC-1AF2A6E16C8B}"/>
+    <hyperlink ref="E281" r:id="rId341" xr:uid="{96721404-CCF2-44A2-9BCC-E8604D34595E}"/>
+    <hyperlink ref="E279" r:id="rId342" xr:uid="{C4C7ED52-DB44-4C33-BB8E-35BEB7281A83}"/>
+    <hyperlink ref="E280" r:id="rId343" xr:uid="{5173BA28-5956-4E15-A77A-2EC7E30FC1EA}"/>
+    <hyperlink ref="E282" r:id="rId344" xr:uid="{74251C99-B647-4AF5-90FF-984998C44E82}"/>
+    <hyperlink ref="E285" r:id="rId345" xr:uid="{43E38533-4E5E-4A3A-B028-87FFDAEA95AF}"/>
+    <hyperlink ref="E265" r:id="rId346" xr:uid="{D8B34417-E714-44C5-92E5-677B9CA2E5A8}"/>
+    <hyperlink ref="E223" r:id="rId347" xr:uid="{CA41E718-82EA-4AAD-BE4C-17139F6C8FCA}"/>
+    <hyperlink ref="E284" r:id="rId348" xr:uid="{072FA124-769A-4A34-ABC3-93893442CE71}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId350"/>
+  <pageSetup orientation="portrait" r:id="rId349"/>
 </worksheet>
 </file>
--- a/Strivers List + other Problems.xlsx
+++ b/Strivers List + other Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA9A1EA-C9CD-4172-9C36-4B6A49ADD0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CDA09C-D57A-4723-83B5-08E673914705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="506">
   <si>
     <t>Mark as Done</t>
   </si>
@@ -920,12 +920,6 @@
     <t xml:space="preserve">Phonepe ,  Google, Apple, Microsoft, Amazon </t>
   </si>
   <si>
-    <t>https://leetcode.com/problems/longest-increasing-path-in-a-matrix/description/?envType=problem-list-v2&amp;envId=topological-sort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprinklr, Google, Amazon, Meta </t>
-  </si>
-  <si>
     <t>Dijkstra's Algorithm</t>
   </si>
   <si>
@@ -1265,9 +1259,6 @@
     <t>https://www.geeksforgeeks.org/problems/number-of-distinct-islands/1</t>
   </si>
   <si>
-    <t>Topoplogical Sorting (BFS)(Khans Algorithm)</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/find-eventual-safe-states/</t>
   </si>
   <si>
@@ -1554,6 +1545,12 @@
   </si>
   <si>
     <t>Longest increasing path in the matrix</t>
+  </si>
+  <si>
+    <t>Minimum multiplications to reach end</t>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/problems/minimum-multiplications-to-reach-end/0</t>
   </si>
 </sst>
 </file>
@@ -2505,7 +2502,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>9</v>
@@ -2542,7 +2539,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>9</v>
@@ -2618,7 +2615,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>9</v>
@@ -2653,7 +2650,7 @@
       </c>
       <c r="C12" s="30"/>
       <c r="D12" s="29" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>9</v>
@@ -2729,7 +2726,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>9</v>
@@ -2766,7 +2763,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>9</v>
@@ -2803,7 +2800,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>9</v>
@@ -2881,7 +2878,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E18" s="21" t="s">
         <v>9</v>
@@ -2918,7 +2915,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E19" s="21" t="s">
         <v>9</v>
@@ -2955,7 +2952,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E20" s="21" t="s">
         <v>9</v>
@@ -2992,7 +2989,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E21" s="31" t="s">
         <v>9</v>
@@ -3068,7 +3065,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E23" s="21" t="s">
         <v>9</v>
@@ -3189,7 +3186,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E26" s="34" t="s">
         <v>9</v>
@@ -3232,7 +3229,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E27" s="21" t="s">
         <v>9</v>
@@ -3310,7 +3307,7 @@
         <v>23</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E29" s="25" t="s">
         <v>9</v>
@@ -3431,7 +3428,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E32" s="21" t="s">
         <v>9</v>
@@ -3509,7 +3506,7 @@
         <v>28</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E34" s="21" t="s">
         <v>9</v>
@@ -3710,7 +3707,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>9</v>
@@ -3747,7 +3744,7 @@
         <v>34</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E40" s="21" t="s">
         <v>9</v>
@@ -3784,7 +3781,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E41" s="34" t="s">
         <v>9</v>
@@ -3866,7 +3863,7 @@
         <v>37</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E43" s="31" t="s">
         <v>9</v>
@@ -4026,7 +4023,7 @@
         <v>41</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E47" s="21" t="s">
         <v>9</v>
@@ -4102,7 +4099,7 @@
         <v>43</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E49" s="21" t="s">
         <v>9</v>
@@ -4263,7 +4260,7 @@
         <v>2</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E54" s="21" t="s">
         <v>9</v>
@@ -4300,7 +4297,7 @@
         <v>3</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E55" s="21" t="s">
         <v>9</v>
@@ -4337,7 +4334,7 @@
         <v>4</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E56" s="21" t="s">
         <v>9</v>
@@ -4374,7 +4371,7 @@
         <v>5</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E57" s="21" t="s">
         <v>9</v>
@@ -4411,7 +4408,7 @@
         <v>6</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E58" s="21" t="s">
         <v>9</v>
@@ -4487,7 +4484,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>9</v>
@@ -4524,7 +4521,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E61" s="21" t="s">
         <v>9</v>
@@ -4561,7 +4558,7 @@
         <v>10</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E62" s="21" t="s">
         <v>9</v>
@@ -4598,7 +4595,7 @@
         <v>11</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>9</v>
@@ -4635,7 +4632,7 @@
         <v>12</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>9</v>
@@ -4672,7 +4669,7 @@
         <v>13</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E65" s="21" t="s">
         <v>9</v>
@@ -4709,7 +4706,7 @@
         <v>14</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E66" s="21" t="s">
         <v>9</v>
@@ -4746,7 +4743,7 @@
         <v>15</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E67" s="21" t="s">
         <v>9</v>
@@ -5051,7 +5048,7 @@
         <v>3</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E76" s="21" t="s">
         <v>9</v>
@@ -5088,7 +5085,7 @@
         <v>4</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E77" s="31" t="s">
         <v>9</v>
@@ -5203,7 +5200,7 @@
         <v>7</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E80" s="21" t="s">
         <v>9</v>
@@ -5240,7 +5237,7 @@
         <v>8</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E81" s="21" t="s">
         <v>9</v>
@@ -5277,7 +5274,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E82" s="21" t="s">
         <v>9</v>
@@ -5433,7 +5430,7 @@
         <v>13</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E86" s="21" t="s">
         <v>9</v>
@@ -5548,7 +5545,7 @@
         <v>16</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E89" s="31" t="s">
         <v>9</v>
@@ -6007,7 +6004,7 @@
         <v>7</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>9</v>
@@ -6045,7 +6042,7 @@
         <v>8</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E103" s="21" t="s">
         <v>9</v>
@@ -6207,7 +6204,7 @@
         <v>13</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E107" s="21" t="s">
         <v>9</v>
@@ -6245,7 +6242,7 @@
         <v>14</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E108" s="21" t="s">
         <v>9</v>
@@ -6380,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="29" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E112" s="41" t="s">
         <v>9</v>
@@ -6419,7 +6416,7 @@
       </c>
       <c r="C113" s="30"/>
       <c r="D113" s="29" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E113" s="21" t="s">
         <v>9</v>
@@ -6454,7 +6451,7 @@
         <v>2</v>
       </c>
       <c r="D114" s="29" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E114" s="41" t="s">
         <v>9</v>
@@ -6495,7 +6492,7 @@
         <v>3</v>
       </c>
       <c r="D115" s="29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E115" s="41" t="s">
         <v>9</v>
@@ -6536,7 +6533,7 @@
         <v>4</v>
       </c>
       <c r="D116" s="29" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E116" s="41" t="s">
         <v>9</v>
@@ -6575,7 +6572,7 @@
         <v>5</v>
       </c>
       <c r="D117" s="29" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E117" s="41" t="s">
         <v>9</v>
@@ -6616,7 +6613,7 @@
         <v>6</v>
       </c>
       <c r="D118" s="29" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E118" s="41" t="s">
         <v>9</v>
@@ -6657,7 +6654,7 @@
         <v>7</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E119" s="41" t="s">
         <v>9</v>
@@ -6739,7 +6736,7 @@
         <v>9</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E121" s="31" t="s">
         <v>9</v>
@@ -6854,7 +6851,7 @@
         <v>12</v>
       </c>
       <c r="D124" s="29" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E124" s="31" t="s">
         <v>9</v>
@@ -6891,7 +6888,7 @@
         <v>13</v>
       </c>
       <c r="D125" s="29" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E125" s="31" t="s">
         <v>9</v>
@@ -6928,7 +6925,7 @@
         <v>14</v>
       </c>
       <c r="D126" s="29" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E126" s="31" t="s">
         <v>9</v>
@@ -7004,7 +7001,7 @@
         <v>16</v>
       </c>
       <c r="D128" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E128" s="21" t="s">
         <v>9</v>
@@ -7082,7 +7079,7 @@
         <v>18</v>
       </c>
       <c r="D130" s="29" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E130" s="31" t="s">
         <v>9</v>
@@ -7431,7 +7428,7 @@
         <v>8</v>
       </c>
       <c r="D139" s="29" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E139" s="21" t="s">
         <v>9</v>
@@ -7509,7 +7506,7 @@
         <v>10</v>
       </c>
       <c r="D141" s="29" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E141" s="21" t="s">
         <v>9</v>
@@ -7546,7 +7543,7 @@
         <v>11</v>
       </c>
       <c r="D142" s="29" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E142" s="21" t="s">
         <v>9</v>
@@ -7583,7 +7580,7 @@
         <v>12</v>
       </c>
       <c r="D143" s="29" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E143" s="21" t="s">
         <v>9</v>
@@ -7881,7 +7878,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="29" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E151" s="41" t="s">
         <v>9</v>
@@ -7922,7 +7919,7 @@
         <v>2</v>
       </c>
       <c r="D152" s="29" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E152" s="41" t="s">
         <v>9</v>
@@ -7963,7 +7960,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="29" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E153" s="41" t="s">
         <v>9</v>
@@ -8002,7 +7999,7 @@
       </c>
       <c r="C154" s="30"/>
       <c r="D154" s="29" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E154" s="21" t="s">
         <v>9</v>
@@ -8039,7 +8036,7 @@
         <v>4</v>
       </c>
       <c r="D155" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E155" s="41" t="s">
         <v>9</v>
@@ -8078,7 +8075,7 @@
         <v>5</v>
       </c>
       <c r="D156" s="29" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E156" s="41" t="s">
         <v>9</v>
@@ -8119,7 +8116,7 @@
         <v>6</v>
       </c>
       <c r="D157" s="29" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E157" s="41" t="s">
         <v>9</v>
@@ -8160,7 +8157,7 @@
         <v>7</v>
       </c>
       <c r="D158" s="29" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E158" s="41" t="s">
         <v>9</v>
@@ -8201,7 +8198,7 @@
         <v>8</v>
       </c>
       <c r="D159" s="29" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E159" s="41" t="s">
         <v>9</v>
@@ -8242,7 +8239,7 @@
         <v>9</v>
       </c>
       <c r="D160" s="29" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E160" s="41" t="s">
         <v>9</v>
@@ -8281,7 +8278,7 @@
         <v>10</v>
       </c>
       <c r="D161" s="29" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E161" s="41" t="s">
         <v>9</v>
@@ -8322,7 +8319,7 @@
         <v>11</v>
       </c>
       <c r="D162" s="29" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E162" s="41" t="s">
         <v>9</v>
@@ -8361,7 +8358,7 @@
         <v>12</v>
       </c>
       <c r="D163" s="29" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E163" s="41" t="s">
         <v>9</v>
@@ -8402,7 +8399,7 @@
         <v>13</v>
       </c>
       <c r="D164" s="29" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E164" s="41" t="s">
         <v>9</v>
@@ -8441,7 +8438,7 @@
         <v>14</v>
       </c>
       <c r="D165" s="29" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E165" s="21" t="s">
         <v>9</v>
@@ -8478,7 +8475,7 @@
         <v>15</v>
       </c>
       <c r="D166" s="29" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E166" s="21" t="s">
         <v>9</v>
@@ -8515,7 +8512,7 @@
         <v>16</v>
       </c>
       <c r="D167" s="29" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E167" s="41" t="s">
         <v>9</v>
@@ -8554,7 +8551,7 @@
         <v>17</v>
       </c>
       <c r="D168" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E168" s="41" t="s">
         <v>9</v>
@@ -8595,7 +8592,7 @@
         <v>18</v>
       </c>
       <c r="D169" s="29" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E169" s="21" t="s">
         <v>9</v>
@@ -8673,7 +8670,7 @@
         <v>20</v>
       </c>
       <c r="D171" s="29" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E171" s="41" t="s">
         <v>9</v>
@@ -8794,7 +8791,7 @@
         <v>23</v>
       </c>
       <c r="D174" s="29" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E174" s="41" t="s">
         <v>9</v>
@@ -8915,7 +8912,7 @@
         <v>26</v>
       </c>
       <c r="D177" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E177" s="41" t="s">
         <v>9</v>
@@ -8993,7 +8990,7 @@
         <v>28</v>
       </c>
       <c r="D179" s="29" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E179" s="31" t="s">
         <v>9</v>
@@ -9030,7 +9027,7 @@
         <v>29</v>
       </c>
       <c r="D180" s="29" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E180" s="31" t="s">
         <v>9</v>
@@ -10265,10 +10262,10 @@
         <v>2</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E213" s="23" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F213" s="27" t="s">
         <v>10</v>
@@ -10539,7 +10536,7 @@
         <v>262</v>
       </c>
       <c r="E220" s="51" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F220" s="26" t="s">
         <v>22</v>
@@ -10651,10 +10648,10 @@
       </c>
       <c r="C223" s="2"/>
       <c r="D223" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F223" s="26" t="s">
         <v>22</v>
@@ -10688,10 +10685,10 @@
         <v>12</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F224" s="26" t="s">
         <v>22</v>
@@ -10725,10 +10722,10 @@
         <v>13</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F225" s="26" t="s">
         <v>22</v>
@@ -10762,10 +10759,10 @@
         <v>14</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E226" s="23" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F226" s="26" t="s">
         <v>22</v>
@@ -10877,10 +10874,10 @@
         <v>17</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E229" s="23" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F229" s="26" t="s">
         <v>22</v>
@@ -10914,7 +10911,7 @@
         <v>18</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E230" s="18" t="s">
         <v>275</v>
@@ -10953,7 +10950,7 @@
         <v>19</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E231" s="23" t="s">
         <v>253</v>
@@ -11070,10 +11067,10 @@
         <v>22</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F234" s="26" t="s">
         <v>22</v>
@@ -11107,10 +11104,10 @@
         <v>24</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F235" s="26" t="s">
         <v>22</v>
@@ -11183,10 +11180,10 @@
         <v>26</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E237" s="23" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F237" s="26" t="s">
         <v>22</v>
@@ -11220,10 +11217,10 @@
         <v>27</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E238" s="23" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F238" s="26" t="s">
         <v>22</v>
@@ -11257,10 +11254,10 @@
         <v>28</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E239" s="23" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F239" s="52" t="s">
         <v>53</v>
@@ -11333,10 +11330,10 @@
         <v>30</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E241" s="23" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F241" s="26" t="s">
         <v>22</v>
@@ -11400,27 +11397,23 @@
       <c r="X242" s="1"/>
       <c r="Y242" s="1"/>
     </row>
-    <row r="243" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A243" s="58"/>
       <c r="B243" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C243" s="2">
-        <v>32</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C243" s="2"/>
       <c r="D243" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E243" s="18" t="s">
-        <v>293</v>
+        <v>504</v>
+      </c>
+      <c r="E243" s="23" t="s">
+        <v>505</v>
       </c>
       <c r="F243" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G243" s="3"/>
-      <c r="H243" s="16" t="s">
-        <v>294</v>
-      </c>
+      <c r="H243" s="15"/>
       <c r="I243" s="3"/>
       <c r="J243" s="1"/>
       <c r="K243" s="1"/>
@@ -11445,20 +11438,20 @@
         <v>0</v>
       </c>
       <c r="C244" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>410</v>
+        <v>292</v>
       </c>
       <c r="E244" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="F244" s="28" t="s">
-        <v>53</v>
+        <v>293</v>
+      </c>
+      <c r="F244" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="G244" s="3"/>
       <c r="H244" s="16" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I244" s="3"/>
       <c r="J244" s="1"/>
@@ -11487,10 +11480,10 @@
         <v>35</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E245" s="23" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F245" s="28" t="s">
         <v>53</v>
@@ -11524,17 +11517,17 @@
         <v>36</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E246" s="18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F246" s="28" t="s">
         <v>53</v>
       </c>
       <c r="G246" s="3"/>
       <c r="H246" s="16" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I246" s="3"/>
       <c r="J246" s="1"/>
@@ -11563,7 +11556,7 @@
         <v>37</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E247" s="18" t="s">
         <v>260</v>
@@ -11573,7 +11566,7 @@
       </c>
       <c r="G247" s="3"/>
       <c r="H247" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I247" s="3"/>
       <c r="J247" s="1"/>
@@ -11602,10 +11595,10 @@
         <v>38</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F248" s="47" t="s">
         <v>10</v>
@@ -11686,7 +11679,7 @@
     </row>
     <row r="251" spans="1:25" ht="15" x14ac:dyDescent="0.35">
       <c r="A251" s="67" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B251" s="50" t="b">
         <v>1</v>
@@ -11695,7 +11688,7 @@
         <v>1</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E251" s="8" t="s">
         <v>9</v>
@@ -11705,7 +11698,7 @@
       </c>
       <c r="G251" s="3"/>
       <c r="H251" s="15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I251" s="3"/>
       <c r="J251" s="1"/>
@@ -11734,7 +11727,7 @@
         <v>2</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E252" s="21" t="s">
         <v>9</v>
@@ -11771,7 +11764,7 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E253" s="21" t="s">
         <v>9</v>
@@ -11808,7 +11801,7 @@
         <v>4</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E254" s="21" t="s">
         <v>9</v>
@@ -11845,7 +11838,7 @@
         <v>5</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E255" s="21" t="s">
         <v>9</v>
@@ -11882,7 +11875,7 @@
         <v>6</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E256" s="21" t="s">
         <v>9</v>
@@ -11919,7 +11912,7 @@
         <v>7</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E257" s="21" t="s">
         <v>9</v>
@@ -11956,7 +11949,7 @@
         <v>8</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E258" s="21" t="s">
         <v>9</v>
@@ -11993,7 +11986,7 @@
         <v>9</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E259" s="21" t="s">
         <v>9</v>
@@ -12030,7 +12023,7 @@
         <v>10</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E260" s="21" t="s">
         <v>9</v>
@@ -12067,7 +12060,7 @@
         <v>11</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E261" s="21" t="s">
         <v>9</v>
@@ -12104,7 +12097,7 @@
         <v>12</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E262" s="21" t="s">
         <v>9</v>
@@ -12141,7 +12134,7 @@
         <v>13</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E263" s="8" t="s">
         <v>9</v>
@@ -12151,7 +12144,7 @@
       </c>
       <c r="G263" s="3"/>
       <c r="H263" s="15" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I263" s="3"/>
       <c r="J263" s="1"/>
@@ -12180,7 +12173,7 @@
         <v>14</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E264" s="46" t="s">
         <v>9</v>
@@ -12190,7 +12183,7 @@
       </c>
       <c r="G264" s="3"/>
       <c r="H264" s="16" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I264" s="3"/>
       <c r="J264" s="1"/>
@@ -12219,7 +12212,7 @@
         <v>15</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E265" s="21" t="s">
         <v>9</v>
@@ -12229,7 +12222,7 @@
       </c>
       <c r="G265" s="3"/>
       <c r="H265" s="16" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I265" s="3"/>
       <c r="J265" s="1"/>
@@ -12258,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E266" s="21" t="s">
         <v>9</v>
@@ -12295,7 +12288,7 @@
         <v>17</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E267" s="8" t="s">
         <v>9</v>
@@ -12305,7 +12298,7 @@
       </c>
       <c r="G267" s="3"/>
       <c r="H267" s="15" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I267" s="3"/>
       <c r="J267" s="1"/>
@@ -12334,7 +12327,7 @@
         <v>18</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E268" s="8" t="s">
         <v>9</v>
@@ -12344,7 +12337,7 @@
       </c>
       <c r="G268" s="3"/>
       <c r="H268" s="15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I268" s="3"/>
       <c r="J268" s="1"/>
@@ -12373,7 +12366,7 @@
         <v>19</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E269" s="21" t="s">
         <v>9</v>
@@ -12410,7 +12403,7 @@
         <v>20</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E270" s="8" t="s">
         <v>9</v>
@@ -12420,7 +12413,7 @@
       </c>
       <c r="G270" s="3"/>
       <c r="H270" s="15" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I270" s="3"/>
       <c r="J270" s="1"/>
@@ -12449,7 +12442,7 @@
         <v>21</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E271" s="8" t="s">
         <v>9</v>
@@ -12459,7 +12452,7 @@
       </c>
       <c r="G271" s="3"/>
       <c r="H271" s="16" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I271" s="3"/>
       <c r="J271" s="1"/>
@@ -12488,7 +12481,7 @@
         <v>22</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E272" s="8" t="s">
         <v>9</v>
@@ -12498,7 +12491,7 @@
       </c>
       <c r="G272" s="3"/>
       <c r="H272" s="15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I272" s="3"/>
       <c r="J272" s="1"/>
@@ -12527,7 +12520,7 @@
         <v>23</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E273" s="8" t="s">
         <v>9</v>
@@ -12537,7 +12530,7 @@
       </c>
       <c r="G273" s="3"/>
       <c r="H273" s="15" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I273" s="3"/>
       <c r="J273" s="1"/>
@@ -12566,7 +12559,7 @@
         <v>24</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E274" s="8" t="s">
         <v>9</v>
@@ -12576,7 +12569,7 @@
       </c>
       <c r="G274" s="3"/>
       <c r="H274" s="16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I274" s="3"/>
       <c r="J274" s="1"/>
@@ -12605,7 +12598,7 @@
         <v>25</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E275" s="8" t="s">
         <v>9</v>
@@ -12615,7 +12608,7 @@
       </c>
       <c r="G275" s="3"/>
       <c r="H275" s="15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I275" s="3"/>
       <c r="J275" s="1"/>
@@ -12644,7 +12637,7 @@
         <v>26</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E276" s="8" t="s">
         <v>9</v>
@@ -12654,7 +12647,7 @@
       </c>
       <c r="G276" s="3"/>
       <c r="H276" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I276" s="3"/>
       <c r="J276" s="1"/>
@@ -12683,7 +12676,7 @@
         <v>27</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E277" s="8" t="s">
         <v>9</v>
@@ -12693,7 +12686,7 @@
       </c>
       <c r="G277" s="3"/>
       <c r="H277" s="15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I277" s="3"/>
       <c r="J277" s="1"/>
@@ -12722,7 +12715,7 @@
         <v>28</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E278" s="8" t="s">
         <v>9</v>
@@ -12732,7 +12725,7 @@
       </c>
       <c r="G278" s="3"/>
       <c r="H278" s="16" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I278" s="3"/>
       <c r="J278" s="1"/>
@@ -12761,7 +12754,7 @@
         <v>29</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E279" s="21" t="s">
         <v>9</v>
@@ -12798,7 +12791,7 @@
         <v>30</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E280" s="21" t="s">
         <v>9</v>
@@ -12835,7 +12828,7 @@
         <v>31</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E281" s="21" t="s">
         <v>9</v>
@@ -12872,7 +12865,7 @@
         <v>32</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E282" s="21" t="s">
         <v>9</v>
@@ -12909,7 +12902,7 @@
         <v>33</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E283" s="21" t="s">
         <v>9</v>
@@ -12944,7 +12937,7 @@
       </c>
       <c r="C284" s="2"/>
       <c r="D284" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E284" s="21" t="s">
         <v>9</v>
@@ -12979,7 +12972,7 @@
       </c>
       <c r="C285" s="2"/>
       <c r="D285" s="1" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E285" s="21" t="s">
         <v>9</v>
@@ -13016,7 +13009,7 @@
         <v>34</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E286" s="8" t="s">
         <v>9</v>
@@ -13026,7 +13019,7 @@
       </c>
       <c r="G286" s="3"/>
       <c r="H286" s="16" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I286" s="3"/>
       <c r="J286" s="1"/>
@@ -13055,7 +13048,7 @@
         <v>35</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E287" s="8" t="s">
         <v>9</v>
@@ -13065,7 +13058,7 @@
       </c>
       <c r="G287" s="3"/>
       <c r="H287" s="16" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I287" s="3"/>
       <c r="J287" s="1"/>
@@ -13094,7 +13087,7 @@
         <v>36</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E288" s="8" t="s">
         <v>9</v>
@@ -13104,7 +13097,7 @@
       </c>
       <c r="G288" s="3"/>
       <c r="H288" s="16" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I288" s="3"/>
       <c r="J288" s="1"/>
@@ -13133,7 +13126,7 @@
         <v>37</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E289" s="8" t="s">
         <v>9</v>
@@ -13143,7 +13136,7 @@
       </c>
       <c r="G289" s="3"/>
       <c r="H289" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I289" s="3"/>
       <c r="J289" s="1"/>
@@ -13172,7 +13165,7 @@
         <v>38</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E290" s="8" t="s">
         <v>9</v>
@@ -13182,7 +13175,7 @@
       </c>
       <c r="G290" s="3"/>
       <c r="H290" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I290" s="3"/>
       <c r="J290" s="1"/>
@@ -13211,7 +13204,7 @@
         <v>39</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E291" s="8" t="s">
         <v>9</v>
@@ -13221,7 +13214,7 @@
       </c>
       <c r="G291" s="3"/>
       <c r="H291" s="16" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I291" s="3"/>
       <c r="J291" s="1"/>
@@ -13297,7 +13290,7 @@
     </row>
     <row r="294" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="67" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B294" s="50" t="b">
         <v>0</v>
@@ -13306,7 +13299,7 @@
         <v>1</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E294" s="22" t="s">
         <v>9</v>
@@ -13316,7 +13309,7 @@
       </c>
       <c r="G294" s="3"/>
       <c r="H294" s="16" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I294" s="3"/>
       <c r="J294" s="1"/>
@@ -13345,7 +13338,7 @@
         <v>2</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E295" s="8" t="s">
         <v>9</v>
@@ -13355,7 +13348,7 @@
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="15" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I295" s="3"/>
       <c r="J295" s="1"/>
@@ -13384,7 +13377,7 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E296" s="8" t="s">
         <v>9</v>
@@ -13394,7 +13387,7 @@
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I296" s="3"/>
       <c r="J296" s="1"/>
@@ -13423,7 +13416,7 @@
         <v>4</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E297" s="8" t="s">
         <v>9</v>
@@ -13433,7 +13426,7 @@
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="15" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I297" s="3"/>
       <c r="J297" s="1"/>
@@ -13462,7 +13455,7 @@
         <v>5</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E298" s="8" t="s">
         <v>9</v>
@@ -13472,7 +13465,7 @@
       </c>
       <c r="G298" s="3"/>
       <c r="H298" s="20" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I298" s="3"/>
       <c r="J298" s="1"/>
@@ -13501,7 +13494,7 @@
         <v>6</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E299" s="8" t="s">
         <v>9</v>
@@ -13511,7 +13504,7 @@
       </c>
       <c r="G299" s="3"/>
       <c r="H299" s="15" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I299" s="3"/>
       <c r="J299" s="1"/>
@@ -13591,7 +13584,7 @@
     </row>
     <row r="302" spans="1:25" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="64" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B302" s="50" t="b">
         <v>0</v>
@@ -13600,13 +13593,13 @@
         <v>1</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E302" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F302" s="40" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G302" s="3"/>
       <c r="H302" s="4"/>
@@ -13637,13 +13630,13 @@
         <v>2</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E303" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F303" s="40" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G303" s="3"/>
       <c r="H303" s="4"/>
@@ -13674,13 +13667,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="24" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E304" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F304" s="40" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G304" s="3"/>
       <c r="H304" s="4"/>
@@ -13711,13 +13704,13 @@
         <v>4</v>
       </c>
       <c r="D305" s="24" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E305" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F305" s="40" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G305" s="3"/>
       <c r="H305" s="4"/>
@@ -13748,13 +13741,13 @@
         <v>5</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E306" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F306" s="40" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G306" s="3"/>
       <c r="H306" s="4"/>
@@ -13785,7 +13778,7 @@
         <v>6</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E307" s="21" t="s">
         <v>9</v>
@@ -34882,182 +34875,182 @@
     <hyperlink ref="E236" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
     <hyperlink ref="E240" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
     <hyperlink ref="E242" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="E243" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="E244" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="E246" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="E247" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="E264" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="E267" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="E268" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="E270" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="E271" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="E272" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="E273" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="E274" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="E275" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="E276" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="E277" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="E278" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="E286" r:id="rId189" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="E287" r:id="rId190" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="E288" r:id="rId191" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="E289" r:id="rId192" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="E290" r:id="rId193" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="E291" r:id="rId194" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="E294" r:id="rId195" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="E295" r:id="rId196" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="E296" r:id="rId197" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="E297" r:id="rId198" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="E298" r:id="rId199" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="E299" r:id="rId200" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="E248" r:id="rId201" xr:uid="{38535620-DA2F-45B6-BE53-7BE35BAD917E}"/>
-    <hyperlink ref="E180" r:id="rId202" xr:uid="{52A62708-7A1B-4947-8125-51CD78E69CDC}"/>
-    <hyperlink ref="E179" r:id="rId203" xr:uid="{90A2CCC4-C963-4688-BF93-898F1AB744EB}"/>
-    <hyperlink ref="G104" r:id="rId204" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="E104" r:id="rId205" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="E103" r:id="rId206" xr:uid="{DDFE149F-872D-40D3-A981-8A2101FAC9BF}"/>
-    <hyperlink ref="E121" r:id="rId207" xr:uid="{B257C977-A47D-4DB0-A09F-C2D9543F22CA}"/>
-    <hyperlink ref="E126" r:id="rId208" xr:uid="{6740D30D-5122-4656-A3AE-0D0EDF0D3361}"/>
-    <hyperlink ref="E125" r:id="rId209" xr:uid="{EE0FF2EF-5A82-4BD2-B997-460C3B05BAF9}"/>
-    <hyperlink ref="E124" r:id="rId210" xr:uid="{8D25C723-BF91-42D1-890E-9CA1BE036008}"/>
-    <hyperlink ref="E77" r:id="rId211" xr:uid="{30B8FDFC-E2BE-4DA3-8FA6-1249AA92CF95}"/>
-    <hyperlink ref="E89" r:id="rId212" xr:uid="{688A3619-4809-464A-A057-9B9FE946F793}"/>
-    <hyperlink ref="E43" r:id="rId213" xr:uid="{0372EC8E-7BC7-4EAC-B994-9672654B43D3}"/>
-    <hyperlink ref="E21" r:id="rId214" xr:uid="{86CAF600-E17D-4EA7-98D0-61A6B60486E9}"/>
-    <hyperlink ref="E6" r:id="rId215" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G6" r:id="rId216" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E14" r:id="rId217" xr:uid="{5942F87D-4C29-438D-B078-6CCBD6F5DD87}"/>
-    <hyperlink ref="G48" r:id="rId218" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="E48" r:id="rId219" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="E46" r:id="rId220" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="G45" r:id="rId221" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="E45" r:id="rId222" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="G44" r:id="rId223" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="E44" r:id="rId224" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="G42" r:id="rId225" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="E42" r:id="rId226" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="G38" r:id="rId227" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="E38" r:id="rId228" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="E37" r:id="rId229" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="E36" r:id="rId230" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="E35" r:id="rId231" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="E33" r:id="rId232" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="G31" r:id="rId233" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="E31" r:id="rId234" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="G30" r:id="rId235" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="E30" r:id="rId236" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="G28" r:id="rId237" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="E28" r:id="rId238" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="G26" r:id="rId239" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="E26" r:id="rId240" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="G25" r:id="rId241" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="E25" r:id="rId242" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G24" r:id="rId243" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="E24" r:id="rId244" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="G22" r:id="rId245" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="E22" r:id="rId246" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="G17" r:id="rId247" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="E17" r:id="rId248" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="G13" r:id="rId249" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="E13" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="G10" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="E10" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G7" r:id="rId253" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="E7" r:id="rId254" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E302" r:id="rId255" xr:uid="{49C446A4-86D9-438E-8C85-C2CBF2D0C601}"/>
-    <hyperlink ref="E29" r:id="rId256" xr:uid="{15B4076B-7C29-451C-A0E0-E0CDB84955C7}"/>
-    <hyperlink ref="E303" r:id="rId257" xr:uid="{5897208F-5F6C-4E1B-8B0F-03D62428448A}"/>
-    <hyperlink ref="E41" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="E15" r:id="rId259" xr:uid="{36657CEA-F972-477D-AC24-77B031A0C947}"/>
-    <hyperlink ref="E304" r:id="rId260" xr:uid="{0B318E6F-5375-45A5-A623-A5D070F4F786}"/>
-    <hyperlink ref="E305" r:id="rId261" xr:uid="{28A35100-95C6-4598-8EAE-4903F97A507B}"/>
-    <hyperlink ref="E32" r:id="rId262" xr:uid="{A642EB9F-9B4D-467C-AA82-CE1A728B251C}"/>
-    <hyperlink ref="E27" r:id="rId263" xr:uid="{A1884A7B-6025-4BC0-B0A7-10DF9BA889E7}"/>
-    <hyperlink ref="E241" r:id="rId264" xr:uid="{DD148482-9331-495D-A315-B2667528DE27}"/>
-    <hyperlink ref="E234" r:id="rId265" xr:uid="{9AFBA357-2FAE-42C6-BAC6-9567300CA7EB}"/>
-    <hyperlink ref="E213" r:id="rId266" xr:uid="{222EEF32-42E7-41DB-92A2-B7E1E19CBDFD}"/>
-    <hyperlink ref="E239" r:id="rId267" xr:uid="{7EFFF805-CE73-433D-8429-8C55CEC7C072}"/>
-    <hyperlink ref="E139" r:id="rId268" xr:uid="{397DA75B-3BBC-4F89-A9DA-27EB8A53151E}"/>
-    <hyperlink ref="E143" r:id="rId269" xr:uid="{ACEE0CD9-D250-46A6-9BEB-25465E3F5877}"/>
-    <hyperlink ref="E142" r:id="rId270" xr:uid="{726ABE82-32B2-45DF-86E4-D4B65D08B99B}"/>
-    <hyperlink ref="E141" r:id="rId271" xr:uid="{DA3C02E3-82C2-4140-B503-2A624A7F3AA8}"/>
-    <hyperlink ref="E169" r:id="rId272" xr:uid="{880B159A-370B-40EE-A5C8-AE68325F8994}"/>
-    <hyperlink ref="E165" r:id="rId273" xr:uid="{96ACD224-977A-4E66-9264-5617B21A7B5A}"/>
-    <hyperlink ref="E166" r:id="rId274" xr:uid="{7FD7344C-2A6A-4318-A67E-05F8EA153E88}"/>
-    <hyperlink ref="E128" r:id="rId275" xr:uid="{B6515FE2-AD7F-4A71-83EF-89020758DE37}"/>
-    <hyperlink ref="E130" r:id="rId276" xr:uid="{E6A8EC51-88D3-49C6-B2C4-B1697B469A5B}"/>
-    <hyperlink ref="E86" r:id="rId277" xr:uid="{AB524FDC-322C-4129-B3D3-C0CD18DF6C39}"/>
-    <hyperlink ref="E76" r:id="rId278" xr:uid="{12F3604F-E330-4354-82A9-2E7144C6C69C}"/>
-    <hyperlink ref="E81" r:id="rId279" xr:uid="{27F80336-44DE-477D-A42B-75FF0BEAEB14}"/>
-    <hyperlink ref="E80" r:id="rId280" xr:uid="{CBD0C4A3-4F0E-49C4-B907-E32F28123DAA}"/>
-    <hyperlink ref="E82" r:id="rId281" xr:uid="{3496D658-F7DB-469C-8D98-A524DB1BB47C}"/>
-    <hyperlink ref="E238" r:id="rId282" xr:uid="{8C4590C0-E71B-4B6F-928F-91CDE3276DD9}"/>
-    <hyperlink ref="E237" r:id="rId283" xr:uid="{9D29C97A-A6D3-48A4-9664-8DCE5B234FAB}"/>
-    <hyperlink ref="E235" r:id="rId284" xr:uid="{9921A962-A113-4002-BDE2-4F4E4320B387}"/>
-    <hyperlink ref="E220" r:id="rId285" xr:uid="{2401C9CC-8D34-433A-BAAD-C1FD2BC14D49}"/>
-    <hyperlink ref="E226" r:id="rId286" xr:uid="{D146BB8F-137F-4456-BBA2-EC755F8EBC46}"/>
-    <hyperlink ref="E229" r:id="rId287" xr:uid="{E360B755-600F-4776-B306-2E5CFACE17ED}"/>
-    <hyperlink ref="E225" r:id="rId288" xr:uid="{A5B75A0D-986A-4F1A-B094-7B65E143FDE2}"/>
-    <hyperlink ref="E107" r:id="rId289" xr:uid="{F858A3E3-5FB0-420A-93A4-648662EF60EA}"/>
-    <hyperlink ref="E108" r:id="rId290" xr:uid="{E4B29D74-9296-485B-83BA-F2FBF277CAEE}"/>
-    <hyperlink ref="E47" r:id="rId291" xr:uid="{AFD749B1-917D-4B9C-A4A3-C3DEE02AC2C0}"/>
-    <hyperlink ref="E245" r:id="rId292" xr:uid="{0CCBA335-85C5-47D0-ABB1-7AD15CE9C6BE}"/>
-    <hyperlink ref="E253" r:id="rId293" xr:uid="{0556EF01-FFEF-410A-8AA8-8CA7BB356178}"/>
-    <hyperlink ref="E251" r:id="rId294" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="E252" r:id="rId295" xr:uid="{CEDFA42B-F516-4AB2-AC3C-789EA49C621B}"/>
-    <hyperlink ref="E56" r:id="rId296" xr:uid="{DD79BAA1-3570-429D-B5E3-B3B22125D45D}"/>
-    <hyperlink ref="E55" r:id="rId297" xr:uid="{AA3B5FD0-ABB7-481B-A828-1CEE4B997FFD}"/>
-    <hyperlink ref="E54" r:id="rId298" xr:uid="{BF9D025F-FFAE-4B6F-BE59-85E6A492D964}"/>
-    <hyperlink ref="E57" r:id="rId299" xr:uid="{25BF0BAB-C327-4860-BE43-460DA2024CB4}"/>
-    <hyperlink ref="E224" r:id="rId300" xr:uid="{A4991D16-BC46-4421-9733-4A0B675397D5}"/>
-    <hyperlink ref="E61" r:id="rId301" xr:uid="{3F28325A-419D-479F-A2CB-A6026E9C1738}"/>
-    <hyperlink ref="E62" r:id="rId302" xr:uid="{B55832FE-CDC8-476F-BFB2-210023AFDA15}"/>
-    <hyperlink ref="E64" r:id="rId303" xr:uid="{B0548B46-2425-4209-B406-7C5E06BB0B37}"/>
-    <hyperlink ref="E63" r:id="rId304" xr:uid="{7E1F57C3-1645-40A6-A0AB-E7D49C5BC286}"/>
-    <hyperlink ref="E67" r:id="rId305" xr:uid="{7F35F4C4-5217-404F-805D-AF7E847E2C3D}"/>
-    <hyperlink ref="E65" r:id="rId306" xr:uid="{492B5D03-5AAD-427D-BE79-33C2CF3C4B10}"/>
-    <hyperlink ref="E66" r:id="rId307" xr:uid="{DA981BF7-21C6-460F-8AB8-B7AC55085F27}"/>
-    <hyperlink ref="E49" r:id="rId308" xr:uid="{AC9DF199-9137-4950-AC5B-3422838E7898}"/>
-    <hyperlink ref="E60" r:id="rId309" xr:uid="{2F280586-B20D-4605-BEDE-548C581301E3}"/>
-    <hyperlink ref="E9" r:id="rId310" xr:uid="{B603EF92-ABB1-43FC-B014-BB1CE6C5F001}"/>
-    <hyperlink ref="E40" r:id="rId311" xr:uid="{7D969BE7-A6DA-49DE-A64E-EEB8E1A4033B}"/>
-    <hyperlink ref="E58" r:id="rId312" xr:uid="{80EB2D2F-2CD1-4A85-B0E5-21F5B54DC575}"/>
-    <hyperlink ref="E8" r:id="rId313" xr:uid="{3EDBF06D-E052-4275-A527-5A8869D64CDF}"/>
-    <hyperlink ref="E39" r:id="rId314" xr:uid="{131947D2-EAB0-4D8C-9AEF-22FB74118A82}"/>
-    <hyperlink ref="E154" r:id="rId315" xr:uid="{3F9A6173-1CC2-4924-8DCB-DA0907EBC497}"/>
-    <hyperlink ref="E23" r:id="rId316" xr:uid="{CFCB346F-57BF-4E1F-A83E-1ECF2056F264}"/>
-    <hyperlink ref="E102" r:id="rId317" xr:uid="{2356458E-6B22-49DA-9E6A-10397CF5FFCB}"/>
-    <hyperlink ref="E306" r:id="rId318" xr:uid="{4E26D969-664E-4EA5-BCDD-C0244659BD80}"/>
-    <hyperlink ref="E11" r:id="rId319" xr:uid="{79FBDA3E-6FA8-4642-9106-ECA30BC0F184}"/>
-    <hyperlink ref="E16" r:id="rId320" xr:uid="{76475329-A2A3-4832-B080-9DF1FCF7B69C}"/>
-    <hyperlink ref="E34" r:id="rId321" xr:uid="{712331F6-B9ED-461A-B3A4-361688CBC32C}"/>
-    <hyperlink ref="E18" r:id="rId322" xr:uid="{AF5DD662-70AC-4699-9546-0F375CEB30DD}"/>
-    <hyperlink ref="E20" r:id="rId323" xr:uid="{7983D009-F451-44FD-810F-30FF2A3718BA}"/>
-    <hyperlink ref="E19" r:id="rId324" xr:uid="{CD31F41D-EA1B-403F-8D0D-B77515C1536B}"/>
-    <hyperlink ref="E113" r:id="rId325" xr:uid="{127B98B1-79F3-43C9-B7FF-4FBC27351376}"/>
-    <hyperlink ref="E254" r:id="rId326" xr:uid="{2D7D988B-76D9-4BEC-8F29-806C1E841434}"/>
-    <hyperlink ref="E263" r:id="rId327" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="E255" r:id="rId328" xr:uid="{243B74CF-B5C2-468E-9F2F-0DA78790403B}"/>
-    <hyperlink ref="E256" r:id="rId329" xr:uid="{9E359A2D-80A4-4440-B6F6-E0BD637BE478}"/>
-    <hyperlink ref="E258" r:id="rId330" xr:uid="{92D99966-CAE9-4A3E-8110-212EFFA305D9}"/>
-    <hyperlink ref="E257" r:id="rId331" xr:uid="{82293A7C-C43B-41FD-91B1-86521EAC11D6}"/>
-    <hyperlink ref="E12" r:id="rId332" xr:uid="{68E8B6A2-6017-4405-9549-B2377AC5DEDF}"/>
-    <hyperlink ref="E259" r:id="rId333" xr:uid="{9E27F39A-FC85-46E5-98FF-497FB0860FA7}"/>
-    <hyperlink ref="E260" r:id="rId334" xr:uid="{3BF3C81C-57C8-46D6-BC82-B24998AE425F}"/>
-    <hyperlink ref="E261" r:id="rId335" xr:uid="{D60890AA-5FFE-44F0-AA27-28E4BFB644F6}"/>
-    <hyperlink ref="E262" r:id="rId336" xr:uid="{BEBCCD33-BF2B-422C-8302-61C8E85BEDED}"/>
-    <hyperlink ref="E307" r:id="rId337" xr:uid="{FC2672B5-6248-497C-B62C-4B7547222ED5}"/>
-    <hyperlink ref="E266" r:id="rId338" xr:uid="{98B6A04A-6AA6-4AC2-974B-16AADA142558}"/>
-    <hyperlink ref="E269" r:id="rId339" xr:uid="{8F938C70-22E3-4D8B-80C3-A2EDD6B55F32}"/>
-    <hyperlink ref="E283" r:id="rId340" xr:uid="{C19ECC48-6755-42E3-93AC-1AF2A6E16C8B}"/>
-    <hyperlink ref="E281" r:id="rId341" xr:uid="{96721404-CCF2-44A2-9BCC-E8604D34595E}"/>
-    <hyperlink ref="E279" r:id="rId342" xr:uid="{C4C7ED52-DB44-4C33-BB8E-35BEB7281A83}"/>
-    <hyperlink ref="E280" r:id="rId343" xr:uid="{5173BA28-5956-4E15-A77A-2EC7E30FC1EA}"/>
-    <hyperlink ref="E282" r:id="rId344" xr:uid="{74251C99-B647-4AF5-90FF-984998C44E82}"/>
-    <hyperlink ref="E285" r:id="rId345" xr:uid="{43E38533-4E5E-4A3A-B028-87FFDAEA95AF}"/>
-    <hyperlink ref="E265" r:id="rId346" xr:uid="{D8B34417-E714-44C5-92E5-677B9CA2E5A8}"/>
-    <hyperlink ref="E223" r:id="rId347" xr:uid="{CA41E718-82EA-4AAD-BE4C-17139F6C8FCA}"/>
-    <hyperlink ref="E284" r:id="rId348" xr:uid="{072FA124-769A-4A34-ABC3-93893442CE71}"/>
+    <hyperlink ref="E244" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="E246" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="E247" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="E264" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="E267" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="E268" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="E270" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="E271" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="E272" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="E273" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="E274" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="E275" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="E276" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="E277" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="E278" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="E286" r:id="rId188" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="E287" r:id="rId189" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="E288" r:id="rId190" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="E289" r:id="rId191" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="E290" r:id="rId192" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="E291" r:id="rId193" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="E294" r:id="rId194" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="E295" r:id="rId195" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="E296" r:id="rId196" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="E297" r:id="rId197" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="E298" r:id="rId198" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="E299" r:id="rId199" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="E248" r:id="rId200" xr:uid="{38535620-DA2F-45B6-BE53-7BE35BAD917E}"/>
+    <hyperlink ref="E180" r:id="rId201" xr:uid="{52A62708-7A1B-4947-8125-51CD78E69CDC}"/>
+    <hyperlink ref="E179" r:id="rId202" xr:uid="{90A2CCC4-C963-4688-BF93-898F1AB744EB}"/>
+    <hyperlink ref="G104" r:id="rId203" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="E104" r:id="rId204" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="E103" r:id="rId205" xr:uid="{DDFE149F-872D-40D3-A981-8A2101FAC9BF}"/>
+    <hyperlink ref="E121" r:id="rId206" xr:uid="{B257C977-A47D-4DB0-A09F-C2D9543F22CA}"/>
+    <hyperlink ref="E126" r:id="rId207" xr:uid="{6740D30D-5122-4656-A3AE-0D0EDF0D3361}"/>
+    <hyperlink ref="E125" r:id="rId208" xr:uid="{EE0FF2EF-5A82-4BD2-B997-460C3B05BAF9}"/>
+    <hyperlink ref="E124" r:id="rId209" xr:uid="{8D25C723-BF91-42D1-890E-9CA1BE036008}"/>
+    <hyperlink ref="E77" r:id="rId210" xr:uid="{30B8FDFC-E2BE-4DA3-8FA6-1249AA92CF95}"/>
+    <hyperlink ref="E89" r:id="rId211" xr:uid="{688A3619-4809-464A-A057-9B9FE946F793}"/>
+    <hyperlink ref="E43" r:id="rId212" xr:uid="{0372EC8E-7BC7-4EAC-B994-9672654B43D3}"/>
+    <hyperlink ref="E21" r:id="rId213" xr:uid="{86CAF600-E17D-4EA7-98D0-61A6B60486E9}"/>
+    <hyperlink ref="E6" r:id="rId214" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G6" r:id="rId215" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E14" r:id="rId216" xr:uid="{5942F87D-4C29-438D-B078-6CCBD6F5DD87}"/>
+    <hyperlink ref="G48" r:id="rId217" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="E48" r:id="rId218" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="E46" r:id="rId219" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="G45" r:id="rId220" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="E45" r:id="rId221" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="G44" r:id="rId222" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="E44" r:id="rId223" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="G42" r:id="rId224" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="E42" r:id="rId225" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="G38" r:id="rId226" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="E38" r:id="rId227" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="E37" r:id="rId228" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="E36" r:id="rId229" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="E35" r:id="rId230" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="E33" r:id="rId231" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="G31" r:id="rId232" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="E31" r:id="rId233" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="G30" r:id="rId234" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="E30" r:id="rId235" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="G28" r:id="rId236" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="E28" r:id="rId237" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="G26" r:id="rId238" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="E26" r:id="rId239" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="G25" r:id="rId240" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="E25" r:id="rId241" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="G24" r:id="rId242" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="E24" r:id="rId243" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="G22" r:id="rId244" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="E22" r:id="rId245" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="G17" r:id="rId246" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="E17" r:id="rId247" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="G13" r:id="rId248" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="E13" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="G10" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="E10" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="G7" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E7" r:id="rId253" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E302" r:id="rId254" xr:uid="{49C446A4-86D9-438E-8C85-C2CBF2D0C601}"/>
+    <hyperlink ref="E29" r:id="rId255" xr:uid="{15B4076B-7C29-451C-A0E0-E0CDB84955C7}"/>
+    <hyperlink ref="E303" r:id="rId256" xr:uid="{5897208F-5F6C-4E1B-8B0F-03D62428448A}"/>
+    <hyperlink ref="E41" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="E15" r:id="rId258" xr:uid="{36657CEA-F972-477D-AC24-77B031A0C947}"/>
+    <hyperlink ref="E304" r:id="rId259" xr:uid="{0B318E6F-5375-45A5-A623-A5D070F4F786}"/>
+    <hyperlink ref="E305" r:id="rId260" xr:uid="{28A35100-95C6-4598-8EAE-4903F97A507B}"/>
+    <hyperlink ref="E32" r:id="rId261" xr:uid="{A642EB9F-9B4D-467C-AA82-CE1A728B251C}"/>
+    <hyperlink ref="E27" r:id="rId262" xr:uid="{A1884A7B-6025-4BC0-B0A7-10DF9BA889E7}"/>
+    <hyperlink ref="E241" r:id="rId263" xr:uid="{DD148482-9331-495D-A315-B2667528DE27}"/>
+    <hyperlink ref="E234" r:id="rId264" xr:uid="{9AFBA357-2FAE-42C6-BAC6-9567300CA7EB}"/>
+    <hyperlink ref="E213" r:id="rId265" xr:uid="{222EEF32-42E7-41DB-92A2-B7E1E19CBDFD}"/>
+    <hyperlink ref="E239" r:id="rId266" xr:uid="{7EFFF805-CE73-433D-8429-8C55CEC7C072}"/>
+    <hyperlink ref="E139" r:id="rId267" xr:uid="{397DA75B-3BBC-4F89-A9DA-27EB8A53151E}"/>
+    <hyperlink ref="E143" r:id="rId268" xr:uid="{ACEE0CD9-D250-46A6-9BEB-25465E3F5877}"/>
+    <hyperlink ref="E142" r:id="rId269" xr:uid="{726ABE82-32B2-45DF-86E4-D4B65D08B99B}"/>
+    <hyperlink ref="E141" r:id="rId270" xr:uid="{DA3C02E3-82C2-4140-B503-2A624A7F3AA8}"/>
+    <hyperlink ref="E169" r:id="rId271" xr:uid="{880B159A-370B-40EE-A5C8-AE68325F8994}"/>
+    <hyperlink ref="E165" r:id="rId272" xr:uid="{96ACD224-977A-4E66-9264-5617B21A7B5A}"/>
+    <hyperlink ref="E166" r:id="rId273" xr:uid="{7FD7344C-2A6A-4318-A67E-05F8EA153E88}"/>
+    <hyperlink ref="E128" r:id="rId274" xr:uid="{B6515FE2-AD7F-4A71-83EF-89020758DE37}"/>
+    <hyperlink ref="E130" r:id="rId275" xr:uid="{E6A8EC51-88D3-49C6-B2C4-B1697B469A5B}"/>
+    <hyperlink ref="E86" r:id="rId276" xr:uid="{AB524FDC-322C-4129-B3D3-C0CD18DF6C39}"/>
+    <hyperlink ref="E76" r:id="rId277" xr:uid="{12F3604F-E330-4354-82A9-2E7144C6C69C}"/>
+    <hyperlink ref="E81" r:id="rId278" xr:uid="{27F80336-44DE-477D-A42B-75FF0BEAEB14}"/>
+    <hyperlink ref="E80" r:id="rId279" xr:uid="{CBD0C4A3-4F0E-49C4-B907-E32F28123DAA}"/>
+    <hyperlink ref="E82" r:id="rId280" xr:uid="{3496D658-F7DB-469C-8D98-A524DB1BB47C}"/>
+    <hyperlink ref="E238" r:id="rId281" xr:uid="{8C4590C0-E71B-4B6F-928F-91CDE3276DD9}"/>
+    <hyperlink ref="E237" r:id="rId282" xr:uid="{9D29C97A-A6D3-48A4-9664-8DCE5B234FAB}"/>
+    <hyperlink ref="E235" r:id="rId283" xr:uid="{9921A962-A113-4002-BDE2-4F4E4320B387}"/>
+    <hyperlink ref="E220" r:id="rId284" xr:uid="{2401C9CC-8D34-433A-BAAD-C1FD2BC14D49}"/>
+    <hyperlink ref="E226" r:id="rId285" xr:uid="{D146BB8F-137F-4456-BBA2-EC755F8EBC46}"/>
+    <hyperlink ref="E229" r:id="rId286" xr:uid="{E360B755-600F-4776-B306-2E5CFACE17ED}"/>
+    <hyperlink ref="E225" r:id="rId287" xr:uid="{A5B75A0D-986A-4F1A-B094-7B65E143FDE2}"/>
+    <hyperlink ref="E107" r:id="rId288" xr:uid="{F858A3E3-5FB0-420A-93A4-648662EF60EA}"/>
+    <hyperlink ref="E108" r:id="rId289" xr:uid="{E4B29D74-9296-485B-83BA-F2FBF277CAEE}"/>
+    <hyperlink ref="E47" r:id="rId290" xr:uid="{AFD749B1-917D-4B9C-A4A3-C3DEE02AC2C0}"/>
+    <hyperlink ref="E245" r:id="rId291" xr:uid="{0CCBA335-85C5-47D0-ABB1-7AD15CE9C6BE}"/>
+    <hyperlink ref="E253" r:id="rId292" xr:uid="{0556EF01-FFEF-410A-8AA8-8CA7BB356178}"/>
+    <hyperlink ref="E251" r:id="rId293" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="E252" r:id="rId294" xr:uid="{CEDFA42B-F516-4AB2-AC3C-789EA49C621B}"/>
+    <hyperlink ref="E56" r:id="rId295" xr:uid="{DD79BAA1-3570-429D-B5E3-B3B22125D45D}"/>
+    <hyperlink ref="E55" r:id="rId296" xr:uid="{AA3B5FD0-ABB7-481B-A828-1CEE4B997FFD}"/>
+    <hyperlink ref="E54" r:id="rId297" xr:uid="{BF9D025F-FFAE-4B6F-BE59-85E6A492D964}"/>
+    <hyperlink ref="E57" r:id="rId298" xr:uid="{25BF0BAB-C327-4860-BE43-460DA2024CB4}"/>
+    <hyperlink ref="E224" r:id="rId299" xr:uid="{A4991D16-BC46-4421-9733-4A0B675397D5}"/>
+    <hyperlink ref="E61" r:id="rId300" xr:uid="{3F28325A-419D-479F-A2CB-A6026E9C1738}"/>
+    <hyperlink ref="E62" r:id="rId301" xr:uid="{B55832FE-CDC8-476F-BFB2-210023AFDA15}"/>
+    <hyperlink ref="E64" r:id="rId302" xr:uid="{B0548B46-2425-4209-B406-7C5E06BB0B37}"/>
+    <hyperlink ref="E63" r:id="rId303" xr:uid="{7E1F57C3-1645-40A6-A0AB-E7D49C5BC286}"/>
+    <hyperlink ref="E67" r:id="rId304" xr:uid="{7F35F4C4-5217-404F-805D-AF7E847E2C3D}"/>
+    <hyperlink ref="E65" r:id="rId305" xr:uid="{492B5D03-5AAD-427D-BE79-33C2CF3C4B10}"/>
+    <hyperlink ref="E66" r:id="rId306" xr:uid="{DA981BF7-21C6-460F-8AB8-B7AC55085F27}"/>
+    <hyperlink ref="E49" r:id="rId307" xr:uid="{AC9DF199-9137-4950-AC5B-3422838E7898}"/>
+    <hyperlink ref="E60" r:id="rId308" xr:uid="{2F280586-B20D-4605-BEDE-548C581301E3}"/>
+    <hyperlink ref="E9" r:id="rId309" xr:uid="{B603EF92-ABB1-43FC-B014-BB1CE6C5F001}"/>
+    <hyperlink ref="E40" r:id="rId310" xr:uid="{7D969BE7-A6DA-49DE-A64E-EEB8E1A4033B}"/>
+    <hyperlink ref="E58" r:id="rId311" xr:uid="{80EB2D2F-2CD1-4A85-B0E5-21F5B54DC575}"/>
+    <hyperlink ref="E8" r:id="rId312" xr:uid="{3EDBF06D-E052-4275-A527-5A8869D64CDF}"/>
+    <hyperlink ref="E39" r:id="rId313" xr:uid="{131947D2-EAB0-4D8C-9AEF-22FB74118A82}"/>
+    <hyperlink ref="E154" r:id="rId314" xr:uid="{3F9A6173-1CC2-4924-8DCB-DA0907EBC497}"/>
+    <hyperlink ref="E23" r:id="rId315" xr:uid="{CFCB346F-57BF-4E1F-A83E-1ECF2056F264}"/>
+    <hyperlink ref="E102" r:id="rId316" xr:uid="{2356458E-6B22-49DA-9E6A-10397CF5FFCB}"/>
+    <hyperlink ref="E306" r:id="rId317" xr:uid="{4E26D969-664E-4EA5-BCDD-C0244659BD80}"/>
+    <hyperlink ref="E11" r:id="rId318" xr:uid="{79FBDA3E-6FA8-4642-9106-ECA30BC0F184}"/>
+    <hyperlink ref="E16" r:id="rId319" xr:uid="{76475329-A2A3-4832-B080-9DF1FCF7B69C}"/>
+    <hyperlink ref="E34" r:id="rId320" xr:uid="{712331F6-B9ED-461A-B3A4-361688CBC32C}"/>
+    <hyperlink ref="E18" r:id="rId321" xr:uid="{AF5DD662-70AC-4699-9546-0F375CEB30DD}"/>
+    <hyperlink ref="E20" r:id="rId322" xr:uid="{7983D009-F451-44FD-810F-30FF2A3718BA}"/>
+    <hyperlink ref="E19" r:id="rId323" xr:uid="{CD31F41D-EA1B-403F-8D0D-B77515C1536B}"/>
+    <hyperlink ref="E113" r:id="rId324" xr:uid="{127B98B1-79F3-43C9-B7FF-4FBC27351376}"/>
+    <hyperlink ref="E254" r:id="rId325" xr:uid="{2D7D988B-76D9-4BEC-8F29-806C1E841434}"/>
+    <hyperlink ref="E263" r:id="rId326" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="E255" r:id="rId327" xr:uid="{243B74CF-B5C2-468E-9F2F-0DA78790403B}"/>
+    <hyperlink ref="E256" r:id="rId328" xr:uid="{9E359A2D-80A4-4440-B6F6-E0BD637BE478}"/>
+    <hyperlink ref="E258" r:id="rId329" xr:uid="{92D99966-CAE9-4A3E-8110-212EFFA305D9}"/>
+    <hyperlink ref="E257" r:id="rId330" xr:uid="{82293A7C-C43B-41FD-91B1-86521EAC11D6}"/>
+    <hyperlink ref="E12" r:id="rId331" xr:uid="{68E8B6A2-6017-4405-9549-B2377AC5DEDF}"/>
+    <hyperlink ref="E259" r:id="rId332" xr:uid="{9E27F39A-FC85-46E5-98FF-497FB0860FA7}"/>
+    <hyperlink ref="E260" r:id="rId333" xr:uid="{3BF3C81C-57C8-46D6-BC82-B24998AE425F}"/>
+    <hyperlink ref="E261" r:id="rId334" xr:uid="{D60890AA-5FFE-44F0-AA27-28E4BFB644F6}"/>
+    <hyperlink ref="E262" r:id="rId335" xr:uid="{BEBCCD33-BF2B-422C-8302-61C8E85BEDED}"/>
+    <hyperlink ref="E307" r:id="rId336" xr:uid="{FC2672B5-6248-497C-B62C-4B7547222ED5}"/>
+    <hyperlink ref="E266" r:id="rId337" xr:uid="{98B6A04A-6AA6-4AC2-974B-16AADA142558}"/>
+    <hyperlink ref="E269" r:id="rId338" xr:uid="{8F938C70-22E3-4D8B-80C3-A2EDD6B55F32}"/>
+    <hyperlink ref="E283" r:id="rId339" xr:uid="{C19ECC48-6755-42E3-93AC-1AF2A6E16C8B}"/>
+    <hyperlink ref="E281" r:id="rId340" xr:uid="{96721404-CCF2-44A2-9BCC-E8604D34595E}"/>
+    <hyperlink ref="E279" r:id="rId341" xr:uid="{C4C7ED52-DB44-4C33-BB8E-35BEB7281A83}"/>
+    <hyperlink ref="E280" r:id="rId342" xr:uid="{5173BA28-5956-4E15-A77A-2EC7E30FC1EA}"/>
+    <hyperlink ref="E282" r:id="rId343" xr:uid="{74251C99-B647-4AF5-90FF-984998C44E82}"/>
+    <hyperlink ref="E285" r:id="rId344" xr:uid="{43E38533-4E5E-4A3A-B028-87FFDAEA95AF}"/>
+    <hyperlink ref="E265" r:id="rId345" xr:uid="{D8B34417-E714-44C5-92E5-677B9CA2E5A8}"/>
+    <hyperlink ref="E223" r:id="rId346" xr:uid="{CA41E718-82EA-4AAD-BE4C-17139F6C8FCA}"/>
+    <hyperlink ref="E284" r:id="rId347" xr:uid="{072FA124-769A-4A34-ABC3-93893442CE71}"/>
+    <hyperlink ref="E243" r:id="rId348" xr:uid="{8E752A2D-DD17-49AE-AC4C-832B03439826}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId349"/>
